--- a/personal/streeteasy-2026-07-12/streeteasy_listings_2026-07-12.xlsx
+++ b/personal/streeteasy-2026-07-12/streeteasy_listings_2026-07-12.xlsx
@@ -965,7 +965,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN2" s="4" t="n"/>
+      <c r="AN2" s="4" t="n">
+        <v>6995</v>
+      </c>
       <c r="AO2" s="5" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $6,995</t>
@@ -1209,7 +1211,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN3" s="8" t="n"/>
+      <c r="AN3" s="8" t="n">
+        <v>7995</v>
+      </c>
       <c r="AO3" s="9" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $7,995</t>
@@ -1410,7 +1414,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN4" s="4" t="n"/>
+      <c r="AN4" s="4" t="n">
+        <v>7995</v>
+      </c>
       <c r="AO4" s="5" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $7,995</t>
@@ -1616,7 +1622,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN5" s="8" t="n"/>
+      <c r="AN5" s="8" t="n">
+        <v>7995</v>
+      </c>
       <c r="AO5" s="9" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $7,995</t>
@@ -1821,7 +1829,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN6" s="4" t="n"/>
+      <c r="AN6" s="4" t="n">
+        <v>8995</v>
+      </c>
       <c r="AO6" s="5" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $8,995</t>
@@ -2006,7 +2016,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN7" s="8" t="n"/>
+      <c r="AN7" s="8" t="n">
+        <v>9500</v>
+      </c>
       <c r="AO7" s="9" t="inlineStr">
         <is>
           <t>Application fee: $300; Background check: $50; Security deposit: $9,500; Early termination: $9,500</t>
@@ -2229,7 +2241,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN8" s="4" t="n"/>
+      <c r="AN8" s="4" t="n">
+        <v>10600</v>
+      </c>
       <c r="AO8" s="5" t="inlineStr">
         <is>
           <t>Application fee: $20; Pet deposit: $250; Security deposit: $10,600; Bike storage: $15; Community amenity: $50; Storage: $50</t>
@@ -2436,7 +2450,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN9" s="8" t="n"/>
+      <c r="AN9" s="8" t="n">
+        <v>12500</v>
+      </c>
       <c r="AO9" s="9" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $12,500</t>
@@ -2643,7 +2659,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN10" s="4" t="n"/>
+      <c r="AN10" s="4" t="n">
+        <v>13400</v>
+      </c>
       <c r="AO10" s="5" t="inlineStr">
         <is>
           <t>Administration: $17; Application fee: $20; Security deposit: $13,400</t>
@@ -2843,7 +2861,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN11" s="8" t="n"/>
+      <c r="AN11" s="8" t="n">
+        <v>14750</v>
+      </c>
       <c r="AO11" s="9" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $14,750</t>
@@ -3048,7 +3068,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN12" s="4" t="n"/>
+      <c r="AN12" s="4" t="n">
+        <v>8300</v>
+      </c>
       <c r="AO12" s="5" t="inlineStr">
         <is>
           <t>Application fee: $0; Security deposit: $8,300</t>
@@ -3257,7 +3279,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN13" s="8" t="n"/>
+      <c r="AN13" s="8" t="n">
+        <v>10850</v>
+      </c>
       <c r="AO13" s="9" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $10,850</t>
@@ -3490,7 +3514,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN14" s="4" t="n"/>
+      <c r="AN14" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AO14" s="5" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $0</t>
@@ -3697,7 +3723,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN15" s="8" t="n"/>
+      <c r="AN15" s="8" t="n">
+        <v>18000</v>
+      </c>
       <c r="AO15" s="9" t="inlineStr">
         <is>
           <t>Move-in deposit: $500; Application fee: $0; Security deposit: $18,000</t>
@@ -3901,7 +3929,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN16" s="4" t="n"/>
+      <c r="AN16" s="4" t="n">
+        <v>18000</v>
+      </c>
       <c r="AO16" s="5" t="inlineStr">
         <is>
           <t>Application fee: $18,000; Security deposit: $18,000</t>
@@ -4136,7 +4166,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN17" s="8" t="n"/>
+      <c r="AN17" s="8" t="n">
+        <v>6995</v>
+      </c>
       <c r="AO17" s="9" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $6,995</t>
@@ -4362,7 +4394,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN18" s="4" t="n"/>
+      <c r="AN18" s="4" t="n">
+        <v>8250</v>
+      </c>
       <c r="AO18" s="5" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $8,250</t>
@@ -4752,7 +4786,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN20" s="4" t="n"/>
+      <c r="AN20" s="4" t="n">
+        <v>12000</v>
+      </c>
       <c r="AO20" s="5" t="inlineStr">
         <is>
           <t>Application fee: $0; Security deposit: $12,000; Credit check: $20</t>
@@ -4948,7 +4984,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN21" s="8" t="n"/>
+      <c r="AN21" s="8" t="n">
+        <v>16500</v>
+      </c>
       <c r="AO21" s="9" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $16,500</t>
@@ -5715,7 +5753,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN25" s="8" t="n"/>
+      <c r="AN25" s="8" t="n">
+        <v>8995</v>
+      </c>
       <c r="AO25" s="9" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $8,995</t>
@@ -5926,7 +5966,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN26" s="4" t="n"/>
+      <c r="AN26" s="4" t="n">
+        <v>4750</v>
+      </c>
       <c r="AO26" s="5" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $4,750</t>
@@ -6127,7 +6169,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN27" s="8" t="n"/>
+      <c r="AN27" s="8" t="n">
+        <v>4997.5</v>
+      </c>
       <c r="AO27" s="9" t="inlineStr">
         <is>
           <t>Move-in fee: $80; Application fee: $20; Key replacement: $75; Security deposit: $4,998</t>
@@ -6337,7 +6381,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN28" s="4" t="n"/>
+      <c r="AN28" s="4" t="n">
+        <v>11995</v>
+      </c>
       <c r="AO28" s="5" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $11,995</t>
@@ -6534,7 +6580,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN29" s="8" t="n"/>
+      <c r="AN29" s="8" t="n">
+        <v>5997.5</v>
+      </c>
       <c r="AO29" s="9" t="inlineStr">
         <is>
           <t>Move-in fee: $80; Application fee: $20; Key replacement: $75; Security deposit: $5,998</t>
@@ -6750,7 +6798,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN30" s="4" t="n"/>
+      <c r="AN30" s="4" t="n">
+        <v>12500</v>
+      </c>
       <c r="AO30" s="5" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $12,500</t>
@@ -6955,7 +7005,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN31" s="8" t="n"/>
+      <c r="AN31" s="8" t="n">
+        <v>14000</v>
+      </c>
       <c r="AO31" s="9" t="inlineStr">
         <is>
           <t>Application fee: $0; Security deposit: $14,000</t>
@@ -7164,7 +7216,9 @@
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN32" s="4" t="n"/>
+      <c r="AN32" s="4" t="n">
+        <v>16999</v>
+      </c>
       <c r="AO32" s="5" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $16,999</t>

--- a/personal/streeteasy-2026-07-12/streeteasy_listings_2026-07-12.xlsx
+++ b/personal/streeteasy-2026-07-12/streeteasy_listings_2026-07-12.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Listings 2026-07-12'!$A$1:$BC$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Listings 2026-07-12'!$A$1:$BC$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC32"/>
+  <dimension ref="A1:BC40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -818,27 +818,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5090360</t>
+          <t>5098192</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>https://streeteasy.com/rental/5090360</t>
+          <t>https://streeteasy.com/rental/5098192</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>356 East 8th Street GARDEN-LEVEL</t>
+          <t>359 West 18th Street #2</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>GARDEN-LEVEL</t>
+          <t>#2</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>East Village</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -848,11 +848,11 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>10009</t>
+          <t>10011</t>
         </is>
       </c>
       <c r="H2" s="4" t="n">
-        <v>6995</v>
+        <v>8395</v>
       </c>
       <c r="I2" s="4" t="n"/>
       <c r="J2" s="2" t="n"/>
@@ -861,23 +861,23 @@
         <v>2</v>
       </c>
       <c r="M2" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N2" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="O2" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>750</v>
+        <v>900</v>
       </c>
       <c r="Q2" s="4" t="n">
         <v>112</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>Rental unit</t>
+          <t>Two-family home</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
@@ -887,67 +887,55 @@
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U2" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>Garden; Roof Rights</t>
+          <t>Terrace</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>City; Garden</t>
         </is>
       </c>
       <c r="Y2" s="5" t="inlineStr">
         <is>
-          <t>Central Ac; Hardwood Floors; Private Outdoor Space; View; Washer Dryer</t>
-        </is>
-      </c>
-      <c r="Z2" s="5" t="inlineStr">
-        <is>
-          <t>Doorman; Fios Available; Shared Outdoor Space</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
+          <t>Fireplace; Hardwood Floors; Private Outdoor Space; View</t>
+        </is>
+      </c>
+      <c r="Z2" s="5" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
       <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>Roof Deck</t>
-        </is>
-      </c>
+      <c r="AC2" s="2" t="inlineStr"/>
       <c r="AD2" s="2" t="inlineStr"/>
       <c r="AE2" s="2" t="inlineStr"/>
       <c r="AF2" s="2" t="n">
-        <v>2026</v>
+        <v>1910</v>
       </c>
       <c r="AG2" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AI2" s="2" t="inlineStr">
         <is>
-          <t>R New York</t>
+          <t>Corcoran</t>
         </is>
       </c>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>R New York</t>
+          <t>Corcoran Group</t>
         </is>
       </c>
       <c r="AK2" s="2" t="inlineStr">
@@ -957,7 +945,7 @@
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>641 Lexington Avenue, 22nd Floor, New York, NY, 10022</t>
+          <t>590 Madison Avenue, New York, NY, 10022</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
@@ -966,29 +954,29 @@
         </is>
       </c>
       <c r="AN2" s="4" t="n">
-        <v>6995</v>
+        <v>8395</v>
       </c>
       <c r="AO2" s="5" t="inlineStr">
         <is>
-          <t>Application fee: $20; Security deposit: $6,995</t>
+          <t>Application fee: $20; Security deposit: $8,395</t>
         </is>
       </c>
       <c r="AP2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02: $6,995</t>
+          <t>2026-07-09: $8,395</t>
         </is>
       </c>
       <c r="AQ2" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02: $6,995 ACTIVE</t>
+          <t>2026-07-12: $8,395 ACTIVE; 2025-07-15: $7,900 RENTED; 2025-07-15: $7,900 IN_CONTRACT; 2025-06-26: $7,900 ACTIVE; 2022-09-15: $5,750 RENTED; 2022-08-12: $5,750 None; 2022-08-12: $4,500 IN_CONTRACT; 2022-08-08: $4,500 TEMPORARILY_OFF_MARKET; 2022-08-04: $4,500 ACTIVE; 2020-10-26: $4,800 DELISTED; 2020-08-05: $4,800 ACTIVE; 2017-07-26: $4,800 RENTED; 2016-10-27: $4,800 NO_LONGER_AVAILABLE; 2016-10-06: $4,800 None; 2016-09-08: $5,500 ACTIVE</t>
         </is>
       </c>
       <c r="AR2" s="4" t="n">
-        <v>5495</v>
+        <v>8600</v>
       </c>
       <c r="AS2" s="2" t="inlineStr"/>
       <c r="AT2" s="2" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="AU2" s="2" t="n">
         <v>0</v>
@@ -1004,13 +992,1047 @@
         </is>
       </c>
       <c r="AZ2" s="2" t="n">
-        <v>40.72432</v>
+        <v>40.743416</v>
       </c>
       <c r="BA2" s="2" t="n">
-        <v>-73.97812</v>
+        <v>-74.003075</v>
       </c>
       <c r="BB2" s="2" t="inlineStr"/>
       <c r="BC2" s="5" t="inlineStr">
+        <is>
+          <t>Rare &amp; Sun-Drenched Duplex Townhouse with Private Terrace in Prime Chelsea
+Welcome home to this unique and charming 900-square-foot duplex apartment, nestled inside a highly private, 3-story boutique townhouse with only two residences. Offering the perfect blend of classic New York character and modern outdoor luxury, this 2-bedroom, 1.5-bathroom sanctuary is a rare Chelsea find.
+The First Level: 
+Living &amp; Entertaining: Walk into a sprawling, full-floor living area anchored by stunning exposed brick walls, rich hardwood floors, and exceptional natural light pouring in from oversized windows facing both north and south. The open, windowed kitchen features a dishwasher and flows seamlessly into the main living space, making it perfect for entertaining. Step right outside onto your own private terrace—an urban oasis ideal for morning coffee, evening grilling, or testing out your green thumb.
+The Upper Level: 
+The Private Quarters: Head up the stairs to find two bright, sun-filled bedrooms that comfortably accommodate King and Queen-sized beds. This level boasts authentic post-and-beam ceilings, an additional full bathroom, and a classic wood-burning fireplace that adds unmatched warmth and character.
+Neighborhood &amp; Lifestyle:
+Located on a serene, picture-perfect, tree-lined Chelsea block, you are steps away from the very best of Downtown Manhattan. Grab fresh ingredients from the nearby Trader Joe’s or Chelsea Market, take a sunset stroll along the High Line and Hudson River Park, or explore the world-class dining and galleries right outside your door.
+Features &amp; Highlights:
+* Rare duplex layout in a private townhouse (only 2 units total)
+* Private terrace perfect for dining and BBQing
+* Hardwood floors &amp; exposed brick throughout
+* Wood-burning fireplace &amp; authentic post-and-beam ceilings
+* Pass-through, windowed kitchen with dishwasher
+* Generous closet space and oversized windows with north/south exposures
+* Excellent transit options: access to the A, C, E, L, 1, 2, 3, F, and M trains
+* Small pets welcome!
+Please note that photos with furniture are virtually staged, and the red wall is currently painted white.
+Move-in costs include a $20 rental application fee, first month's rent, and one month's security deposit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>5093619</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>https://streeteasy.com/rental/5093619</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>135 West 15th Street #1</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>10011</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>10500</v>
+      </c>
+      <c r="I3" s="8" t="n"/>
+      <c r="J3" s="6" t="n"/>
+      <c r="K3" s="6" t="n"/>
+      <c r="L3" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr"/>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>Four-family home</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="V3" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="W3" s="6" t="inlineStr">
+        <is>
+          <t>Garden</t>
+        </is>
+      </c>
+      <c r="X3" s="6" t="inlineStr">
+        <is>
+          <t>City; Garden</t>
+        </is>
+      </c>
+      <c r="Y3" s="9" t="inlineStr">
+        <is>
+          <t>Central Ac; Hardwood Floors; Private Outdoor Space; View; Washer Dryer</t>
+        </is>
+      </c>
+      <c r="Z3" s="9" t="inlineStr">
+        <is>
+          <t>Fios Available</t>
+        </is>
+      </c>
+      <c r="AA3" s="6" t="inlineStr"/>
+      <c r="AB3" s="6" t="inlineStr"/>
+      <c r="AC3" s="6" t="inlineStr"/>
+      <c r="AD3" s="6" t="inlineStr"/>
+      <c r="AE3" s="6" t="inlineStr"/>
+      <c r="AF3" s="6" t="n">
+        <v>1910</v>
+      </c>
+      <c r="AG3" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH3" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI3" s="6" t="inlineStr">
+        <is>
+          <t>Corcoran</t>
+        </is>
+      </c>
+      <c r="AJ3" s="6" t="inlineStr">
+        <is>
+          <t>Corcoran Group</t>
+        </is>
+      </c>
+      <c r="AK3" s="6" t="inlineStr">
+        <is>
+          <t>Limited Liability Broker</t>
+        </is>
+      </c>
+      <c r="AL3" s="6" t="inlineStr">
+        <is>
+          <t>590 Madison Avenue, New York, NY, 10022</t>
+        </is>
+      </c>
+      <c r="AM3" s="6" t="inlineStr">
+        <is>
+          <t>None listed</t>
+        </is>
+      </c>
+      <c r="AN3" s="8" t="n">
+        <v>10500</v>
+      </c>
+      <c r="AO3" s="9" t="inlineStr">
+        <is>
+          <t>Application fee: $20; Security deposit: $10,500</t>
+        </is>
+      </c>
+      <c r="AP3" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06: $10,500</t>
+        </is>
+      </c>
+      <c r="AQ3" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-06: $10,500 ACTIVE</t>
+        </is>
+      </c>
+      <c r="AR3" s="8" t="n">
+        <v>9895</v>
+      </c>
+      <c r="AS3" s="6" t="inlineStr"/>
+      <c r="AT3" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="6" t="inlineStr"/>
+      <c r="AX3" s="6" t="inlineStr"/>
+      <c r="AY3" s="6" t="inlineStr">
+        <is>
+          <t>PARTNER</t>
+        </is>
+      </c>
+      <c r="AZ3" s="6" t="n">
+        <v>40.73884</v>
+      </c>
+      <c r="BA3" s="6" t="n">
+        <v>-73.99762</v>
+      </c>
+      <c r="BB3" s="6" t="inlineStr"/>
+      <c r="BC3" s="9" t="inlineStr">
+        <is>
+          <t>135 West 15th Street — A Serene Chelsea Townhouse Garden Residence
+Reside in a beautifully renovated Chelsea GARDEN townhouse residence with private backyard, central AC throughout, two striking full bathrooms, and flexible three-bedroom living in the heart of downtown Manhattan where Chelsea meets West Village vibes!
+Set within a classic townhouse on one of Chelsea’s most convenient blocks, this home offers a rare blend of private outdoor space, townhouse character, and flexible interior use. The layout can function as a true three-bedroom, or as a two-bedroom with a separate den, media room, home office, or secondary living area.
+The front room features exposed brick, oversized windows, warm wood trim, and excellent character, making it ideal as a lounge, den, or additional bedroom. The open kitchen/dining area in the center of the home offers plenty of room to dine or entertain in. Both the rear bedrooms open toward the garden and offers plenty of light coming from double corner exposure windows. Two pristine luxurious bathrooms are finished with clean modern tile, glass shower/tub enclosures, updated vanities, and a polished contemporary feel. There's also an enormous walk-in closet for all your storage needs and an entry foyer/mud room area with built-in shoe storage.
+The private backyard is the true standout: a rare Chelsea outdoor retreat with room for lounging, dining, and entertaining. It becomes a true extension of the residence and a major lifestyle feature.
+Located at 135 West 15th Street, the home sits at the crossroads of Chelsea, the West Village, Flatiron, and Union Square, with easy access to the 1/2/3, A/C/E, F/M, L, and PATH trains, plus neighborhood favorites along 7th Avenue, 8th Avenue, 14th Street, and the surrounding downtown corridor.
+FARE Act disclosure charges: $20 application fee to run credit when applying, and due at signing is 1 month rent and 1 month security deposit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>5088856</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>https://streeteasy.com/rental/5088856</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>245 West 25th Street #PHD</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>#PHD</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>12995</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>11912</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>1356</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>115</v>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Rental unit</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>Private Roof Deck</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="5" t="inlineStr">
+        <is>
+          <t>Central Ac; Dishwasher; Hardwood Floors; Private Outdoor Space; Washer Dryer</t>
+        </is>
+      </c>
+      <c r="Z4" s="5" t="inlineStr">
+        <is>
+          <t>Bike Room; Doorman; Elevator; Fios Available; Gym; Laundry; Live In Super; Package Room; Shared Outdoor Space; Storage Space; Wheelchair Access</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>Roof Deck</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>Locker Cage</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>The Arthur</t>
+        </is>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>1938</v>
+      </c>
+      <c r="AG4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH4" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="AI4" s="2" t="inlineStr">
+        <is>
+          <t>Compass</t>
+        </is>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>Compass</t>
+        </is>
+      </c>
+      <c r="AK4" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Broker</t>
+        </is>
+      </c>
+      <c r="AL4" s="2" t="inlineStr">
+        <is>
+          <t>90 5th Avenue, 3rd Floor, New York, NY, 10011-7624</t>
+        </is>
+      </c>
+      <c r="AM4" s="2" t="inlineStr">
+        <is>
+          <t>None listed</t>
+        </is>
+      </c>
+      <c r="AN4" s="4" t="n">
+        <v>12995</v>
+      </c>
+      <c r="AO4" s="5" t="inlineStr">
+        <is>
+          <t>Application fee: $20; Security deposit: $12,995</t>
+        </is>
+      </c>
+      <c r="AP4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01: $12,995</t>
+        </is>
+      </c>
+      <c r="AQ4" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01: $12,995 ACTIVE; 2025-06-18: $10,900 RENTED; 2025-06-14: $10,900 IN_CONTRACT; 2025-06-11: $10,900 ACTIVE; 2023-11-08: $9,800 RENTED; 2023-10-12: $9,800 None; 2023-09-28: $10,900 ACTIVE; 2023-09-18: $10,900 RENTED; 2023-09-14: $10,900 ACTIVE; 2021-09-24: $9,500 RENTED; 2021-08-24: $9,500 ACTIVE; 2019-07-01: $7,998 RENTED; 2019-06-25: $7,998 IN_CONTRACT; 2019-06-17: $7,998 None; 2019-06-04: $8,755 ACTIVE; 2017-05-26: $7,880 NO_LONGER_AVAILABLE; 2017-05-23: $7,880 IN_CONTRACT; 2017-05-23: $7,880 None; 2017-05-11: $7,335 None; 2017-04-24: $8,065 None; 2017-03-20: $8,425 ACTIVE; 2016-08-08: $8,250 RENTED; 2016-08-03: $8,250 IN_CONTRACT; 2016-07-12: $8,250 None; 2016-07-06: $8,874 ACTIVE; 2016-02-17: $8,075 RENTED; 2015-12-22: $8,075 NO_LONGER_AVAILABLE; 2015-12-01: $8,075 None; 2015-11-08: $9,500 ACTIVE</t>
+        </is>
+      </c>
+      <c r="AR4" s="4" t="n">
+        <v>9895</v>
+      </c>
+      <c r="AS4" s="2" t="inlineStr">
+        <is>
+          <t>{'id': '20990578', 'startTime': '2026-07-16T16:00:00.000-04:00', 'endTime': '2026-07-16T17:00:00.000-04:00', 'appointmentOnly': True, 'showingNotes': None}</t>
+        </is>
+      </c>
+      <c r="AT4" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW4" s="2" t="inlineStr"/>
+      <c r="AX4" s="2" t="inlineStr"/>
+      <c r="AY4" s="2" t="inlineStr">
+        <is>
+          <t>PARTNER</t>
+        </is>
+      </c>
+      <c r="AZ4" s="2" t="n">
+        <v>40.746346</v>
+      </c>
+      <c r="BA4" s="2" t="n">
+        <v>-73.996414</v>
+      </c>
+      <c r="BB4" s="2" t="inlineStr"/>
+      <c r="BC4" s="5" t="inlineStr">
+        <is>
+          <t>*Chelsea Luxury - Spacious 3BD/2BA Duplex Penthouse Unit with Massive Private Terrace, Stainless Steel Appliances, D/W, M/W, Washer/Dryer In Unit, in a Pet-Friendly Elevator Building with Rooftop Terrace and Outdoor Shower, BBQ Area, On-Site Fitness Center, Lounge, Bike and Private Storage Available, and Live-In Super*
+Welcome to The Arthur, a building redefined with newly renovated interiors and modern amenities. The residences at 245 West 25th Street boast luxurious features including entrance foyer blending to a large, open step-down living space, unbelievable closet space, additional storage, in-unit Bosch washer and dryer, custom kitchens with stainless steel appliances, white lacquer cabinets, Caesarstone countertops and backsplashes, and porcelain tile-clad bathrooms with custom vanities and glass-enclosed showers. The apartment features classic hardwood floors throughout, solid core wood doors with chrome hardware.
+The custom Chef's Kitchen features a coordinated stainless steel appliance package, complete with dishwasher and built-in microwave. The countertops and large-tiled backsplash enhance the lacquered soft closing cabinets.
+Located in the heart of Chelsea, this is truly in the middle of one of Manhattan’s most desirable neighborhoods – known for its famous art galleries, the High Line, shopping and dining. The Arthur is close to public transportation and everyday conveniences like Whole Foods, Trader Joe's, and Crunch Fitness.
+This luxury residence puts you in the center of an all-encompassing lifestyle offering 24-hour doorman, elevator, gym, live in super, Verizon Fios, a fully landscaped roof garden with bbq, bike storage, and private storage also available. All housed on an amazing tree-lined street. The apartment is perfectly positioned to give you the best New York City experience and is pet-friendly to boot. Photos of similar unit.
+**Pursuant to the Fairness in Apartment Rental Expenses (FARE) Act and the Fair Housing Act, we are required to disclose all fees associated with the rental process.
+A comprehensive list of fees will be disclosed prior to lease signing in the form of a Tenant Fee Disclosure form and will include and is not limited to the following:
+Application Fee: $20 per leaseholder/guarantor
+Security Deposit: Equal to 1 month’s rent
+First Month’s rent: Equal to First Month’s rent **</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>5070347</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>https://streeteasy.com/rental/5070347</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>152 9th Avenue #2</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>10011</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>13900</v>
+      </c>
+      <c r="I5" s="8" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>Mixed-use building</t>
+        </is>
+      </c>
+      <c r="S5" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="T5" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="U5" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="V5" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="W5" s="6" t="inlineStr">
+        <is>
+          <t>Private Roof Deck</t>
+        </is>
+      </c>
+      <c r="X5" s="6" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="Y5" s="9" t="inlineStr">
+        <is>
+          <t>Dishwasher; Fireplace; Hardwood Floors; Private Outdoor Space; View; Washer Dryer</t>
+        </is>
+      </c>
+      <c r="Z5" s="9" t="inlineStr">
+        <is>
+          <t>Doorman; Fios Available</t>
+        </is>
+      </c>
+      <c r="AA5" s="6" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="AB5" s="6" t="inlineStr"/>
+      <c r="AC5" s="6" t="inlineStr"/>
+      <c r="AD5" s="6" t="inlineStr"/>
+      <c r="AE5" s="6" t="inlineStr"/>
+      <c r="AF5" s="6" t="n">
+        <v>1910</v>
+      </c>
+      <c r="AG5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI5" s="6" t="inlineStr">
+        <is>
+          <t>Douglas Elliman</t>
+        </is>
+      </c>
+      <c r="AJ5" s="6" t="inlineStr">
+        <is>
+          <t>Douglas Elliman Real Estate</t>
+        </is>
+      </c>
+      <c r="AK5" s="6" t="inlineStr">
+        <is>
+          <t>Limited Liability Broker</t>
+        </is>
+      </c>
+      <c r="AL5" s="6" t="inlineStr">
+        <is>
+          <t>575 Madison Avenue, 4th Floor, New York, NY, 10022</t>
+        </is>
+      </c>
+      <c r="AM5" s="6" t="inlineStr">
+        <is>
+          <t>None listed</t>
+        </is>
+      </c>
+      <c r="AN5" s="8" t="n">
+        <v>13900</v>
+      </c>
+      <c r="AO5" s="9" t="inlineStr">
+        <is>
+          <t>Application fee: $20; Security deposit: $13,900</t>
+        </is>
+      </c>
+      <c r="AP5" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-11: $13,900</t>
+        </is>
+      </c>
+      <c r="AQ5" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-11: $13,900 ACTIVE; 2024-06-18: $11,950 RENTED; 2024-06-16: $11,950 IN_CONTRACT; 2024-05-24: $11,950 ACTIVE; 2024-05-21: $11,950 TEMPORARILY_OFF_MARKET; 2024-04-23: $11,950 ACTIVE; 2021-10-06: $10,950 RENTED; 2021-10-02: $10,950 TEMPORARILY_OFF_MARKET; 2021-09-26: $10,950 ACTIVE; 2021-09-22: $10,950 TEMPORARILY_OFF_MARKET; 2021-09-08: $10,950 ACTIVE</t>
+        </is>
+      </c>
+      <c r="AR5" s="8" t="n">
+        <v>9895</v>
+      </c>
+      <c r="AS5" s="6" t="inlineStr"/>
+      <c r="AT5" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW5" s="6" t="inlineStr"/>
+      <c r="AX5" s="6" t="inlineStr"/>
+      <c r="AY5" s="6" t="inlineStr">
+        <is>
+          <t>PARTNER</t>
+        </is>
+      </c>
+      <c r="AZ5" s="6" t="n">
+        <v>40.74414</v>
+      </c>
+      <c r="BA5" s="6" t="n">
+        <v>-74.00270999999999</v>
+      </c>
+      <c r="BB5" s="6" t="inlineStr"/>
+      <c r="BC5" s="9" t="inlineStr">
+        <is>
+          <t>Elevate your lifestyle in this stunning three-bedroom duplex residence with an expansive 1000 square foot, private, outdoor space. Where modern sophistication blends seamlessly with effortless comfort while oversized windows flood the home with natural light, creating a bright, open ambiance throughout. 
+The open-concept living and dining area features a sleek, contemporary kitchen that anchors the space. Outfitted with top-of-the-line appliances, custom cabinetry, and refined finishes that cater to both everyday living and culinary pursuits.
+The primary bedrooms and living room each feature a working fireplace, adding warmth and character to the home. The home is thoughtfully equipped with an in-unit washer/dryer, while abundant closet space, ensuring effortless storage.
+A spacious private rooftop terrace crowns the home, offering sweeping views and an exceptional setting for both relaxation and entertaining. Whether enjoying quiet mornings or hosting under the open sky, this extraordinary outdoor retreat provides a rare sense of openness and escape above the city.
+Pets case by case</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>4833587</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>https://streeteasy.com/rental/4833587</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>251 West 19th Street #1G</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>#1G</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>10011</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>16000</v>
+      </c>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>Condo</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr">
+        <is>
+          <t>Private Outdoor Space</t>
+        </is>
+      </c>
+      <c r="Z6" s="5" t="inlineStr">
+        <is>
+          <t>Doorman; Elevator; Fios Available</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="n">
+        <v>1910</v>
+      </c>
+      <c r="AG6" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH6" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="AI6" s="2" t="inlineStr">
+        <is>
+          <t>Compass</t>
+        </is>
+      </c>
+      <c r="AJ6" s="2" t="inlineStr">
+        <is>
+          <t>Compass</t>
+        </is>
+      </c>
+      <c r="AK6" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Broker</t>
+        </is>
+      </c>
+      <c r="AL6" s="2" t="inlineStr">
+        <is>
+          <t>90 5th Avenue, 3rd Floor, New York, NY, 10011-7624</t>
+        </is>
+      </c>
+      <c r="AM6" s="2" t="inlineStr">
+        <is>
+          <t>None listed</t>
+        </is>
+      </c>
+      <c r="AN6" s="4" t="n"/>
+      <c r="AO6" s="5" t="inlineStr"/>
+      <c r="AP6" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-18: $16,000</t>
+        </is>
+      </c>
+      <c r="AQ6" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-18: $16,000 ACTIVE</t>
+        </is>
+      </c>
+      <c r="AR6" s="4" t="n">
+        <v>8600</v>
+      </c>
+      <c r="AS6" s="2" t="inlineStr"/>
+      <c r="AT6" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" s="2" t="inlineStr"/>
+      <c r="AX6" s="2" t="inlineStr"/>
+      <c r="AY6" s="2" t="inlineStr">
+        <is>
+          <t>PARTNER</t>
+        </is>
+      </c>
+      <c r="AZ6" s="2" t="n">
+        <v>40.7426</v>
+      </c>
+      <c r="BA6" s="2" t="n">
+        <v>-73.9992</v>
+      </c>
+      <c r="BB6" s="2" t="inlineStr"/>
+      <c r="BC6" s="5" t="inlineStr">
+        <is>
+          <t>Your Chelsea Triplex Oasis Awaits: Live, Create, and Thrive
+Discover an exceptionally creative residential triplex loft in the heart of Chelsea's vibrant gallery district – a space as unique and inspiring as you are.Currently a thriving live/work (residential  zoning)art gallery, this stunning property offers endless possibilities to craft your dream lifestyle.
+Imagine:
+• Transforming this open canvas into a private Pilates, Yoga, or Personal Training studio. The privacy-rich layout, primarily on one level, provides the perfect environment for focused practice and client sessions.
+• Entertaining in the combined living/dining/kitchen area, the heart of this spectacular triplex loft.
+• Waking up in a serene top-level bedroom, complete with its own private outdoor space – your personal sanctuary to start or end the day.
+Nestled within a bespoke doorman condominium, you'll enjoy the security and convenience of a premier building in one of Manhattan's most sought-after neighborhoods. The irresistible appeal of Chelsea's industrial lofts, with their high ceilings and open floor plans, offers a sense of spaciousness and freedom rarely found elsewhere in the city.
+Beyond your doorstep, Central Chelsea offers a world-class experience:
+• Effortless access to transportation for easy navigation throughout the city.
+• A thriving art scene with world-renowned galleries at your fingertips.
+• An array of wonderful cafes and restaurants to satisfy every culinary craving.
+This is more than just a home; it's an opportunity to invest in your passion and cultivate your ideal lifestyle. Unlock the potential of this unique Chelsea triplex – a space where creativity meets luxury and convenience.
+Don't miss out on this rare find! Contact us today to schedule a private viewing and step into a world of possibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>5090360</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>https://streeteasy.com/rental/5090360</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>356 East 8th Street GARDEN-LEVEL</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>GARDEN-LEVEL</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>East Village</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>10009</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>6995</v>
+      </c>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v>750</v>
+      </c>
+      <c r="Q7" s="8" t="n">
+        <v>112</v>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>Rental unit</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="T7" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="U7" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="V7" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="W7" s="6" t="inlineStr">
+        <is>
+          <t>Garden; Roof Rights</t>
+        </is>
+      </c>
+      <c r="X7" s="6" t="inlineStr">
+        <is>
+          <t>Garden</t>
+        </is>
+      </c>
+      <c r="Y7" s="9" t="inlineStr">
+        <is>
+          <t>Central Ac; Hardwood Floors; Private Outdoor Space; View; Washer Dryer</t>
+        </is>
+      </c>
+      <c r="Z7" s="9" t="inlineStr">
+        <is>
+          <t>Doorman; Fios Available; Shared Outdoor Space</t>
+        </is>
+      </c>
+      <c r="AA7" s="6" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="AB7" s="6" t="inlineStr"/>
+      <c r="AC7" s="6" t="inlineStr">
+        <is>
+          <t>Roof Deck</t>
+        </is>
+      </c>
+      <c r="AD7" s="6" t="inlineStr"/>
+      <c r="AE7" s="6" t="inlineStr"/>
+      <c r="AF7" s="6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AG7" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH7" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI7" s="6" t="inlineStr">
+        <is>
+          <t>R New York</t>
+        </is>
+      </c>
+      <c r="AJ7" s="6" t="inlineStr">
+        <is>
+          <t>R New York</t>
+        </is>
+      </c>
+      <c r="AK7" s="6" t="inlineStr">
+        <is>
+          <t>Limited Liability Broker</t>
+        </is>
+      </c>
+      <c r="AL7" s="6" t="inlineStr">
+        <is>
+          <t>641 Lexington Avenue, 22nd Floor, New York, NY, 10022</t>
+        </is>
+      </c>
+      <c r="AM7" s="6" t="inlineStr">
+        <is>
+          <t>None listed</t>
+        </is>
+      </c>
+      <c r="AN7" s="8" t="n">
+        <v>6995</v>
+      </c>
+      <c r="AO7" s="9" t="inlineStr">
+        <is>
+          <t>Application fee: $20; Security deposit: $6,995</t>
+        </is>
+      </c>
+      <c r="AP7" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02: $6,995</t>
+        </is>
+      </c>
+      <c r="AQ7" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-02: $6,995 ACTIVE</t>
+        </is>
+      </c>
+      <c r="AR7" s="8" t="n">
+        <v>5495</v>
+      </c>
+      <c r="AS7" s="6" t="inlineStr"/>
+      <c r="AT7" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AU7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" s="6" t="inlineStr"/>
+      <c r="AX7" s="6" t="inlineStr"/>
+      <c r="AY7" s="6" t="inlineStr">
+        <is>
+          <t>PARTNER</t>
+        </is>
+      </c>
+      <c r="AZ7" s="6" t="n">
+        <v>40.72432</v>
+      </c>
+      <c r="BA7" s="6" t="n">
+        <v>-73.97812</v>
+      </c>
+      <c r="BB7" s="6" t="inlineStr"/>
+      <c r="BC7" s="9" t="inlineStr">
         <is>
           <t>Private Luxury Garden Residence with Expansive Patio
 Now leasing — a rare garden residence at 356 East 8th Street featuring a massive private patio and beautifully finished interiors in a newly built boutique luxury building. This is a unique opportunity to enjoy indoor-outdoor living in the heart of the East Village, with the scale and privacy of a personal outdoor retreat rarely found in Manhattan.
@@ -1065,198 +2087,198 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>5085327</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5085327</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>432 East 13th Street #6B</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>#6B</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>East Village</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>10009</t>
         </is>
       </c>
-      <c r="H3" s="8" t="n">
+      <c r="H8" s="4" t="n">
         <v>7995</v>
       </c>
-      <c r="I3" s="8" t="n"/>
-      <c r="J3" s="6" t="n"/>
-      <c r="K3" s="6" t="n"/>
-      <c r="L3" s="6" t="n">
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M3" s="6" t="n">
+      <c r="M8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="6" t="n">
+      <c r="N8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P3" s="6" t="inlineStr"/>
-      <c r="Q3" s="8" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>Rental unit</t>
         </is>
       </c>
-      <c r="S3" s="6" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T3" s="6" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="U3" s="6" t="n">
+      <c r="U8" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="V3" s="6" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="W3" s="6" t="inlineStr">
+      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>Private Roof Deck; Roof Rights</t>
         </is>
       </c>
-      <c r="X3" s="6" t="inlineStr">
+      <c r="X8" s="2" t="inlineStr">
         <is>
           <t>City; Skyline</t>
         </is>
       </c>
-      <c r="Y3" s="9" t="inlineStr">
+      <c r="Y8" s="5" t="inlineStr">
         <is>
           <t>Dishwasher; Hardwood Floors; Private Outdoor Space; View; Washer Dryer</t>
         </is>
       </c>
-      <c r="Z3" s="9" t="inlineStr">
+      <c r="Z8" s="5" t="inlineStr">
         <is>
           <t>Doorman; Fios Available; Laundry; Live In Super; Package Room; Shared Outdoor Space</t>
         </is>
       </c>
-      <c r="AA3" s="6" t="inlineStr">
+      <c r="AA8" s="2" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="AB3" s="6" t="inlineStr"/>
-      <c r="AC3" s="6" t="inlineStr">
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>Roof Deck</t>
         </is>
       </c>
-      <c r="AD3" s="6" t="inlineStr"/>
-      <c r="AE3" s="6" t="inlineStr"/>
-      <c r="AF3" s="6" t="n">
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="n">
         <v>1900</v>
       </c>
-      <c r="AG3" s="6" t="n">
+      <c r="AG8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AH3" s="6" t="n">
+      <c r="AH8" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="AI3" s="6" t="inlineStr">
+      <c r="AI8" s="2" t="inlineStr">
         <is>
           <t>DALLAL</t>
         </is>
       </c>
-      <c r="AJ3" s="6" t="inlineStr">
+      <c r="AJ8" s="2" t="inlineStr">
         <is>
           <t>Dallal Group Llc</t>
         </is>
       </c>
-      <c r="AK3" s="6" t="inlineStr">
+      <c r="AK8" s="2" t="inlineStr">
         <is>
           <t>Real Estate Principal Office</t>
         </is>
       </c>
-      <c r="AL3" s="6" t="inlineStr">
+      <c r="AL8" s="2" t="inlineStr">
         <is>
           <t>260 Madison Avenue, 8th Floor, New York, NY, 10016</t>
         </is>
       </c>
-      <c r="AM3" s="6" t="inlineStr">
+      <c r="AM8" s="2" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN3" s="8" t="n">
+      <c r="AN8" s="4" t="n">
         <v>7995</v>
       </c>
-      <c r="AO3" s="9" t="inlineStr">
+      <c r="AO8" s="5" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $7,995</t>
         </is>
       </c>
-      <c r="AP3" s="6" t="inlineStr">
+      <c r="AP8" s="2" t="inlineStr">
         <is>
           <t>2026-06-26: $7,995</t>
         </is>
       </c>
-      <c r="AQ3" s="9" t="inlineStr">
+      <c r="AQ8" s="5" t="inlineStr">
         <is>
           <t>2026-06-26: $7,995 ACTIVE</t>
         </is>
       </c>
-      <c r="AR3" s="8" t="n">
+      <c r="AR8" s="4" t="n">
         <v>7722</v>
       </c>
-      <c r="AS3" s="6" t="inlineStr"/>
-      <c r="AT3" s="6" t="n">
+      <c r="AS8" s="2" t="inlineStr"/>
+      <c r="AT8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AU3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" s="6" t="inlineStr"/>
-      <c r="AX3" s="6" t="inlineStr"/>
-      <c r="AY3" s="6" t="inlineStr">
+      <c r="AU8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="2" t="inlineStr"/>
+      <c r="AX8" s="2" t="inlineStr"/>
+      <c r="AY8" s="2" t="inlineStr">
         <is>
           <t>PARTNER</t>
         </is>
       </c>
-      <c r="AZ3" s="6" t="n">
+      <c r="AZ8" s="2" t="n">
         <v>40.7299</v>
       </c>
-      <c r="BA3" s="6" t="n">
+      <c r="BA8" s="2" t="n">
         <v>-73.9819</v>
       </c>
-      <c r="BB3" s="6" t="inlineStr"/>
-      <c r="BC3" s="9" t="inlineStr">
+      <c r="BB8" s="2" t="inlineStr"/>
+      <c r="BC8" s="5" t="inlineStr">
         <is>
           <t>Beautifully Renovated 3 Bedroom in Prime East Village.
 This stunning home is available for an immediate lease start, located in a well-maintained building and offers a thoughtfully updated interior with modern finishes throughout.
@@ -1272,194 +2294,194 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>5085344</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5085344</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>432 East 13th Street #1C</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>#1C</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>East Village</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>10009</t>
         </is>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H9" s="8" t="n">
         <v>7995</v>
       </c>
-      <c r="I4" s="4" t="n"/>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
-      <c r="L4" s="2" t="n">
+      <c r="I9" s="8" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="M9" s="6" t="n">
         <v>1.5</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="O9" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="P9" s="6" t="inlineStr"/>
+      <c r="Q9" s="8" t="inlineStr"/>
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>Rental unit</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="S9" s="6" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="T9" s="6" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="U4" s="2" t="n">
+      <c r="U9" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V9" s="6" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="W9" s="6" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="X4" s="2" t="inlineStr">
+      <c r="X9" s="6" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="Y4" s="5" t="inlineStr">
+      <c r="Y9" s="9" t="inlineStr">
         <is>
           <t>Dishwasher; Hardwood Floors; Private Outdoor Space; View; Washer Dryer</t>
         </is>
       </c>
-      <c r="Z4" s="5" t="inlineStr">
+      <c r="Z9" s="9" t="inlineStr">
         <is>
           <t>Doorman; Fios Available; Laundry; Live In Super; Package Room</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
+      <c r="AA9" s="6" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr"/>
-      <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="n">
+      <c r="AB9" s="6" t="inlineStr"/>
+      <c r="AC9" s="6" t="inlineStr"/>
+      <c r="AD9" s="6" t="inlineStr"/>
+      <c r="AE9" s="6" t="inlineStr"/>
+      <c r="AF9" s="6" t="n">
         <v>1900</v>
       </c>
-      <c r="AG4" s="2" t="n">
+      <c r="AG9" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="AH4" s="2" t="n">
+      <c r="AH9" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="AI4" s="2" t="inlineStr">
+      <c r="AI9" s="6" t="inlineStr">
         <is>
           <t>DALLAL</t>
         </is>
       </c>
-      <c r="AJ4" s="2" t="inlineStr">
+      <c r="AJ9" s="6" t="inlineStr">
         <is>
           <t>Dallal Group Llc</t>
         </is>
       </c>
-      <c r="AK4" s="2" t="inlineStr">
+      <c r="AK9" s="6" t="inlineStr">
         <is>
           <t>Real Estate Principal Office</t>
         </is>
       </c>
-      <c r="AL4" s="2" t="inlineStr">
+      <c r="AL9" s="6" t="inlineStr">
         <is>
           <t>260 Madison Avenue, 8th Floor, New York, NY, 10016</t>
         </is>
       </c>
-      <c r="AM4" s="2" t="inlineStr">
+      <c r="AM9" s="6" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN4" s="4" t="n">
+      <c r="AN9" s="8" t="n">
         <v>7995</v>
       </c>
-      <c r="AO4" s="5" t="inlineStr">
+      <c r="AO9" s="9" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $7,995</t>
         </is>
       </c>
-      <c r="AP4" s="2" t="inlineStr">
+      <c r="AP9" s="6" t="inlineStr">
         <is>
           <t>2026-06-26: $7,995</t>
         </is>
       </c>
-      <c r="AQ4" s="5" t="inlineStr">
+      <c r="AQ9" s="9" t="inlineStr">
         <is>
           <t>2026-06-26: $7,995 ACTIVE</t>
         </is>
       </c>
-      <c r="AR4" s="4" t="n">
+      <c r="AR9" s="8" t="n">
         <v>7722</v>
       </c>
-      <c r="AS4" s="2" t="inlineStr"/>
-      <c r="AT4" s="2" t="n">
+      <c r="AS9" s="6" t="inlineStr"/>
+      <c r="AT9" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="AU4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" s="2" t="inlineStr"/>
-      <c r="AX4" s="2" t="inlineStr"/>
-      <c r="AY4" s="2" t="inlineStr">
+      <c r="AU9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="6" t="inlineStr"/>
+      <c r="AX9" s="6" t="inlineStr"/>
+      <c r="AY9" s="6" t="inlineStr">
         <is>
           <t>PARTNER</t>
         </is>
       </c>
-      <c r="AZ4" s="2" t="n">
+      <c r="AZ9" s="6" t="n">
         <v>40.7299</v>
       </c>
-      <c r="BA4" s="2" t="n">
+      <c r="BA9" s="6" t="n">
         <v>-73.9819</v>
       </c>
-      <c r="BB4" s="2" t="inlineStr"/>
-      <c r="BC4" s="5" t="inlineStr">
+      <c r="BB9" s="6" t="inlineStr"/>
+      <c r="BC9" s="9" t="inlineStr">
         <is>
           <t>Beautifully Renovated 3 Bedroom in Prime East Village.
 This stunning home is available for an immediate lease start, located in a well-maintained building and offers a thoughtfully updated interior with modern finishes throughout.
@@ -1476,198 +2498,198 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>5093671</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5093671</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>432 East 13th Street #A6</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>#A6</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>East Village</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>10009</t>
         </is>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="H10" s="4" t="n">
         <v>7995</v>
       </c>
-      <c r="I5" s="8" t="n"/>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="6" t="n">
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="M10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="6" t="n">
+      <c r="N10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P5" s="6" t="inlineStr"/>
-      <c r="Q5" s="8" t="inlineStr"/>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="4" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>Rental unit</t>
         </is>
       </c>
-      <c r="S5" s="6" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T5" s="6" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="U5" s="6" t="n">
+      <c r="U10" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="V5" s="6" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="W5" s="6" t="inlineStr">
+      <c r="W10" s="2" t="inlineStr">
         <is>
           <t>Private Roof Deck; Roof Rights</t>
         </is>
       </c>
-      <c r="X5" s="6" t="inlineStr">
+      <c r="X10" s="2" t="inlineStr">
         <is>
           <t>City; Skyline</t>
         </is>
       </c>
-      <c r="Y5" s="9" t="inlineStr">
+      <c r="Y10" s="5" t="inlineStr">
         <is>
           <t>Dishwasher; Hardwood Floors; Private Outdoor Space; View; Washer Dryer</t>
         </is>
       </c>
-      <c r="Z5" s="9" t="inlineStr">
+      <c r="Z10" s="5" t="inlineStr">
         <is>
           <t>Doorman; Fios Available; Laundry; Live In Super; Package Room; Shared Outdoor Space</t>
         </is>
       </c>
-      <c r="AA5" s="6" t="inlineStr">
+      <c r="AA10" s="2" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="AB5" s="6" t="inlineStr"/>
-      <c r="AC5" s="6" t="inlineStr">
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
         <is>
           <t>Roof Deck</t>
         </is>
       </c>
-      <c r="AD5" s="6" t="inlineStr"/>
-      <c r="AE5" s="6" t="inlineStr"/>
-      <c r="AF5" s="6" t="n">
+      <c r="AD10" s="2" t="inlineStr"/>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="n">
         <v>1900</v>
       </c>
-      <c r="AG5" s="6" t="n">
+      <c r="AG10" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AH5" s="6" t="n">
+      <c r="AH10" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="AI5" s="6" t="inlineStr">
+      <c r="AI10" s="2" t="inlineStr">
         <is>
           <t>DALLAL</t>
         </is>
       </c>
-      <c r="AJ5" s="6" t="inlineStr">
+      <c r="AJ10" s="2" t="inlineStr">
         <is>
           <t>Dallal Group Llc</t>
         </is>
       </c>
-      <c r="AK5" s="6" t="inlineStr">
+      <c r="AK10" s="2" t="inlineStr">
         <is>
           <t>Real Estate Principal Office</t>
         </is>
       </c>
-      <c r="AL5" s="6" t="inlineStr">
+      <c r="AL10" s="2" t="inlineStr">
         <is>
           <t>260 Madison Avenue, 8th Floor, New York, NY, 10016</t>
         </is>
       </c>
-      <c r="AM5" s="6" t="inlineStr">
+      <c r="AM10" s="2" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN5" s="8" t="n">
+      <c r="AN10" s="4" t="n">
         <v>7995</v>
       </c>
-      <c r="AO5" s="9" t="inlineStr">
+      <c r="AO10" s="5" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $7,995</t>
         </is>
       </c>
-      <c r="AP5" s="6" t="inlineStr">
+      <c r="AP10" s="2" t="inlineStr">
         <is>
           <t>2026-07-06: $7,995</t>
         </is>
       </c>
-      <c r="AQ5" s="9" t="inlineStr">
+      <c r="AQ10" s="5" t="inlineStr">
         <is>
           <t>2026-07-06: $7,995 ACTIVE</t>
         </is>
       </c>
-      <c r="AR5" s="8" t="n">
+      <c r="AR10" s="4" t="n">
         <v>7722</v>
       </c>
-      <c r="AS5" s="6" t="inlineStr"/>
-      <c r="AT5" s="6" t="n">
+      <c r="AS10" s="2" t="inlineStr"/>
+      <c r="AT10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AU5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" s="6" t="inlineStr"/>
-      <c r="AX5" s="6" t="inlineStr"/>
-      <c r="AY5" s="6" t="inlineStr">
+      <c r="AU10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" s="2" t="inlineStr"/>
+      <c r="AX10" s="2" t="inlineStr"/>
+      <c r="AY10" s="2" t="inlineStr">
         <is>
           <t>PARTNER</t>
         </is>
       </c>
-      <c r="AZ5" s="6" t="n">
+      <c r="AZ10" s="2" t="n">
         <v>40.7299</v>
       </c>
-      <c r="BA5" s="6" t="n">
+      <c r="BA10" s="2" t="n">
         <v>-73.9819</v>
       </c>
-      <c r="BB5" s="6" t="inlineStr"/>
-      <c r="BC5" s="9" t="inlineStr">
+      <c r="BB10" s="2" t="inlineStr"/>
+      <c r="BC10" s="5" t="inlineStr">
         <is>
           <t>This stunning 3 bedroom is located in a well-maintained building in prime East Village, and offers a thoughtfully updated interior with modern finishes throughout.
 PH Duplex, Featuring:
@@ -1683,198 +2705,198 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>5087527</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5087527</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>432 East 13th Street #5B</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>#5B</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>East Village</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>10009</t>
         </is>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H11" s="8" t="n">
         <v>8995</v>
       </c>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="n">
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="M11" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="N6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="2" t="n">
+      <c r="N11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="P11" s="6" t="inlineStr"/>
+      <c r="Q11" s="8" t="inlineStr"/>
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>Rental unit</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr">
+      <c r="S11" s="6" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="T11" s="6" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="U6" s="2" t="n">
+      <c r="U11" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V11" s="6" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="W6" s="2" t="inlineStr">
+      <c r="W11" s="6" t="inlineStr">
         <is>
           <t>Private Roof Deck; Roof Rights</t>
         </is>
       </c>
-      <c r="X6" s="2" t="inlineStr">
+      <c r="X11" s="6" t="inlineStr">
         <is>
           <t>City; Skyline</t>
         </is>
       </c>
-      <c r="Y6" s="5" t="inlineStr">
+      <c r="Y11" s="9" t="inlineStr">
         <is>
           <t>Dishwasher; Hardwood Floors; Private Outdoor Space; View; Washer Dryer</t>
         </is>
       </c>
-      <c r="Z6" s="5" t="inlineStr">
+      <c r="Z11" s="9" t="inlineStr">
         <is>
           <t>Doorman; Fios Available; Laundry; Live In Super; Package Room; Shared Outdoor Space</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
+      <c r="AA11" s="6" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr"/>
-      <c r="AC6" s="2" t="inlineStr">
+      <c r="AB11" s="6" t="inlineStr"/>
+      <c r="AC11" s="6" t="inlineStr">
         <is>
           <t>Roof Deck</t>
         </is>
       </c>
-      <c r="AD6" s="2" t="inlineStr"/>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="n">
+      <c r="AD11" s="6" t="inlineStr"/>
+      <c r="AE11" s="6" t="inlineStr"/>
+      <c r="AF11" s="6" t="n">
         <v>1900</v>
       </c>
-      <c r="AG6" s="2" t="n">
+      <c r="AG11" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="AH6" s="2" t="n">
+      <c r="AH11" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="AI6" s="2" t="inlineStr">
+      <c r="AI11" s="6" t="inlineStr">
         <is>
           <t>DALLAL</t>
         </is>
       </c>
-      <c r="AJ6" s="2" t="inlineStr">
+      <c r="AJ11" s="6" t="inlineStr">
         <is>
           <t>Dallal Group Llc</t>
         </is>
       </c>
-      <c r="AK6" s="2" t="inlineStr">
+      <c r="AK11" s="6" t="inlineStr">
         <is>
           <t>Real Estate Principal Office</t>
         </is>
       </c>
-      <c r="AL6" s="2" t="inlineStr">
+      <c r="AL11" s="6" t="inlineStr">
         <is>
           <t>260 Madison Avenue, 8th Floor, New York, NY, 10016</t>
         </is>
       </c>
-      <c r="AM6" s="2" t="inlineStr">
+      <c r="AM11" s="6" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN6" s="4" t="n">
+      <c r="AN11" s="8" t="n">
         <v>8995</v>
       </c>
-      <c r="AO6" s="5" t="inlineStr">
+      <c r="AO11" s="9" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $8,995</t>
         </is>
       </c>
-      <c r="AP6" s="2" t="inlineStr">
+      <c r="AP11" s="6" t="inlineStr">
         <is>
           <t>2026-06-30: $8,995</t>
         </is>
       </c>
-      <c r="AQ6" s="5" t="inlineStr">
+      <c r="AQ11" s="9" t="inlineStr">
         <is>
           <t>2026-06-30: $8,995 ACTIVE</t>
         </is>
       </c>
-      <c r="AR6" s="4" t="n">
+      <c r="AR11" s="8" t="n">
         <v>7722</v>
       </c>
-      <c r="AS6" s="2" t="inlineStr"/>
-      <c r="AT6" s="2" t="n">
+      <c r="AS11" s="6" t="inlineStr"/>
+      <c r="AT11" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="AU6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" s="2" t="inlineStr"/>
-      <c r="AX6" s="2" t="inlineStr"/>
-      <c r="AY6" s="2" t="inlineStr">
+      <c r="AU11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" s="6" t="inlineStr"/>
+      <c r="AX11" s="6" t="inlineStr"/>
+      <c r="AY11" s="6" t="inlineStr">
         <is>
           <t>PARTNER</t>
         </is>
       </c>
-      <c r="AZ6" s="2" t="n">
+      <c r="AZ11" s="6" t="n">
         <v>40.7299</v>
       </c>
-      <c r="BA6" s="2" t="n">
+      <c r="BA11" s="6" t="n">
         <v>-73.9819</v>
       </c>
-      <c r="BB6" s="2" t="inlineStr"/>
-      <c r="BC6" s="5" t="inlineStr">
+      <c r="BB11" s="6" t="inlineStr"/>
+      <c r="BC11" s="9" t="inlineStr">
         <is>
           <t>This stunning 3 bedroom is located in a well-maintained building in prime East Village, and offers a thoughtfully updated interior with modern finishes throughout.
 PH Duplex, Featuring:
@@ -1890,178 +2912,178 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>5078224</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5078224</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>50 Avenue A #4A</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>#4A</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>East Village</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>10009</t>
         </is>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H12" s="4" t="n">
         <v>9500</v>
       </c>
-      <c r="I7" s="8" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n">
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M7" s="6" t="n">
+      <c r="M12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="N7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="6" t="n">
+      <c r="N12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="P12" s="2" t="n">
         <v>1200</v>
       </c>
-      <c r="Q7" s="8" t="n">
+      <c r="Q12" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="S7" s="6" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>RENTED</t>
         </is>
       </c>
-      <c r="T7" s="6" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="U7" s="6" t="n">
+      <c r="U12" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="V7" s="6" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="W7" s="6" t="inlineStr">
+      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>Balcony; Terrace</t>
         </is>
       </c>
-      <c r="X7" s="6" t="inlineStr"/>
-      <c r="Y7" s="9" t="inlineStr">
+      <c r="X12" s="2" t="inlineStr"/>
+      <c r="Y12" s="5" t="inlineStr">
         <is>
           <t>Dishwasher; Fireplace; Furnished; Hardwood Floors; Private Outdoor Space; Washer Dryer</t>
         </is>
       </c>
-      <c r="Z7" s="9" t="inlineStr">
+      <c r="Z12" s="5" t="inlineStr">
         <is>
           <t>Elevator; Fios Available</t>
         </is>
       </c>
-      <c r="AA7" s="6" t="inlineStr"/>
-      <c r="AB7" s="6" t="inlineStr"/>
-      <c r="AC7" s="6" t="inlineStr"/>
-      <c r="AD7" s="6" t="inlineStr"/>
-      <c r="AE7" s="6" t="inlineStr"/>
-      <c r="AF7" s="6" t="n">
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="n">
         <v>1920</v>
       </c>
-      <c r="AG7" s="6" t="n">
+      <c r="AG12" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AH7" s="6" t="n">
+      <c r="AH12" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="AI7" s="6" t="inlineStr">
+      <c r="AI12" s="2" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AJ7" s="6" t="inlineStr"/>
-      <c r="AK7" s="6" t="inlineStr"/>
-      <c r="AL7" s="6" t="inlineStr"/>
-      <c r="AM7" s="6" t="inlineStr">
+      <c r="AJ12" s="2" t="inlineStr"/>
+      <c r="AK12" s="2" t="inlineStr"/>
+      <c r="AL12" s="2" t="inlineStr"/>
+      <c r="AM12" s="2" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN7" s="8" t="n">
+      <c r="AN12" s="4" t="n">
         <v>9500</v>
       </c>
-      <c r="AO7" s="9" t="inlineStr">
+      <c r="AO12" s="5" t="inlineStr">
         <is>
           <t>Application fee: $300; Background check: $50; Security deposit: $9,500; Early termination: $9,500</t>
         </is>
       </c>
-      <c r="AP7" s="6" t="inlineStr">
+      <c r="AP12" s="2" t="inlineStr">
         <is>
           <t>2026-06-19: $9,500</t>
         </is>
       </c>
-      <c r="AQ7" s="9" t="inlineStr">
+      <c r="AQ12" s="5" t="inlineStr">
         <is>
           <t>2026-07-12: $9,500 RENTED; 2026-06-29: $9,500 ACTIVE; 2024-09-20: $8,250 RENTED; 2024-08-23: $8,250 IN_CONTRACT; 2024-08-19: $8,250 ACTIVE</t>
         </is>
       </c>
-      <c r="AR7" s="8" t="n">
+      <c r="AR12" s="4" t="n">
         <v>5495</v>
       </c>
-      <c r="AS7" s="6" t="inlineStr"/>
-      <c r="AT7" s="6" t="n">
+      <c r="AS12" s="2" t="inlineStr"/>
+      <c r="AT12" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="AU7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" s="6" t="inlineStr"/>
-      <c r="AX7" s="6" t="inlineStr"/>
-      <c r="AY7" s="6" t="inlineStr">
+      <c r="AU12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" s="2" t="inlineStr"/>
+      <c r="AX12" s="2" t="inlineStr"/>
+      <c r="AY12" s="2" t="inlineStr">
         <is>
           <t>OWNER</t>
         </is>
       </c>
-      <c r="AZ7" s="6" t="n">
+      <c r="AZ12" s="2" t="n">
         <v>40.72383</v>
       </c>
-      <c r="BA7" s="6" t="n">
+      <c r="BA12" s="2" t="n">
         <v>-73.98478</v>
       </c>
-      <c r="BB7" s="6" t="inlineStr"/>
-      <c r="BC7" s="9" t="inlineStr">
+      <c r="BB12" s="2" t="inlineStr"/>
+      <c r="BC12" s="5" t="inlineStr">
         <is>
           <t>Renovated duplex home, offered furnished for August 6th lease start. A true 2bed/2bath with a wood-burning fireplace and a bonus sun room for guests, meditation, and morning coffee. The home also has two private patios with views of the neighborhood.
 The apartment features an incredible custom-built wooden staircase leading to the upper floor, also built out with matching hardwood, curved ceiling, two skylights, glass railing, floor-to-ceiling windows, and an upper patio. The living and dining rooms make for a sprawling common area filled with sunlight and a fireplace area. There is a second patio off of the living space that is internal to the block and very quiet, with beautiful views of the church next door.
@@ -2081,212 +3103,212 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>5088998</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5088998</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>644 East 14th Street #2002</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>#2002</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>East Village</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>10009</t>
         </is>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H13" s="8" t="n">
         <v>10200</v>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I13" s="8" t="n">
         <v>9415</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="J13" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="K13" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L13" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="M8" s="2" t="n">
+      <c r="M13" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="N8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="2" t="n">
+      <c r="N13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="P13" s="6" t="inlineStr"/>
+      <c r="Q13" s="8" t="inlineStr"/>
+      <c r="R13" s="6" t="inlineStr">
         <is>
           <t>Rental unit</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr">
+      <c r="S13" s="6" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T8" s="2" t="inlineStr">
+      <c r="T13" s="6" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="U8" s="2" t="n">
+      <c r="U13" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V13" s="6" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="W8" s="2" t="inlineStr">
+      <c r="W13" s="6" t="inlineStr">
         <is>
           <t>Terrace</t>
         </is>
       </c>
-      <c r="X8" s="2" t="inlineStr">
+      <c r="X13" s="6" t="inlineStr">
         <is>
           <t>City; Skyline; Water</t>
         </is>
       </c>
-      <c r="Y8" s="5" t="inlineStr">
+      <c r="Y13" s="9" t="inlineStr">
         <is>
           <t>Central Ac; Private Outdoor Space; View; Washer Dryer</t>
         </is>
       </c>
-      <c r="Z8" s="5" t="inlineStr">
+      <c r="Z13" s="9" t="inlineStr">
         <is>
           <t>Bike Room; Doorman; Elevator; Fios Available; Gym; Laundry; Live In Super; Media Room; Package Room; Shared Outdoor Space; Storage Space; Wheelchair Access</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
+      <c r="AA13" s="6" t="inlineStr">
         <is>
           <t>Part Time</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr"/>
-      <c r="AC8" s="2" t="inlineStr">
+      <c r="AB13" s="6" t="inlineStr"/>
+      <c r="AC13" s="6" t="inlineStr">
         <is>
           <t>Patio; Roof Deck</t>
         </is>
       </c>
-      <c r="AD8" s="2" t="inlineStr">
+      <c r="AD13" s="6" t="inlineStr">
         <is>
           <t>Locker Cage</t>
         </is>
       </c>
-      <c r="AE8" s="2" t="inlineStr">
+      <c r="AE13" s="6" t="inlineStr">
         <is>
           <t>The East</t>
         </is>
       </c>
-      <c r="AF8" s="2" t="n">
+      <c r="AF13" s="6" t="n">
         <v>2026</v>
       </c>
-      <c r="AG8" s="2" t="n">
+      <c r="AG13" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="AH8" s="2" t="n">
+      <c r="AH13" s="6" t="n">
         <v>196</v>
       </c>
-      <c r="AI8" s="2" t="inlineStr">
+      <c r="AI13" s="6" t="inlineStr">
         <is>
           <t>Corcoran</t>
         </is>
       </c>
-      <c r="AJ8" s="2" t="inlineStr">
+      <c r="AJ13" s="6" t="inlineStr">
         <is>
           <t>Corcoran Group</t>
         </is>
       </c>
-      <c r="AK8" s="2" t="inlineStr">
+      <c r="AK13" s="6" t="inlineStr">
         <is>
           <t>Limited Liability Broker</t>
         </is>
       </c>
-      <c r="AL8" s="2" t="inlineStr">
+      <c r="AL13" s="6" t="inlineStr">
         <is>
           <t>590 Madison Avenue, New York, NY, 10022</t>
         </is>
       </c>
-      <c r="AM8" s="2" t="inlineStr">
+      <c r="AM13" s="6" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN8" s="4" t="n">
+      <c r="AN13" s="8" t="n">
         <v>10600</v>
       </c>
-      <c r="AO8" s="5" t="inlineStr">
+      <c r="AO13" s="9" t="inlineStr">
         <is>
           <t>Application fee: $20; Pet deposit: $250; Security deposit: $10,600; Bike storage: $15; Community amenity: $50; Storage: $50</t>
         </is>
       </c>
-      <c r="AP8" s="2" t="inlineStr">
+      <c r="AP13" s="6" t="inlineStr">
         <is>
           <t>2026-07-02: $10,200</t>
         </is>
       </c>
-      <c r="AQ8" s="5" t="inlineStr">
+      <c r="AQ13" s="9" t="inlineStr">
         <is>
           <t>2026-07-02: $10,200 ACTIVE</t>
         </is>
       </c>
-      <c r="AR8" s="4" t="n">
+      <c r="AR13" s="8" t="n">
         <v>6399</v>
       </c>
-      <c r="AS8" s="2" t="inlineStr"/>
-      <c r="AT8" s="2" t="n">
+      <c r="AS13" s="6" t="inlineStr"/>
+      <c r="AT13" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="AU8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" s="2" t="n">
+      <c r="AU13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="AW8" s="2" t="inlineStr"/>
-      <c r="AX8" s="2" t="inlineStr"/>
-      <c r="AY8" s="2" t="inlineStr">
+      <c r="AW13" s="6" t="inlineStr"/>
+      <c r="AX13" s="6" t="inlineStr"/>
+      <c r="AY13" s="6" t="inlineStr">
         <is>
           <t>PARTNER</t>
         </is>
       </c>
-      <c r="AZ8" s="2" t="n">
+      <c r="AZ13" s="6" t="n">
         <v>40.7283</v>
       </c>
-      <c r="BA8" s="2" t="n">
+      <c r="BA13" s="6" t="n">
         <v>-73.97613</v>
       </c>
-      <c r="BB8" s="2" t="inlineStr"/>
-      <c r="BC8" s="5" t="inlineStr">
+      <c r="BB13" s="6" t="inlineStr"/>
+      <c r="BC13" s="9" t="inlineStr">
         <is>
           <t>Welcome to Residence 2002 at The East.  
 New, clean, and modern, this expansive two-bedroom, two-bathroom home offers a functional layout that maximizes space, light, and outdoor living. Oversized windows in the living room and both bedrooms fill the home with natural light and provide north and east-facing views of the East River, Manhattan, and Brooklyn skyline, creating a stunning backdrop for everyday living. A 376-square-foot private terrace spans the length of the living and dining areas, offering an exceptional setting for dining, entertaining, or relaxing outdoors. 
@@ -2308,194 +3330,194 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>5068611</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5068611</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>194 East 2nd Street #6D</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>#6D</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>East Village</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>10009</t>
         </is>
       </c>
-      <c r="H9" s="8" t="n">
+      <c r="H14" s="4" t="n">
         <v>12500</v>
       </c>
-      <c r="I9" s="8" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n">
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M9" s="6" t="n">
+      <c r="M14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="N9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="6" t="n">
+      <c r="N14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="P9" s="6" t="inlineStr"/>
-      <c r="Q9" s="8" t="inlineStr"/>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="4" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>Rental unit</t>
         </is>
       </c>
-      <c r="S9" s="6" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T9" s="6" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="U9" s="6" t="n">
+      <c r="U14" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="V9" s="6" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="W9" s="6" t="inlineStr">
+      <c r="W14" s="2" t="inlineStr">
         <is>
           <t>Balcony; Private Roof Deck; Terrace</t>
         </is>
       </c>
-      <c r="X9" s="6" t="inlineStr">
+      <c r="X14" s="2" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="Y9" s="9" t="inlineStr">
+      <c r="Y14" s="5" t="inlineStr">
         <is>
           <t>Central Ac; Dishwasher; Hardwood Floors; Private Outdoor Space; View</t>
         </is>
       </c>
-      <c r="Z9" s="9" t="inlineStr">
+      <c r="Z14" s="5" t="inlineStr">
         <is>
           <t>Bike Room; Doorman; Elevator; Fios Available; Laundry; Live In Super; Package Room; Shared Outdoor Space</t>
         </is>
       </c>
-      <c r="AA9" s="6" t="inlineStr"/>
-      <c r="AB9" s="6" t="inlineStr"/>
-      <c r="AC9" s="6" t="inlineStr">
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
         <is>
           <t>Courtyard; Patio</t>
         </is>
       </c>
-      <c r="AD9" s="6" t="inlineStr"/>
-      <c r="AE9" s="6" t="inlineStr"/>
-      <c r="AF9" s="6" t="n">
+      <c r="AD14" s="2" t="inlineStr"/>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="n">
         <v>1997</v>
       </c>
-      <c r="AG9" s="6" t="n">
+      <c r="AG14" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AH9" s="6" t="n">
+      <c r="AH14" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="AI9" s="6" t="inlineStr">
+      <c r="AI14" s="2" t="inlineStr">
         <is>
           <t>Pure Leasing LLC</t>
         </is>
       </c>
-      <c r="AJ9" s="6" t="inlineStr">
+      <c r="AJ14" s="2" t="inlineStr">
         <is>
           <t>Pure Leasing Llc</t>
         </is>
       </c>
-      <c r="AK9" s="6" t="inlineStr">
+      <c r="AK14" s="2" t="inlineStr">
         <is>
           <t>Real Estate Principal Office</t>
         </is>
       </c>
-      <c r="AL9" s="6" t="inlineStr">
+      <c r="AL14" s="2" t="inlineStr">
         <is>
           <t>6 East 39th Street, 9th Fl, New York, NY, 10016</t>
         </is>
       </c>
-      <c r="AM9" s="6" t="inlineStr">
+      <c r="AM14" s="2" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN9" s="8" t="n">
+      <c r="AN14" s="4" t="n">
         <v>12500</v>
       </c>
-      <c r="AO9" s="9" t="inlineStr">
+      <c r="AO14" s="5" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $12,500</t>
         </is>
       </c>
-      <c r="AP9" s="6" t="inlineStr">
+      <c r="AP14" s="2" t="inlineStr">
         <is>
           <t>2026-06-10: $12,500</t>
         </is>
       </c>
-      <c r="AQ9" s="9" t="inlineStr">
+      <c r="AQ14" s="5" t="inlineStr">
         <is>
           <t>2026-06-10: $12,500 ACTIVE; 2016-04-02: $7,500 NO_LONGER_AVAILABLE; 2015-12-01: $7,500 ACTIVE</t>
         </is>
       </c>
-      <c r="AR9" s="8" t="n">
+      <c r="AR14" s="4" t="n">
         <v>7722</v>
       </c>
-      <c r="AS9" s="6" t="inlineStr"/>
-      <c r="AT9" s="6" t="n">
+      <c r="AS14" s="2" t="inlineStr"/>
+      <c r="AT14" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="AU9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" s="6" t="n">
+      <c r="AU14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AW9" s="6" t="inlineStr"/>
-      <c r="AX9" s="6" t="inlineStr"/>
-      <c r="AY9" s="6" t="inlineStr">
+      <c r="AW14" s="2" t="inlineStr"/>
+      <c r="AX14" s="2" t="inlineStr"/>
+      <c r="AY14" s="2" t="inlineStr">
         <is>
           <t>PARTNER</t>
         </is>
       </c>
-      <c r="AZ9" s="6" t="n">
+      <c r="AZ14" s="2" t="n">
         <v>40.7223</v>
       </c>
-      <c r="BA9" s="6" t="n">
+      <c r="BA14" s="2" t="n">
         <v>-73.9837</v>
       </c>
-      <c r="BB9" s="6" t="inlineStr"/>
-      <c r="BC9" s="9" t="inlineStr">
+      <c r="BB14" s="2" t="inlineStr"/>
+      <c r="BC14" s="5" t="inlineStr">
         <is>
           <t>⭐PENTHOUSE | TOP FLOOR | PRIVATE TERRACE | BRIGHT AND SPACIOUS | FLEX 4⭐
 194 East 2nd Street is a full-service elevator building featuring a 24-hour doorman, beautifully redesigned hallways and common areas, a high-end fitness center with an infrared sauna and yoga/pilates room, and a tenant lounge with a billiards table.
@@ -2509,408 +3531,408 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>5087925</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5087925</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>21 Avenue B #401</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>#401</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>East Village</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>10009</t>
         </is>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H15" s="8" t="n">
         <v>13400</v>
       </c>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="n">
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="M10" s="2" t="n">
+      <c r="M15" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="N10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="2" t="n">
+      <c r="N15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="P15" s="6" t="inlineStr"/>
+      <c r="Q15" s="8" t="inlineStr"/>
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>Rental unit</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr">
+      <c r="S15" s="6" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T10" s="2" t="inlineStr">
+      <c r="T15" s="6" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="U10" s="2" t="n">
+      <c r="U15" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V15" s="6" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="W10" s="2" t="inlineStr">
+      <c r="W15" s="6" t="inlineStr">
         <is>
           <t>Roof Rights</t>
         </is>
       </c>
-      <c r="X10" s="2" t="inlineStr">
+      <c r="X15" s="6" t="inlineStr">
         <is>
           <t>City; Skyline</t>
         </is>
       </c>
-      <c r="Y10" s="5" t="inlineStr">
+      <c r="Y15" s="9" t="inlineStr">
         <is>
           <t>Central Ac; Dishwasher; Hardwood Floors; Private Outdoor Space; View; Washer Dryer</t>
         </is>
       </c>
-      <c r="Z10" s="5" t="inlineStr">
+      <c r="Z15" s="9" t="inlineStr">
         <is>
           <t>Bike Room; Doorman; Fios Available; Shared Outdoor Space; Storage Space</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
+      <c r="AA15" s="6" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr"/>
-      <c r="AC10" s="2" t="inlineStr">
+      <c r="AB15" s="6" t="inlineStr"/>
+      <c r="AC15" s="6" t="inlineStr">
         <is>
           <t>Roof Deck</t>
         </is>
       </c>
-      <c r="AD10" s="2" t="inlineStr">
+      <c r="AD15" s="6" t="inlineStr">
         <is>
           <t>Locker Cage</t>
         </is>
       </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="n">
+      <c r="AE15" s="6" t="inlineStr"/>
+      <c r="AF15" s="6" t="n">
         <v>1900</v>
       </c>
-      <c r="AG10" s="2" t="n">
+      <c r="AG15" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="AH10" s="2" t="n">
+      <c r="AH15" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="AI10" s="2" t="inlineStr">
+      <c r="AI15" s="6" t="inlineStr">
         <is>
           <t>Corcoran</t>
         </is>
       </c>
-      <c r="AJ10" s="2" t="inlineStr">
+      <c r="AJ15" s="6" t="inlineStr">
         <is>
           <t>Corcoran Group</t>
         </is>
       </c>
-      <c r="AK10" s="2" t="inlineStr">
+      <c r="AK15" s="6" t="inlineStr">
         <is>
           <t>Limited Liability Broker</t>
         </is>
       </c>
-      <c r="AL10" s="2" t="inlineStr">
+      <c r="AL15" s="6" t="inlineStr">
         <is>
           <t>590 Madison Avenue, New York, NY, 10022</t>
         </is>
       </c>
-      <c r="AM10" s="2" t="inlineStr">
+      <c r="AM15" s="6" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN10" s="4" t="n">
+      <c r="AN15" s="8" t="n">
         <v>13400</v>
       </c>
-      <c r="AO10" s="5" t="inlineStr">
+      <c r="AO15" s="9" t="inlineStr">
         <is>
           <t>Administration: $17; Application fee: $20; Security deposit: $13,400</t>
         </is>
       </c>
-      <c r="AP10" s="2" t="inlineStr">
+      <c r="AP15" s="6" t="inlineStr">
         <is>
           <t>2026-07-03: $13,400</t>
         </is>
       </c>
-      <c r="AQ10" s="5" t="inlineStr">
+      <c r="AQ15" s="9" t="inlineStr">
         <is>
           <t>2026-07-03: $13,400 ACTIVE; 2025-09-30: $12,300 DELISTED; 2025-09-30: $12,300 None; 2025-09-08: $11,700 ACTIVE; 2023-07-26: $11,300 RENTED; 2023-06-27: $11,300 ACTIVE</t>
         </is>
       </c>
-      <c r="AR10" s="4" t="n">
+      <c r="AR15" s="8" t="n">
         <v>13400</v>
       </c>
-      <c r="AS10" s="2" t="inlineStr"/>
-      <c r="AT10" s="2" t="n">
+      <c r="AS15" s="6" t="inlineStr"/>
+      <c r="AT15" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="AU10" s="2" t="n">
+      <c r="AU15" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="AV10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" s="2" t="inlineStr"/>
-      <c r="AX10" s="2" t="inlineStr"/>
-      <c r="AY10" s="2" t="inlineStr">
+      <c r="AV15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" s="6" t="inlineStr"/>
+      <c r="AX15" s="6" t="inlineStr"/>
+      <c r="AY15" s="6" t="inlineStr">
         <is>
           <t>PARTNER</t>
         </is>
       </c>
-      <c r="AZ10" s="2" t="n">
+      <c r="AZ15" s="6" t="n">
         <v>40.7221</v>
       </c>
-      <c r="BA10" s="2" t="n">
+      <c r="BA15" s="6" t="n">
         <v>-73.98309999999999</v>
       </c>
-      <c r="BB10" s="2" t="inlineStr"/>
-      <c r="BC10" s="5" t="inlineStr">
+      <c r="BB15" s="6" t="inlineStr"/>
+      <c r="BC15" s="9" t="inlineStr">
         <is>
           <t>HAPPY 250 , USA!!! ~ ENJOY YOUR WEEKEND AND STAY COOL OUT THERE!!!
 SHOWS BY OPEN HOUSE ONLY! - NEXT OPEN HOUSE IS TUESDAY ( 7/7/26 )  -5 - 6 pm.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>5077478</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5077478</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>528 East 6th Street #2</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>East Village</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>10009</t>
         </is>
       </c>
-      <c r="H11" s="8" t="n">
+      <c r="H16" s="4" t="n">
         <v>14500</v>
       </c>
-      <c r="I11" s="8" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n">
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="M16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="N11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="6" t="n">
+      <c r="N16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="P16" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="Q11" s="8" t="n">
+      <c r="Q16" s="4" t="n">
         <v>116</v>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>Rental unit</t>
         </is>
       </c>
-      <c r="S11" s="6" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T11" s="6" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
         <is>
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="U11" s="6" t="n">
+      <c r="U16" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="V11" s="6" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="W11" s="6" t="inlineStr">
+      <c r="W16" s="2" t="inlineStr">
         <is>
           <t>Garden; Terrace</t>
         </is>
       </c>
-      <c r="X11" s="6" t="inlineStr">
+      <c r="X16" s="2" t="inlineStr">
         <is>
           <t>City; Garden</t>
         </is>
       </c>
-      <c r="Y11" s="9" t="inlineStr">
+      <c r="Y16" s="5" t="inlineStr">
         <is>
           <t>Central Ac; Dishwasher; Hardwood Floors; Private Outdoor Space; View; Washer Dryer</t>
         </is>
       </c>
-      <c r="Z11" s="9" t="inlineStr">
+      <c r="Z16" s="5" t="inlineStr">
         <is>
           <t>Doorman; Elevator; Fios Available; Shared Outdoor Space</t>
         </is>
       </c>
-      <c r="AA11" s="6" t="inlineStr">
+      <c r="AA16" s="2" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="AB11" s="6" t="inlineStr"/>
-      <c r="AC11" s="6" t="inlineStr">
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
         <is>
           <t>Roof Deck</t>
         </is>
       </c>
-      <c r="AD11" s="6" t="inlineStr"/>
-      <c r="AE11" s="6" t="inlineStr"/>
-      <c r="AF11" s="6" t="n">
+      <c r="AD16" s="2" t="inlineStr"/>
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="n">
         <v>2008</v>
       </c>
-      <c r="AG11" s="6" t="n">
+      <c r="AG16" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AH11" s="6" t="n">
+      <c r="AH16" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="AI11" s="6" t="inlineStr">
+      <c r="AI16" s="2" t="inlineStr">
         <is>
           <t>MK Realty Group LLC</t>
         </is>
       </c>
-      <c r="AJ11" s="6" t="inlineStr">
+      <c r="AJ16" s="2" t="inlineStr">
         <is>
           <t>Mk Realty Group Llc</t>
         </is>
       </c>
-      <c r="AK11" s="6" t="inlineStr">
+      <c r="AK16" s="2" t="inlineStr">
         <is>
           <t>Real Estate Principal Office</t>
         </is>
       </c>
-      <c r="AL11" s="6" t="inlineStr">
+      <c r="AL16" s="2" t="inlineStr">
         <is>
           <t>100 Carlyle Dr, Ste 3ms, Cliffside Park, NJ, 07010-3540</t>
         </is>
       </c>
-      <c r="AM11" s="6" t="inlineStr">
+      <c r="AM16" s="2" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN11" s="8" t="n">
+      <c r="AN16" s="4" t="n">
         <v>14750</v>
       </c>
-      <c r="AO11" s="9" t="inlineStr">
+      <c r="AO16" s="5" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $14,750</t>
         </is>
       </c>
-      <c r="AP11" s="6" t="inlineStr">
+      <c r="AP16" s="2" t="inlineStr">
         <is>
           <t>2026-06-19: $14,750; 2026-07-07: $14,500</t>
         </is>
       </c>
-      <c r="AQ11" s="9" t="inlineStr">
+      <c r="AQ16" s="5" t="inlineStr">
         <is>
           <t>2026-07-07: $14,500 None; 2026-06-19: $14,750 ACTIVE; 2024-09-23: $9,000 NO_LONGER_AVAILABLE; 2024-06-24: $9,000 TEMPORARILY_OFF_MARKET; 2024-05-06: $9,000 ACTIVE; 2022-04-21: $8,500 RENTED; 2022-04-21: $8,500 IN_CONTRACT; 2022-04-20: $8,500 TEMPORARILY_OFF_MARKET; 2022-04-19: $8,500 ACTIVE; 2019-04-06: $7,200 RENTED; 2019-04-03: $7,200 None; 2017-05-01: $7,250 RENTED; 2014-11-26: $7,200 NO_LONGER_AVAILABLE; 2014-11-26: $7,200 ACTIVE; 2014-11-26: $7,250 NO_LONGER_AVAILABLE; 2014-11-26: $7,250 ACTIVE; 2014-11-26: $7,300 RENTED; 2014-11-26: $7,300 NO_LONGER_AVAILABLE; 2014-11-21: $7,300 None; 2014-11-19: $6,700 ACTIVE</t>
         </is>
       </c>
-      <c r="AR11" s="8" t="n">
+      <c r="AR16" s="4" t="n">
         <v>7722</v>
       </c>
-      <c r="AS11" s="6" t="inlineStr"/>
-      <c r="AT11" s="6" t="n">
+      <c r="AS16" s="2" t="inlineStr"/>
+      <c r="AT16" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="AU11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" s="6" t="n">
+      <c r="AU16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AW11" s="6" t="inlineStr"/>
-      <c r="AX11" s="6" t="inlineStr"/>
-      <c r="AY11" s="6" t="inlineStr">
+      <c r="AW16" s="2" t="inlineStr"/>
+      <c r="AX16" s="2" t="inlineStr"/>
+      <c r="AY16" s="2" t="inlineStr">
         <is>
           <t>PARTNER</t>
         </is>
       </c>
-      <c r="AZ11" s="6" t="n">
+      <c r="AZ16" s="2" t="n">
         <v>40.72468</v>
       </c>
-      <c r="BA11" s="6" t="n">
+      <c r="BA16" s="2" t="n">
         <v>-73.98266599999999</v>
       </c>
-      <c r="BB11" s="6" t="inlineStr">
+      <c r="BB16" s="2" t="inlineStr">
         <is>
           <t>corcoran.com listing for 528 E 6th St #2 ('approximately 1,500 sq ft')</t>
         </is>
       </c>
-      <c r="BC11" s="9" t="inlineStr">
+      <c r="BC16" s="5" t="inlineStr">
         <is>
           <t>FULL-FLOOR 3 BEDROOM WITH PRIVATE GARDEN, 3 FULL BATHS &amp; IN-UNIT WASHER/DRYER. 
 Welcome to a rare opportunity to enjoy true indoor-outdoor living in the heart of downtown Manhattan. This expansive full-floor residence offers 3 king-sized bedrooms, 3 full bathrooms, soaring ceilings, oversized floor-to-ceiling windows, and both northern and southern exposures that fill the home with natural light throughout the day.
@@ -2922,198 +3944,198 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>5084015</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5084015</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>96 West Houston Street #1F</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>#1F</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>Greenwich Village</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>10012</t>
         </is>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H17" s="8" t="n">
         <v>8300</v>
       </c>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="n">
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="M12" s="2" t="n">
+      <c r="M17" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="N12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="2" t="n">
+      <c r="N17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="P12" s="2" t="n">
+      <c r="P17" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="Q12" s="4" t="n">
+      <c r="Q17" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>Rental unit</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr">
+      <c r="S17" s="6" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T12" s="2" t="inlineStr">
+      <c r="T17" s="6" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="U12" s="2" t="n">
+      <c r="U17" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V17" s="6" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="W12" s="2" t="inlineStr">
+      <c r="W17" s="6" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="X12" s="2" t="inlineStr">
+      <c r="X17" s="6" t="inlineStr">
         <is>
           <t>City; Garden</t>
         </is>
       </c>
-      <c r="Y12" s="5" t="inlineStr">
+      <c r="Y17" s="9" t="inlineStr">
         <is>
           <t>Central Ac; Dishwasher; Furnished; Hardwood Floors; Loft; Private Outdoor Space; View; Washer Dryer</t>
         </is>
       </c>
-      <c r="Z12" s="5" t="inlineStr">
+      <c r="Z17" s="9" t="inlineStr">
         <is>
           <t>Laundry; Shared Outdoor Space</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr"/>
-      <c r="AB12" s="2" t="inlineStr"/>
-      <c r="AC12" s="2" t="inlineStr">
+      <c r="AA17" s="6" t="inlineStr"/>
+      <c r="AB17" s="6" t="inlineStr"/>
+      <c r="AC17" s="6" t="inlineStr">
         <is>
           <t>Courtyard</t>
         </is>
       </c>
-      <c r="AD12" s="2" t="inlineStr"/>
-      <c r="AE12" s="2" t="inlineStr"/>
-      <c r="AF12" s="2" t="n">
+      <c r="AD17" s="6" t="inlineStr"/>
+      <c r="AE17" s="6" t="inlineStr"/>
+      <c r="AF17" s="6" t="n">
         <v>1900</v>
       </c>
-      <c r="AG12" s="2" t="n">
+      <c r="AG17" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="AH12" s="2" t="n">
+      <c r="AH17" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="AI12" s="2" t="inlineStr">
+      <c r="AI17" s="6" t="inlineStr">
         <is>
           <t>Benjamin James</t>
         </is>
       </c>
-      <c r="AJ12" s="2" t="inlineStr">
+      <c r="AJ17" s="6" t="inlineStr">
         <is>
           <t>Benjamin James Re Inc</t>
         </is>
       </c>
-      <c r="AK12" s="2" t="inlineStr">
+      <c r="AK17" s="6" t="inlineStr">
         <is>
           <t>Real Estate Principal Office</t>
         </is>
       </c>
-      <c r="AL12" s="2" t="inlineStr">
+      <c r="AL17" s="6" t="inlineStr">
         <is>
           <t>96 West Houston Street, 3rd Fl, New York, NY, 10012</t>
         </is>
       </c>
-      <c r="AM12" s="2" t="inlineStr">
+      <c r="AM17" s="6" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN12" s="4" t="n">
+      <c r="AN17" s="8" t="n">
         <v>8300</v>
       </c>
-      <c r="AO12" s="5" t="inlineStr">
+      <c r="AO17" s="9" t="inlineStr">
         <is>
           <t>Application fee: $0; Security deposit: $8,300</t>
         </is>
       </c>
-      <c r="AP12" s="2" t="inlineStr">
+      <c r="AP17" s="6" t="inlineStr">
         <is>
           <t>2026-06-25: $8,300</t>
         </is>
       </c>
-      <c r="AQ12" s="5" t="inlineStr">
+      <c r="AQ17" s="9" t="inlineStr">
         <is>
           <t>2026-06-25: $8,300 ACTIVE; 2025-07-24: $8,300 RENTED; 2025-07-02: $8,300 ACTIVE; 2023-01-19: $6,900 NO_LONGER_AVAILABLE; 2023-01-04: $6,900 ACTIVE; 2023-01-04: $6,900 None; 2023-01-03: $7,500 NO_LONGER_AVAILABLE; 2022-12-19: $7,500 ACTIVE; 2015-10-30: $5,700 RENTED; 2015-10-09: $5,700 ACTIVE</t>
         </is>
       </c>
-      <c r="AR12" s="4" t="n">
+      <c r="AR17" s="8" t="n">
         <v>6995</v>
       </c>
-      <c r="AS12" s="2" t="inlineStr"/>
-      <c r="AT12" s="2" t="n">
+      <c r="AS17" s="6" t="inlineStr"/>
+      <c r="AT17" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="AU12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" s="2" t="inlineStr"/>
-      <c r="AX12" s="2" t="inlineStr"/>
-      <c r="AY12" s="2" t="inlineStr">
+      <c r="AU17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" s="6" t="inlineStr"/>
+      <c r="AX17" s="6" t="inlineStr"/>
+      <c r="AY17" s="6" t="inlineStr">
         <is>
           <t>PARTNER</t>
         </is>
       </c>
-      <c r="AZ12" s="2" t="n">
+      <c r="AZ17" s="6" t="n">
         <v>40.727364</v>
       </c>
-      <c r="BA12" s="2" t="n">
+      <c r="BA17" s="6" t="n">
         <v>-74.00009</v>
       </c>
-      <c r="BB12" s="2" t="inlineStr"/>
-      <c r="BC12" s="5" t="inlineStr">
+      <c r="BB17" s="6" t="inlineStr"/>
+      <c r="BC17" s="9" t="inlineStr">
         <is>
           <t>No fee.
 Fully renovated full floor townhouse/loft on the border of West Village and Soho. You'll be amazed by the 15' ceilings with 8" crown molding, dark almond oak floors throughout, gourmet chef's kitchen with slate floors, custom cabinetry, granite countertops, high end stainless appliances and a washer dryer.
@@ -3127,204 +4149,204 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>5082561</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5082561</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>20 East 13th Street #4A</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>#4A</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Greenwich Village</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>10003</t>
         </is>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H18" s="4" t="n">
         <v>10500</v>
       </c>
-      <c r="I13" s="8" t="n">
+      <c r="I18" s="4" t="n">
         <v>9625</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="J18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="6" t="n">
+      <c r="K18" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="L18" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M13" s="6" t="n">
+      <c r="M18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="6" t="n">
+      <c r="N18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="P13" s="6" t="inlineStr"/>
-      <c r="Q13" s="8" t="inlineStr"/>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="4" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>Rental unit</t>
         </is>
       </c>
-      <c r="S13" s="6" t="inlineStr">
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T13" s="6" t="inlineStr">
+      <c r="T18" s="2" t="inlineStr">
         <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="U13" s="6" t="n">
+      <c r="U18" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="V13" s="6" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="W13" s="6" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>Balcony; Private Roof Deck; Roof Rights</t>
         </is>
       </c>
-      <c r="X13" s="6" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr">
         <is>
           <t>City; Garden</t>
         </is>
       </c>
-      <c r="Y13" s="9" t="inlineStr">
+      <c r="Y18" s="5" t="inlineStr">
         <is>
           <t>Central Ac; Dishwasher; Hardwood Floors; Private Outdoor Space; View; Washer Dryer</t>
         </is>
       </c>
-      <c r="Z13" s="9" t="inlineStr">
+      <c r="Z18" s="5" t="inlineStr">
         <is>
           <t>Doorman; Fios Available; Shared Outdoor Space</t>
         </is>
       </c>
-      <c r="AA13" s="6" t="inlineStr">
+      <c r="AA18" s="2" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="AB13" s="6" t="inlineStr"/>
-      <c r="AC13" s="6" t="inlineStr">
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
         <is>
           <t>Roof Deck</t>
         </is>
       </c>
-      <c r="AD13" s="6" t="inlineStr"/>
-      <c r="AE13" s="6" t="inlineStr"/>
-      <c r="AF13" s="6" t="n">
+      <c r="AD18" s="2" t="inlineStr"/>
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="n">
         <v>1900</v>
       </c>
-      <c r="AG13" s="6" t="n">
+      <c r="AG18" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AH13" s="6" t="n">
+      <c r="AH18" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AI13" s="6" t="inlineStr">
+      <c r="AI18" s="2" t="inlineStr">
         <is>
           <t>REAL New York</t>
         </is>
       </c>
-      <c r="AJ13" s="6" t="inlineStr">
+      <c r="AJ18" s="2" t="inlineStr">
         <is>
           <t>Real New York</t>
         </is>
       </c>
-      <c r="AK13" s="6" t="inlineStr">
+      <c r="AK18" s="2" t="inlineStr">
         <is>
           <t>Limited Liability Broker</t>
         </is>
       </c>
-      <c r="AL13" s="6" t="inlineStr">
+      <c r="AL18" s="2" t="inlineStr">
         <is>
           <t>29 West 30th Street West 30th Street, 4th Fl, New York, NY, 10001</t>
         </is>
       </c>
-      <c r="AM13" s="6" t="inlineStr">
+      <c r="AM18" s="2" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN13" s="8" t="n">
+      <c r="AN18" s="4" t="n">
         <v>10850</v>
       </c>
-      <c r="AO13" s="9" t="inlineStr">
+      <c r="AO18" s="5" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $10,850</t>
         </is>
       </c>
-      <c r="AP13" s="6" t="inlineStr">
+      <c r="AP18" s="2" t="inlineStr">
         <is>
           <t>2026-06-24: $10,850; 2026-07-08: $10,500</t>
         </is>
       </c>
-      <c r="AQ13" s="9" t="inlineStr">
+      <c r="AQ18" s="5" t="inlineStr">
         <is>
           <t>2026-07-08: $10,500 None; 2026-06-24: $10,850 ACTIVE; 2025-05-17: $10,450 NO_LONGER_AVAILABLE; 2025-05-02: $10,450 ACTIVE</t>
         </is>
       </c>
-      <c r="AR13" s="8" t="n">
+      <c r="AR18" s="4" t="n">
         <v>9695</v>
       </c>
-      <c r="AS13" s="6" t="inlineStr"/>
-      <c r="AT13" s="6" t="n">
+      <c r="AS18" s="2" t="inlineStr"/>
+      <c r="AT18" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="AU13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" s="6" t="inlineStr"/>
-      <c r="AX13" s="6" t="inlineStr"/>
-      <c r="AY13" s="6" t="inlineStr">
+      <c r="AU18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" s="2" t="inlineStr"/>
+      <c r="AX18" s="2" t="inlineStr"/>
+      <c r="AY18" s="2" t="inlineStr">
         <is>
           <t>PARTNER</t>
         </is>
       </c>
-      <c r="AZ13" s="6" t="n">
+      <c r="AZ18" s="2" t="n">
         <v>40.73472</v>
       </c>
-      <c r="BA13" s="6" t="n">
+      <c r="BA18" s="2" t="n">
         <v>-73.99321999999999</v>
       </c>
-      <c r="BB13" s="6" t="inlineStr"/>
-      <c r="BC13" s="9" t="inlineStr">
+      <c r="BB18" s="2" t="inlineStr"/>
+      <c r="BC18" s="5" t="inlineStr">
         <is>
           <t>Brand-New Full-Floor Residence in the Heart of Union Square with Private Outdoor Space
 Welcome to an exceptional living experience at 20 East 13th Street — a brand-new full-floor 3-bedroom residence designed with luxury, comfort, and modern city living in mind. Featuring condo-quality finishes, expansive living spaces, and dramatic floor-to-ceiling windows, this one-of-a-kind home offers the perfect blend of sophistication and convenience in one of Manhattan’s most vibrant neighborhoods.
@@ -3356,210 +4378,210 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>5083885</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5083885</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>112 4th Avenue #5A</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>#5A</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>Greenwich Village</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>10003</t>
         </is>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H19" s="8" t="n">
         <v>14500</v>
       </c>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
-      <c r="L14" s="2" t="n">
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="M14" s="2" t="n">
+      <c r="M19" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="2" t="n">
+      <c r="N19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="P14" s="2" t="n">
+      <c r="P19" s="6" t="n">
         <v>1675</v>
       </c>
-      <c r="Q14" s="4" t="n">
+      <c r="Q19" s="8" t="n">
         <v>104</v>
       </c>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>Rental unit</t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr">
+      <c r="S19" s="6" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T14" s="2" t="inlineStr">
+      <c r="T19" s="6" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="U14" s="2" t="n">
+      <c r="U19" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V19" s="6" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="W14" s="2" t="inlineStr">
+      <c r="W19" s="6" t="inlineStr">
         <is>
           <t>Private Roof Deck</t>
         </is>
       </c>
-      <c r="X14" s="2" t="inlineStr">
+      <c r="X19" s="6" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="Y14" s="5" t="inlineStr">
+      <c r="Y19" s="9" t="inlineStr">
         <is>
           <t>Central Ac; Dishwasher; Hardwood Floors; Loft; Private Outdoor Space; View; Washer Dryer</t>
         </is>
       </c>
-      <c r="Z14" s="5" t="inlineStr">
+      <c r="Z19" s="9" t="inlineStr">
         <is>
           <t>Doorman; Elevator; Shared Outdoor Space; Storage Space</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
+      <c r="AA19" s="6" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr"/>
-      <c r="AC14" s="2" t="inlineStr">
+      <c r="AB19" s="6" t="inlineStr"/>
+      <c r="AC19" s="6" t="inlineStr">
         <is>
           <t>Roof Deck</t>
         </is>
       </c>
-      <c r="AD14" s="2" t="inlineStr">
+      <c r="AD19" s="6" t="inlineStr">
         <is>
           <t>Locker Cage</t>
         </is>
       </c>
-      <c r="AE14" s="2" t="inlineStr">
+      <c r="AE19" s="6" t="inlineStr">
         <is>
           <t>The Roselyn</t>
         </is>
       </c>
-      <c r="AF14" s="2" t="n">
+      <c r="AF19" s="6" t="n">
         <v>1900</v>
       </c>
-      <c r="AG14" s="2" t="n">
+      <c r="AG19" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="AH14" s="2" t="n">
+      <c r="AH19" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="AI14" s="2" t="inlineStr">
+      <c r="AI19" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Bridge Real Estate Advisory LLC </t>
         </is>
       </c>
-      <c r="AJ14" s="2" t="inlineStr">
+      <c r="AJ19" s="6" t="inlineStr">
         <is>
           <t>Bridge Real Estate Advisory Llc</t>
         </is>
       </c>
-      <c r="AK14" s="2" t="inlineStr">
+      <c r="AK19" s="6" t="inlineStr">
         <is>
           <t>Real Estate Principal Office</t>
         </is>
       </c>
-      <c r="AL14" s="2" t="inlineStr">
+      <c r="AL19" s="6" t="inlineStr">
         <is>
           <t>600 Third Avenue, 10th Fl, New York, NY, 10016</t>
         </is>
       </c>
-      <c r="AM14" s="2" t="inlineStr">
+      <c r="AM19" s="6" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="5" t="inlineStr">
+      <c r="AN19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" s="9" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $0</t>
         </is>
       </c>
-      <c r="AP14" s="2" t="inlineStr">
+      <c r="AP19" s="6" t="inlineStr">
         <is>
           <t>2026-06-25: $14,500</t>
         </is>
       </c>
-      <c r="AQ14" s="5" t="inlineStr">
+      <c r="AQ19" s="9" t="inlineStr">
         <is>
           <t>2026-06-25: $14,500 ACTIVE; 2025-08-22: $16,000 NO_LONGER_AVAILABLE; 2025-05-23: $16,000 TEMPORARILY_OFF_MARKET; 2025-04-01: $16,000 ACTIVE</t>
         </is>
       </c>
-      <c r="AR14" s="4" t="n">
+      <c r="AR19" s="8" t="n">
         <v>6995</v>
       </c>
-      <c r="AS14" s="2" t="inlineStr"/>
-      <c r="AT14" s="2" t="n">
+      <c r="AS19" s="6" t="inlineStr"/>
+      <c r="AT19" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="AU14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" s="2" t="n">
+      <c r="AU19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="AW14" s="2" t="inlineStr"/>
-      <c r="AX14" s="2" t="inlineStr"/>
-      <c r="AY14" s="2" t="inlineStr">
+      <c r="AW19" s="6" t="inlineStr"/>
+      <c r="AX19" s="6" t="inlineStr"/>
+      <c r="AY19" s="6" t="inlineStr">
         <is>
           <t>PARTNER</t>
         </is>
       </c>
-      <c r="AZ14" s="2" t="n">
+      <c r="AZ19" s="6" t="n">
         <v>40.732613</v>
       </c>
-      <c r="BA14" s="2" t="n">
+      <c r="BA19" s="6" t="n">
         <v>-73.99046</v>
       </c>
-      <c r="BB14" s="2" t="inlineStr"/>
-      <c r="BC14" s="5" t="inlineStr">
+      <c r="BB19" s="6" t="inlineStr"/>
+      <c r="BC19" s="9" t="inlineStr">
         <is>
           <t>Available at 112 4th Avenue!
 Apartment Features:
@@ -3585,190 +4607,190 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>5092580</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5092580</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>21 Bleecker Street #1E</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>#1E</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Noho</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>10012</t>
         </is>
       </c>
-      <c r="H15" s="8" t="n">
+      <c r="H20" s="4" t="n">
         <v>18000</v>
       </c>
-      <c r="I15" s="8" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n">
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M15" s="6" t="n">
+      <c r="M20" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="N20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O15" s="6" t="n">
+      <c r="O20" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="P20" s="2" t="n">
         <v>2300</v>
       </c>
-      <c r="Q15" s="8" t="n">
+      <c r="Q20" s="4" t="n">
         <v>94</v>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>Co-op</t>
         </is>
       </c>
-      <c r="S15" s="6" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T15" s="6" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="U15" s="6" t="n">
+      <c r="U20" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="V15" s="6" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="W15" s="6" t="inlineStr">
+      <c r="W20" s="2" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="X15" s="6" t="inlineStr">
+      <c r="X20" s="2" t="inlineStr">
         <is>
           <t>City; Garden</t>
         </is>
       </c>
-      <c r="Y15" s="9" t="inlineStr">
+      <c r="Y20" s="5" t="inlineStr">
         <is>
           <t>Central Ac; Dishwasher; Furnished; Hardwood Floors; Private Outdoor Space; View; Washer Dryer</t>
         </is>
       </c>
-      <c r="Z15" s="9" t="inlineStr"/>
-      <c r="AA15" s="6" t="inlineStr"/>
-      <c r="AB15" s="6" t="inlineStr"/>
-      <c r="AC15" s="6" t="inlineStr"/>
-      <c r="AD15" s="6" t="inlineStr"/>
-      <c r="AE15" s="6" t="inlineStr"/>
-      <c r="AF15" s="6" t="n">
+      <c r="Z20" s="5" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AD20" s="2" t="inlineStr"/>
+      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="2" t="n">
         <v>1830</v>
       </c>
-      <c r="AG15" s="6" t="n">
+      <c r="AG20" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AH15" s="6" t="n">
+      <c r="AH20" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AI15" s="6" t="inlineStr">
+      <c r="AI20" s="2" t="inlineStr">
         <is>
           <t>Corcoran</t>
         </is>
       </c>
-      <c r="AJ15" s="6" t="inlineStr">
+      <c r="AJ20" s="2" t="inlineStr">
         <is>
           <t>Corcoran Group</t>
         </is>
       </c>
-      <c r="AK15" s="6" t="inlineStr">
+      <c r="AK20" s="2" t="inlineStr">
         <is>
           <t>Limited Liability Broker</t>
         </is>
       </c>
-      <c r="AL15" s="6" t="inlineStr">
+      <c r="AL20" s="2" t="inlineStr">
         <is>
           <t>590 Madison Avenue, New York, NY, 10022</t>
         </is>
       </c>
-      <c r="AM15" s="6" t="inlineStr">
+      <c r="AM20" s="2" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN15" s="8" t="n">
+      <c r="AN20" s="4" t="n">
         <v>18000</v>
       </c>
-      <c r="AO15" s="9" t="inlineStr">
+      <c r="AO20" s="5" t="inlineStr">
         <is>
           <t>Move-in deposit: $500; Application fee: $0; Security deposit: $18,000</t>
         </is>
       </c>
-      <c r="AP15" s="6" t="inlineStr">
+      <c r="AP20" s="2" t="inlineStr">
         <is>
           <t>2026-07-06: $18,000</t>
         </is>
       </c>
-      <c r="AQ15" s="9" t="inlineStr">
+      <c r="AQ20" s="5" t="inlineStr">
         <is>
           <t>2026-07-06: $18,000 ACTIVE; 2024-06-24: $15,000 RENTED; 2024-06-03: $15,000 DELISTED; 2024-05-29: $15,000 ACTIVE; 2024-05-22: $15,000 DELISTED; 2024-05-16: $15,000 ACTIVE; 2020-09-28: $10,000 NO_LONGER_AVAILABLE; 2020-09-28: $10,000 IN_CONTRACT; 2020-08-28: $10,000 None; 2020-05-18: $12,000 ACTIVE; 2020-05-12: $12,000 RENTED; 2019-08-26: $12,000 NO_LONGER_AVAILABLE; 2019-08-05: $12,000 ACTIVE; 2019-07-29: $12,000 NO_LONGER_AVAILABLE; 2019-07-22: $12,000 ACTIVE; 2019-07-18: $12,000 NO_LONGER_AVAILABLE; 2019-07-09: $12,000 ACTIVE</t>
         </is>
       </c>
-      <c r="AR15" s="8" t="n">
+      <c r="AR20" s="4" t="n">
         <v>14750</v>
       </c>
-      <c r="AS15" s="6" t="inlineStr"/>
-      <c r="AT15" s="6" t="n">
+      <c r="AS20" s="2" t="inlineStr"/>
+      <c r="AT20" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="AU15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" s="6" t="n">
+      <c r="AU20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AW15" s="6" t="inlineStr"/>
-      <c r="AX15" s="6" t="inlineStr"/>
-      <c r="AY15" s="6" t="inlineStr">
+      <c r="AW20" s="2" t="inlineStr"/>
+      <c r="AX20" s="2" t="inlineStr"/>
+      <c r="AY20" s="2" t="inlineStr">
         <is>
           <t>PARTNER</t>
         </is>
       </c>
-      <c r="AZ15" s="6" t="n">
+      <c r="AZ20" s="2" t="n">
         <v>40.72569</v>
       </c>
-      <c r="BA15" s="6" t="n">
+      <c r="BA20" s="2" t="n">
         <v>-73.99328</v>
       </c>
-      <c r="BB15" s="6" t="inlineStr"/>
-      <c r="BC15" s="9" t="inlineStr">
+      <c r="BB20" s="2" t="inlineStr"/>
+      <c r="BC20" s="5" t="inlineStr">
         <is>
           <t>Welcome home to this 2300sf luxury duplex loft on a prime block in the heart of NoHo. Custom designed throughout with a separate entrance and 400sf private garden.
 The upper level features open-plan living with 10 foot ceilings, a chef's kitchen and dining room. The downstairs has a pin-drop quiet primary bedroom suite, a home office, a second bedroom and additional studio for guests or rec space.
@@ -3783,198 +4805,198 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>5093530</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5093530</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>139 Wooster Street #5B</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>#5B</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>Soho</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>10012</t>
         </is>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="H21" s="8" t="n">
         <v>18000</v>
       </c>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n">
+      <c r="I21" s="8" t="n"/>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
+      <c r="L21" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="M16" s="2" t="n">
+      <c r="M21" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="N16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="2" t="n">
+      <c r="N21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="P16" s="2" t="n">
+      <c r="P21" s="6" t="n">
         <v>1472</v>
       </c>
-      <c r="Q16" s="4" t="n">
+      <c r="Q21" s="8" t="n">
         <v>147</v>
       </c>
-      <c r="R16" s="2" t="inlineStr">
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="S16" s="2" t="inlineStr">
+      <c r="S21" s="6" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T16" s="2" t="inlineStr">
+      <c r="T21" s="6" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="U16" s="2" t="n">
+      <c r="U21" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V21" s="6" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="W16" s="2" t="inlineStr">
+      <c r="W21" s="6" t="inlineStr">
         <is>
           <t>Balcony</t>
         </is>
       </c>
-      <c r="X16" s="2" t="inlineStr"/>
-      <c r="Y16" s="5" t="inlineStr">
+      <c r="X21" s="6" t="inlineStr"/>
+      <c r="Y21" s="9" t="inlineStr">
         <is>
           <t>Central Ac; Dishwasher; Hardwood Floors; Private Outdoor Space; Washer Dryer</t>
         </is>
       </c>
-      <c r="Z16" s="5" t="inlineStr">
+      <c r="Z21" s="9" t="inlineStr">
         <is>
           <t>Concierge; Doorman; Elevator; Fios Available; Gym; Shared Outdoor Space</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
+      <c r="AA21" s="6" t="inlineStr">
         <is>
           <t>Full Time</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr"/>
-      <c r="AC16" s="2" t="inlineStr">
+      <c r="AB21" s="6" t="inlineStr"/>
+      <c r="AC21" s="6" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="AD16" s="2" t="inlineStr"/>
-      <c r="AE16" s="2" t="inlineStr"/>
-      <c r="AF16" s="2" t="n">
+      <c r="AD21" s="6" t="inlineStr"/>
+      <c r="AE21" s="6" t="inlineStr"/>
+      <c r="AF21" s="6" t="n">
         <v>2006</v>
       </c>
-      <c r="AG16" s="2" t="n">
+      <c r="AG21" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="AH16" s="2" t="n">
+      <c r="AH21" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="AI16" s="2" t="inlineStr">
+      <c r="AI21" s="6" t="inlineStr">
         <is>
           <t>Corcoran</t>
         </is>
       </c>
-      <c r="AJ16" s="2" t="inlineStr">
+      <c r="AJ21" s="6" t="inlineStr">
         <is>
           <t>Corcoran Group</t>
         </is>
       </c>
-      <c r="AK16" s="2" t="inlineStr">
+      <c r="AK21" s="6" t="inlineStr">
         <is>
           <t>Limited Liability Broker</t>
         </is>
       </c>
-      <c r="AL16" s="2" t="inlineStr">
+      <c r="AL21" s="6" t="inlineStr">
         <is>
           <t>590 Madison Avenue, New York, NY, 10022</t>
         </is>
       </c>
-      <c r="AM16" s="2" t="inlineStr">
+      <c r="AM21" s="6" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN16" s="4" t="n">
+      <c r="AN21" s="8" t="n">
         <v>18000</v>
       </c>
-      <c r="AO16" s="5" t="inlineStr">
+      <c r="AO21" s="9" t="inlineStr">
         <is>
           <t>Application fee: $18,000; Security deposit: $18,000</t>
         </is>
       </c>
-      <c r="AP16" s="2" t="inlineStr">
+      <c r="AP21" s="6" t="inlineStr">
         <is>
           <t>2026-07-06: $18,000</t>
         </is>
       </c>
-      <c r="AQ16" s="5" t="inlineStr">
+      <c r="AQ21" s="9" t="inlineStr">
         <is>
           <t>2026-07-06: $18,000 ACTIVE; 2020-11-23: $9,950 DELISTED; 2020-09-21: $9,950 ACTIVE; 2011-08-19: $12,500 RENTED; 2011-06-24: $12,500 NO_LONGER_AVAILABLE; 2011-05-20: $12,500 ACTIVE</t>
         </is>
       </c>
-      <c r="AR16" s="4" t="n">
+      <c r="AR21" s="8" t="n">
         <v>6250</v>
       </c>
-      <c r="AS16" s="2" t="inlineStr"/>
-      <c r="AT16" s="2" t="n">
+      <c r="AS21" s="6" t="inlineStr"/>
+      <c r="AT21" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="AU16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" s="2" t="n">
+      <c r="AU21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="AW16" s="2" t="inlineStr"/>
-      <c r="AX16" s="2" t="inlineStr"/>
-      <c r="AY16" s="2" t="inlineStr">
+      <c r="AW21" s="6" t="inlineStr"/>
+      <c r="AX21" s="6" t="inlineStr"/>
+      <c r="AY21" s="6" t="inlineStr">
         <is>
           <t>PARTNER</t>
         </is>
       </c>
-      <c r="AZ16" s="2" t="n">
+      <c r="AZ21" s="6" t="n">
         <v>40.72592</v>
       </c>
-      <c r="BA16" s="2" t="n">
+      <c r="BA21" s="6" t="n">
         <v>-74.00011000000001</v>
       </c>
-      <c r="BB16" s="2" t="inlineStr"/>
-      <c r="BC16" s="5" t="inlineStr">
+      <c r="BB21" s="6" t="inlineStr"/>
+      <c r="BC21" s="9" t="inlineStr">
         <is>
           <t>Brand-New Designer Loft Rental in the Heart of SoHo
 Introducing Residence 5B at 139 Wooster Street—an extraordinary, never-lived-in designer residence that has been meticulously reimagined from top to bottom. Perfectly positioned on one of SoHo's most coveted cobblestone streets, this exceptional two-bedroom, two-bathroom condominium seamlessly blends authentic loft architecture with sophisticated contemporary design, creating a turnkey home of remarkable quality and style.
@@ -4008,210 +5030,210 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>5081661</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5081661</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>50 Murray Street #1839</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>#1839</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Tribeca</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>10007</t>
         </is>
       </c>
-      <c r="H17" s="8" t="n">
+      <c r="H22" s="4" t="n">
         <v>6995</v>
       </c>
-      <c r="I17" s="8" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n">
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M17" s="6" t="n">
+      <c r="M22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="6" t="n">
+      <c r="N22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="P17" s="6" t="inlineStr"/>
-      <c r="Q17" s="8" t="inlineStr"/>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="4" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>Rental unit</t>
         </is>
       </c>
-      <c r="S17" s="6" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T17" s="6" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="U17" s="6" t="n">
+      <c r="U22" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="V17" s="6" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>2026-07-04</t>
         </is>
       </c>
-      <c r="W17" s="6" t="inlineStr">
+      <c r="W22" s="2" t="inlineStr">
         <is>
           <t>Balcony; Terrace</t>
         </is>
       </c>
-      <c r="X17" s="6" t="inlineStr">
+      <c r="X22" s="2" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="Y17" s="9" t="inlineStr">
+      <c r="Y22" s="5" t="inlineStr">
         <is>
           <t>Central Ac; Dishwasher; Hardwood Floors; Private Outdoor Space; View</t>
         </is>
       </c>
-      <c r="Z17" s="9" t="inlineStr">
+      <c r="Z22" s="5" t="inlineStr">
         <is>
           <t>Bike Room; Childrens Playroom; Concierge; Doorman; Elevator; Fios Available; Gym; Laundry; Live In Super; Media Room; Package Room; Parking; Shared Outdoor Space; Storage Space; Valet Service</t>
         </is>
       </c>
-      <c r="AA17" s="6" t="inlineStr">
+      <c r="AA22" s="2" t="inlineStr">
         <is>
           <t>Full Time</t>
         </is>
       </c>
-      <c r="AB17" s="6" t="inlineStr">
+      <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>Garage; Valet</t>
         </is>
       </c>
-      <c r="AC17" s="6" t="inlineStr">
+      <c r="AC22" s="2" t="inlineStr">
         <is>
           <t>Deck; Garden; Patio; Roof Deck</t>
         </is>
       </c>
-      <c r="AD17" s="6" t="inlineStr">
+      <c r="AD22" s="2" t="inlineStr">
         <is>
           <t>Locker Cage</t>
         </is>
       </c>
-      <c r="AE17" s="6" t="inlineStr">
+      <c r="AE22" s="2" t="inlineStr">
         <is>
           <t>Tribeca House</t>
         </is>
       </c>
-      <c r="AF17" s="6" t="n">
+      <c r="AF22" s="2" t="n">
         <v>1964</v>
       </c>
-      <c r="AG17" s="6" t="n">
+      <c r="AG22" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="AH17" s="6" t="n">
+      <c r="AH22" s="2" t="n">
         <v>389</v>
       </c>
-      <c r="AI17" s="6" t="inlineStr">
+      <c r="AI22" s="2" t="inlineStr">
         <is>
           <t>REAL New York</t>
         </is>
       </c>
-      <c r="AJ17" s="6" t="inlineStr">
+      <c r="AJ22" s="2" t="inlineStr">
         <is>
           <t>Real New York</t>
         </is>
       </c>
-      <c r="AK17" s="6" t="inlineStr">
+      <c r="AK22" s="2" t="inlineStr">
         <is>
           <t>Limited Liability Broker</t>
         </is>
       </c>
-      <c r="AL17" s="6" t="inlineStr">
+      <c r="AL22" s="2" t="inlineStr">
         <is>
           <t>29 West 30th Street West 30th Street, 4th Fl, New York, NY, 10001</t>
         </is>
       </c>
-      <c r="AM17" s="6" t="inlineStr">
+      <c r="AM22" s="2" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN17" s="8" t="n">
+      <c r="AN22" s="4" t="n">
         <v>6995</v>
       </c>
-      <c r="AO17" s="9" t="inlineStr">
+      <c r="AO22" s="5" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $6,995</t>
         </is>
       </c>
-      <c r="AP17" s="6" t="inlineStr">
+      <c r="AP22" s="2" t="inlineStr">
         <is>
           <t>2026-06-23: $6,995</t>
         </is>
       </c>
-      <c r="AQ17" s="9" t="inlineStr">
+      <c r="AQ22" s="5" t="inlineStr">
         <is>
           <t>2026-06-23: $6,995 ACTIVE; 2026-05-19: $7,695 RENTED; 2026-04-27: $7,695 ACTIVE</t>
         </is>
       </c>
-      <c r="AR17" s="8" t="n">
+      <c r="AR22" s="4" t="n">
         <v>10555</v>
       </c>
-      <c r="AS17" s="6" t="inlineStr"/>
-      <c r="AT17" s="6" t="n">
+      <c r="AS22" s="2" t="inlineStr"/>
+      <c r="AT22" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="AU17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" s="6" t="inlineStr"/>
-      <c r="AX17" s="6" t="inlineStr"/>
-      <c r="AY17" s="6" t="inlineStr">
+      <c r="AU22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" s="2" t="inlineStr"/>
+      <c r="AX22" s="2" t="inlineStr"/>
+      <c r="AY22" s="2" t="inlineStr">
         <is>
           <t>PARTNER</t>
         </is>
       </c>
-      <c r="AZ17" s="6" t="n">
+      <c r="AZ22" s="2" t="n">
         <v>40.7136</v>
       </c>
-      <c r="BA17" s="6" t="n">
+      <c r="BA22" s="2" t="n">
         <v>-74.0095</v>
       </c>
-      <c r="BB17" s="6" t="inlineStr"/>
-      <c r="BC17" s="9" t="inlineStr">
+      <c r="BB22" s="2" t="inlineStr"/>
+      <c r="BC22" s="5" t="inlineStr">
         <is>
           <t>Welcome to Tribeca House! 50 Murray Street and 53 Park Place! – Luxury Living in the Heart of
 *Private Terrace*
@@ -4236,210 +5258,210 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>5089734</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5089734</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>50 Murray Street #1550</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>#1550</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>Tribeca</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>10007</t>
         </is>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="H23" s="8" t="n">
         <v>8250</v>
       </c>
-      <c r="I18" s="4" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n">
+      <c r="I23" s="8" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="M18" s="2" t="n">
+      <c r="M23" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="N18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="2" t="n">
+      <c r="N23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="4" t="inlineStr"/>
-      <c r="R18" s="2" t="inlineStr">
+      <c r="P23" s="6" t="inlineStr"/>
+      <c r="Q23" s="8" t="inlineStr"/>
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>Rental unit</t>
         </is>
       </c>
-      <c r="S18" s="2" t="inlineStr">
+      <c r="S23" s="6" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T18" s="2" t="inlineStr">
+      <c r="T23" s="6" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="U18" s="2" t="n">
+      <c r="U23" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V23" s="6" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="W18" s="2" t="inlineStr">
+      <c r="W23" s="6" t="inlineStr">
         <is>
           <t>Balcony; Terrace</t>
         </is>
       </c>
-      <c r="X18" s="2" t="inlineStr">
+      <c r="X23" s="6" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="Y18" s="5" t="inlineStr">
+      <c r="Y23" s="9" t="inlineStr">
         <is>
           <t>Central Ac; Dishwasher; Hardwood Floors; Private Outdoor Space; View</t>
         </is>
       </c>
-      <c r="Z18" s="5" t="inlineStr">
+      <c r="Z23" s="9" t="inlineStr">
         <is>
           <t>Bike Room; Childrens Playroom; Concierge; Doorman; Elevator; Fios Available; Gym; Laundry; Live In Super; Media Room; Package Room; Parking; Shared Outdoor Space; Storage Space; Valet Service</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
+      <c r="AA23" s="6" t="inlineStr">
         <is>
           <t>Full Time</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
+      <c r="AB23" s="6" t="inlineStr">
         <is>
           <t>Garage; Valet</t>
         </is>
       </c>
-      <c r="AC18" s="2" t="inlineStr">
+      <c r="AC23" s="6" t="inlineStr">
         <is>
           <t>Deck; Garden; Patio; Roof Deck</t>
         </is>
       </c>
-      <c r="AD18" s="2" t="inlineStr">
+      <c r="AD23" s="6" t="inlineStr">
         <is>
           <t>Locker Cage</t>
         </is>
       </c>
-      <c r="AE18" s="2" t="inlineStr">
+      <c r="AE23" s="6" t="inlineStr">
         <is>
           <t>Tribeca House</t>
         </is>
       </c>
-      <c r="AF18" s="2" t="n">
+      <c r="AF23" s="6" t="n">
         <v>1964</v>
       </c>
-      <c r="AG18" s="2" t="n">
+      <c r="AG23" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="AH18" s="2" t="n">
+      <c r="AH23" s="6" t="n">
         <v>389</v>
       </c>
-      <c r="AI18" s="2" t="inlineStr">
+      <c r="AI23" s="6" t="inlineStr">
         <is>
           <t>REAL New York</t>
         </is>
       </c>
-      <c r="AJ18" s="2" t="inlineStr">
+      <c r="AJ23" s="6" t="inlineStr">
         <is>
           <t>Real New York</t>
         </is>
       </c>
-      <c r="AK18" s="2" t="inlineStr">
+      <c r="AK23" s="6" t="inlineStr">
         <is>
           <t>Limited Liability Broker</t>
         </is>
       </c>
-      <c r="AL18" s="2" t="inlineStr">
+      <c r="AL23" s="6" t="inlineStr">
         <is>
           <t>29 West 30th Street West 30th Street, 4th Fl, New York, NY, 10001</t>
         </is>
       </c>
-      <c r="AM18" s="2" t="inlineStr">
+      <c r="AM23" s="6" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN18" s="4" t="n">
+      <c r="AN23" s="8" t="n">
         <v>8250</v>
       </c>
-      <c r="AO18" s="5" t="inlineStr">
+      <c r="AO23" s="9" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $8,250</t>
         </is>
       </c>
-      <c r="AP18" s="2" t="inlineStr">
+      <c r="AP23" s="6" t="inlineStr">
         <is>
           <t>2026-07-01: $8,250</t>
         </is>
       </c>
-      <c r="AQ18" s="5" t="inlineStr">
+      <c r="AQ23" s="9" t="inlineStr">
         <is>
           <t>2026-07-01: $8,250 ACTIVE</t>
         </is>
       </c>
-      <c r="AR18" s="4" t="n">
+      <c r="AR23" s="8" t="n">
         <v>16000</v>
       </c>
-      <c r="AS18" s="2" t="inlineStr"/>
-      <c r="AT18" s="2" t="n">
+      <c r="AS23" s="6" t="inlineStr"/>
+      <c r="AT23" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="AU18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" s="2" t="inlineStr"/>
-      <c r="AX18" s="2" t="inlineStr"/>
-      <c r="AY18" s="2" t="inlineStr">
+      <c r="AU23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" s="6" t="inlineStr"/>
+      <c r="AX23" s="6" t="inlineStr"/>
+      <c r="AY23" s="6" t="inlineStr">
         <is>
           <t>PARTNER</t>
         </is>
       </c>
-      <c r="AZ18" s="2" t="n">
+      <c r="AZ23" s="6" t="n">
         <v>40.7136</v>
       </c>
-      <c r="BA18" s="2" t="n">
+      <c r="BA23" s="6" t="n">
         <v>-74.0095</v>
       </c>
-      <c r="BB18" s="2" t="inlineStr"/>
-      <c r="BC18" s="5" t="inlineStr">
+      <c r="BB23" s="6" t="inlineStr"/>
+      <c r="BC23" s="9" t="inlineStr">
         <is>
           <t>Welcome to Tribeca House! 50 Murray Street and 53 Park Place! – Luxury Living in the Heart of Tribeca
 *Private Balcony*
@@ -4464,374 +5486,374 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>5085382</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5085382</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>105 Duane Street #28B</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>#28B</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Tribeca</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>10007</t>
         </is>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="H24" s="4" t="n">
         <v>10375</v>
       </c>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="n">
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M19" s="6" t="n">
+      <c r="M24" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="N19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="6" t="n">
+      <c r="N24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="P19" s="6" t="inlineStr"/>
-      <c r="Q19" s="8" t="inlineStr"/>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="4" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>Rental unit</t>
         </is>
       </c>
-      <c r="S19" s="6" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T19" s="6" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="U19" s="6" t="n">
+      <c r="U24" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="V19" s="6" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="W19" s="6" t="inlineStr">
+      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>Patio</t>
         </is>
       </c>
-      <c r="X19" s="6" t="inlineStr"/>
-      <c r="Y19" s="9" t="inlineStr">
+      <c r="X24" s="2" t="inlineStr"/>
+      <c r="Y24" s="5" t="inlineStr">
         <is>
           <t>Private Outdoor Space</t>
         </is>
       </c>
-      <c r="Z19" s="9" t="inlineStr">
+      <c r="Z24" s="5" t="inlineStr">
         <is>
           <t>Bike Room; Concierge; Doorman; Elevator; Fios Available; Gym; Parking; Pool; Shared Outdoor Space</t>
         </is>
       </c>
-      <c r="AA19" s="6" t="inlineStr"/>
-      <c r="AB19" s="6" t="inlineStr">
+      <c r="AA24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>Garage</t>
         </is>
       </c>
-      <c r="AC19" s="6" t="inlineStr">
+      <c r="AC24" s="2" t="inlineStr">
         <is>
           <t>Garden; Roof Deck</t>
         </is>
       </c>
-      <c r="AD19" s="6" t="inlineStr"/>
-      <c r="AE19" s="6" t="inlineStr">
+      <c r="AD24" s="2" t="inlineStr"/>
+      <c r="AE24" s="2" t="inlineStr">
         <is>
           <t>Tribeca Tower</t>
         </is>
       </c>
-      <c r="AF19" s="6" t="n">
+      <c r="AF24" s="2" t="n">
         <v>1988</v>
       </c>
-      <c r="AG19" s="6" t="n">
+      <c r="AG24" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="AH19" s="6" t="n">
+      <c r="AH24" s="2" t="n">
         <v>440</v>
       </c>
-      <c r="AI19" s="6" t="inlineStr">
+      <c r="AI24" s="2" t="inlineStr">
         <is>
           <t>Related Rentals</t>
         </is>
       </c>
-      <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="6" t="inlineStr"/>
-      <c r="AL19" s="6" t="inlineStr"/>
-      <c r="AM19" s="6" t="inlineStr">
+      <c r="AJ24" s="2" t="inlineStr"/>
+      <c r="AK24" s="2" t="inlineStr"/>
+      <c r="AL24" s="2" t="inlineStr"/>
+      <c r="AM24" s="2" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN19" s="8" t="n"/>
-      <c r="AO19" s="9" t="inlineStr"/>
-      <c r="AP19" s="6" t="inlineStr">
+      <c r="AN24" s="4" t="n"/>
+      <c r="AO24" s="5" t="inlineStr"/>
+      <c r="AP24" s="2" t="inlineStr">
         <is>
           <t>2026-06-26: $10,375</t>
         </is>
       </c>
-      <c r="AQ19" s="9" t="inlineStr">
+      <c r="AQ24" s="5" t="inlineStr">
         <is>
           <t>2026-07-10: $10,375 ACTIVE; 2026-06-29: $10,375 RENTED; 2026-06-26: $10,375 ACTIVE; 2024-12-10: $9,375 RENTED; 2024-12-10: $9,375 ACTIVE; 2022-03-05: $8,350 RENTED; 2022-03-04: $8,350 ACTIVE; 2021-04-14: $7,800 RENTED; 2021-04-13: $7,800 NO_LONGER_AVAILABLE; 2021-04-02: $7,800 RENTED; 2021-03-02: $7,800 ACTIVE; 2020-08-22: $7,895 RENTED; 2020-08-21: $7,895 ACTIVE</t>
         </is>
       </c>
-      <c r="AR19" s="8" t="n">
+      <c r="AR24" s="4" t="n">
         <v>10555</v>
       </c>
-      <c r="AS19" s="6" t="inlineStr"/>
-      <c r="AT19" s="6" t="n">
+      <c r="AS24" s="2" t="inlineStr"/>
+      <c r="AT24" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="AU19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" s="6" t="n">
+      <c r="AU24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AW19" s="6" t="inlineStr"/>
-      <c r="AX19" s="6" t="inlineStr"/>
-      <c r="AY19" s="6" t="inlineStr">
+      <c r="AW24" s="2" t="inlineStr"/>
+      <c r="AX24" s="2" t="inlineStr"/>
+      <c r="AY24" s="2" t="inlineStr">
         <is>
           <t>FEED</t>
         </is>
       </c>
-      <c r="AZ19" s="6" t="n">
+      <c r="AZ24" s="2" t="n">
         <v>40.7158</v>
       </c>
-      <c r="BA19" s="6" t="n">
+      <c r="BA24" s="2" t="n">
         <v>-74.00620000000001</v>
       </c>
-      <c r="BB19" s="6" t="inlineStr"/>
-      <c r="BC19" s="9" t="inlineStr">
+      <c r="BB24" s="2" t="inlineStr"/>
+      <c r="BC24" s="5" t="inlineStr">
         <is>
           <t>Fully renovated Corner 2 Bedroom, 2 Bath with a gourmet windowed pass-through kitchen, floor-to-ceiling windows, solarium dining alcove, spacious closets, strip wood flooring, solar shades, and southwestern exposure.
 If you are looking for pet-friendly Tribeca apartments where art and the art of living are taken seriously, look no further. Tribeca Tower's luxurious rentals are studies in spaciousness, luxury and amenities. Towering fifty-two stories above it all, these Tribeca apartments are situated in one of the city's oldest and most historic neighborhoods. There is an apartment to suit every lifestyle from perfectly appointed pied-a-terre studios to dramatic one and two-bedroom residences, many with spectacular dining solariums featuring stunning floor-to-ceiling windows. Gourmet kitchens with full-sized appliances and white cabinetry, baths with marble top vanities, oak parquet floors and custom closets are sought-after features of these Downtown apartments. Condo-quality amenities include an entertainment lounge, private rooftop sun terrace, indoor swimming pool, and state-of-the art fitness center. The soaring two-story lobby, designed by David Rockwell, is concierge-attended 24/7.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>5096123</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5096123</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>277 Church Street #4</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>Tribeca</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>10013</t>
         </is>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="H25" s="8" t="n">
         <v>12000</v>
       </c>
-      <c r="I20" s="4" t="n"/>
-      <c r="J20" s="2" t="n"/>
-      <c r="K20" s="2" t="n"/>
-      <c r="L20" s="2" t="n">
+      <c r="I25" s="8" t="n"/>
+      <c r="J25" s="6" t="n"/>
+      <c r="K25" s="6" t="n"/>
+      <c r="L25" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="M20" s="2" t="n">
+      <c r="M25" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="N20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="2" t="n">
+      <c r="N25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="P20" s="2" t="n">
+      <c r="P25" s="6" t="n">
         <v>1650</v>
       </c>
-      <c r="Q20" s="4" t="n">
+      <c r="Q25" s="8" t="n">
         <v>87</v>
       </c>
-      <c r="R20" s="2" t="inlineStr">
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>Mixed-use building</t>
         </is>
       </c>
-      <c r="S20" s="2" t="inlineStr">
+      <c r="S25" s="6" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T20" s="2" t="inlineStr">
+      <c r="T25" s="6" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="U20" s="2" t="n">
+      <c r="U25" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V25" s="6" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="W20" s="2" t="inlineStr">
+      <c r="W25" s="6" t="inlineStr">
         <is>
           <t>Private Roof Deck</t>
         </is>
       </c>
-      <c r="X20" s="2" t="inlineStr">
+      <c r="X25" s="6" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="Y20" s="5" t="inlineStr">
+      <c r="Y25" s="9" t="inlineStr">
         <is>
           <t>Central Ac; Dishwasher; Hardwood Floors; Private Outdoor Space; View; Washer Dryer</t>
         </is>
       </c>
-      <c r="Z20" s="5" t="inlineStr">
+      <c r="Z25" s="9" t="inlineStr">
         <is>
           <t>Fios Available</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr"/>
-      <c r="AB20" s="2" t="inlineStr"/>
-      <c r="AC20" s="2" t="inlineStr"/>
-      <c r="AD20" s="2" t="inlineStr"/>
-      <c r="AE20" s="2" t="inlineStr"/>
-      <c r="AF20" s="2" t="n">
+      <c r="AA25" s="6" t="inlineStr"/>
+      <c r="AB25" s="6" t="inlineStr"/>
+      <c r="AC25" s="6" t="inlineStr"/>
+      <c r="AD25" s="6" t="inlineStr"/>
+      <c r="AE25" s="6" t="inlineStr"/>
+      <c r="AF25" s="6" t="n">
         <v>1910</v>
       </c>
-      <c r="AG20" s="2" t="n">
+      <c r="AG25" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="AH20" s="2" t="n">
+      <c r="AH25" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="AI20" s="2" t="inlineStr">
+      <c r="AI25" s="6" t="inlineStr">
         <is>
           <t>Corcoran</t>
         </is>
       </c>
-      <c r="AJ20" s="2" t="inlineStr">
+      <c r="AJ25" s="6" t="inlineStr">
         <is>
           <t>Corcoran Group</t>
         </is>
       </c>
-      <c r="AK20" s="2" t="inlineStr">
+      <c r="AK25" s="6" t="inlineStr">
         <is>
           <t>Limited Liability Broker</t>
         </is>
       </c>
-      <c r="AL20" s="2" t="inlineStr">
+      <c r="AL25" s="6" t="inlineStr">
         <is>
           <t>590 Madison Avenue, New York, NY, 10022</t>
         </is>
       </c>
-      <c r="AM20" s="2" t="inlineStr">
+      <c r="AM25" s="6" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN20" s="4" t="n">
+      <c r="AN25" s="8" t="n">
         <v>12000</v>
       </c>
-      <c r="AO20" s="5" t="inlineStr">
+      <c r="AO25" s="9" t="inlineStr">
         <is>
           <t>Application fee: $0; Security deposit: $12,000; Credit check: $20</t>
         </is>
       </c>
-      <c r="AP20" s="2" t="inlineStr">
+      <c r="AP25" s="6" t="inlineStr">
         <is>
           <t>2026-07-08: $12,000</t>
         </is>
       </c>
-      <c r="AQ20" s="5" t="inlineStr">
+      <c r="AQ25" s="9" t="inlineStr">
         <is>
           <t>2026-07-08: $12,000 ACTIVE; 2019-07-31: $8,000 RENTED; 2019-07-02: $8,000 None; 2019-05-20: $8,200 None; 2019-05-01: $8,500 ACTIVE</t>
         </is>
       </c>
-      <c r="AR20" s="4" t="n">
+      <c r="AR25" s="8" t="n">
         <v>10555</v>
       </c>
-      <c r="AS20" s="2" t="inlineStr"/>
-      <c r="AT20" s="2" t="n">
+      <c r="AS25" s="6" t="inlineStr"/>
+      <c r="AT25" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="AU20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" s="2" t="n">
+      <c r="AU25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="AW20" s="2" t="inlineStr"/>
-      <c r="AX20" s="2" t="inlineStr"/>
-      <c r="AY20" s="2" t="inlineStr">
+      <c r="AW25" s="6" t="inlineStr"/>
+      <c r="AX25" s="6" t="inlineStr"/>
+      <c r="AY25" s="6" t="inlineStr">
         <is>
           <t>PARTNER</t>
         </is>
       </c>
-      <c r="AZ20" s="2" t="n">
+      <c r="AZ25" s="6" t="n">
         <v>40.718533</v>
       </c>
-      <c r="BA20" s="2" t="n">
+      <c r="BA25" s="6" t="n">
         <v>-74.00476999999999</v>
       </c>
-      <c r="BB20" s="2" t="inlineStr"/>
-      <c r="BC20" s="5" t="inlineStr">
+      <c r="BB25" s="6" t="inlineStr"/>
+      <c r="BC25" s="9" t="inlineStr">
         <is>
           <t>A sun-filled two-bedroom, two-bathroom loft with a private roof deck and two skylights, set on a classic cast-iron block at 277 Church Street in the heart of Tribeca, New York. This is a home defined by light, scale, and outdoor space, a rare full-floor rental where sky and city are part of the everyday.
 Enter into an expansive open living and dining great room, crowned by an overhead skylight and warmed by an original exposed-brick wall. Oversized windows frame downtown rooftop views, soaring ceilings lift the space, and pale maple hardwood floors run throughout. The living room flows directly into a generous kitchen, outfitted with natural maple cabinetry, stainless steel appliances, a gas range, dishwasher, and a central island with breakfast-bar seating, the natural gathering point of the home.
@@ -4842,194 +5864,407 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>5096543</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>https://streeteasy.com/rental/5096543</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>315 Greenwich Street #4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Tribeca</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>10013</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="4" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>Mixed-use building</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>Roof Rights</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>City; Garden; Park; Skyline; Water</t>
+        </is>
+      </c>
+      <c r="Y26" s="5" t="inlineStr">
+        <is>
+          <t>Central Ac; Dishwasher; Hardwood Floors; Private Outdoor Space; View; Washer Dryer</t>
+        </is>
+      </c>
+      <c r="Z26" s="5" t="inlineStr">
+        <is>
+          <t>Elevator; Fios Available; Laundry</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr"/>
+      <c r="AE26" s="2" t="inlineStr"/>
+      <c r="AF26" s="2" t="n">
+        <v>1930</v>
+      </c>
+      <c r="AG26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI26" s="2" t="inlineStr">
+        <is>
+          <t>The Leasing Office</t>
+        </is>
+      </c>
+      <c r="AJ26" s="2" t="inlineStr">
+        <is>
+          <t>The Leasing Office</t>
+        </is>
+      </c>
+      <c r="AK26" s="2" t="inlineStr">
+        <is>
+          <t>Real Estate Principal Office</t>
+        </is>
+      </c>
+      <c r="AL26" s="2" t="inlineStr">
+        <is>
+          <t>310 Riverside Dr, Suite 200b, New York, NY, 10025</t>
+        </is>
+      </c>
+      <c r="AM26" s="2" t="inlineStr">
+        <is>
+          <t>None listed</t>
+        </is>
+      </c>
+      <c r="AN26" s="4" t="n">
+        <v>12000</v>
+      </c>
+      <c r="AO26" s="5" t="inlineStr">
+        <is>
+          <t>Application fee: $20; Security deposit: $12,000</t>
+        </is>
+      </c>
+      <c r="AP26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08: $12,000</t>
+        </is>
+      </c>
+      <c r="AQ26" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-09: $12,000 ACTIVE; 2021-02-05: $4,875 RENTED; 2021-01-25: $4,875 None; 2021-01-19: $5,075 None; 2021-01-11: $5,125 None; 2020-12-09: $4,975 None; 2020-11-30: $4,950 None; 2020-11-22: $4,995 None; 2020-11-17: $5,295 ACTIVE; 2019-08-19: $5,495 RENTED; 2019-07-26: $5,495 None; 2019-06-18: $5,595 ACTIVE; 2015-07-10: $5,650 RENTED; 2015-07-09: $5,650 NO_LONGER_AVAILABLE; 2015-06-15: $5,650 IN_CONTRACT; 2015-04-27: $5,650 ACTIVE; 2013-05-17: $5,500 RENTED; 2013-05-15: $5,500 IN_CONTRACT; 2013-05-15: $5,500 RENTED; 2013-05-08: $5,500 None; 2013-04-10: $5,700 None; 2013-03-26: $5,500 None; 2013-03-21: $5,900 None; 2013-02-11: $6,000 ACTIVE</t>
+        </is>
+      </c>
+      <c r="AR26" s="4" t="n">
+        <v>16000</v>
+      </c>
+      <c r="AS26" s="2" t="inlineStr"/>
+      <c r="AT26" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" s="2" t="inlineStr"/>
+      <c r="AX26" s="2" t="inlineStr"/>
+      <c r="AY26" s="2" t="inlineStr">
+        <is>
+          <t>PARTNER</t>
+        </is>
+      </c>
+      <c r="AZ26" s="2" t="n">
+        <v>40.716938</v>
+      </c>
+      <c r="BA26" s="2" t="n">
+        <v>-74.01052</v>
+      </c>
+      <c r="BB26" s="2" t="inlineStr"/>
+      <c r="BC26" s="5" t="inlineStr">
+        <is>
+          <t>✨ LUXURY TRIBECA PENTHOUSE — IN-UNIT WASHER/DRYER, PRIVATE STORAGE &amp; STUNNING CITY VIEWS! ✨
+Experience luxury living in this exceptional penthouse residence in the heart of Tribeca. Offering an expansive 3-bedroom, 2-bathroom layout, premium finishes, breathtaking city views, and a dedicated private storage unit, this home is designed for those seeking the very best of Manhattan living.
+Flooded with natural light through floor-to-ceiling windows, the open-concept living and dining area is perfect for entertaining or relaxing in style. The chef's kitchen features stainless steel appliances, granite countertops, and abundant cabinet space, while the spacious primary suite offers a walk-in closet and a luxurious en-suite bathroom.
+✅ Apartment Features:
+✔️ Penthouse Residence
+✔️ True 3-Bedroom, 2-Bathroom Layout
+✔️ Floor-to-Ceiling Windows
+✔️ In-Unit Washer &amp; Dryer
+✔️ Dedicated Private Storage Unit Included
+✔️ Open-Concept Living &amp; Dining Area
+✔️ Chef's Kitchen with Stainless Steel Appliances
+✔️ Granite Countertops
+✔️ Spacious Primary Suite with Walk-In Closet
+✔️ Spa-Inspired En-Suite Bathroom
+✔️ Two Additional Generously Sized Bedrooms
+✔️ High Ceilings Throughout
+✅ Building Amenities:
+✔️ Rooftop Deck
+✔️ Pet-Friendly Building
+✔️ Well-Maintained Luxury Property
+✅ Prime Tribeca Location:
+Perfectly situated in one of Manhattan's most prestigious neighborhoods, just moments from Hudson River Park, world-renowned restaurants, boutique shopping, art galleries, and multiple subway lines. Experience the best of downtown living with everything you need just outside your door.
+Please note: Tenant occupied unit, showings strictly by appointment.
+☎️ Call, email, or inquire today to schedule a viewing. Open house is by appointment only. 
+Disclaimer: Some images may be digitally edited. Furniture and décor may appear for illustrative purposes only. Photos ARE of the actual apartment, NOT a similar unit. Prospective renters are responsible to independently verify all information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>5074300</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5074300</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>83 Warren Street #5</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>Tribeca</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>10007</t>
         </is>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H27" s="8" t="n">
         <v>16500</v>
       </c>
-      <c r="I21" s="8" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="6" t="n">
+      <c r="I27" s="8" t="n"/>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="6" t="n"/>
+      <c r="L27" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="M21" s="6" t="n">
+      <c r="M27" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="N27" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O21" s="6" t="n">
+      <c r="O27" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="P21" s="6" t="inlineStr"/>
-      <c r="Q21" s="8" t="inlineStr"/>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="P27" s="6" t="inlineStr"/>
+      <c r="Q27" s="8" t="inlineStr"/>
+      <c r="R27" s="6" t="inlineStr">
         <is>
           <t>Multifamily home</t>
         </is>
       </c>
-      <c r="S21" s="6" t="inlineStr">
+      <c r="S27" s="6" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T21" s="6" t="inlineStr">
+      <c r="T27" s="6" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="U21" s="6" t="n">
+      <c r="U27" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="V21" s="6" t="inlineStr">
+      <c r="V27" s="6" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="W21" s="6" t="inlineStr">
+      <c r="W27" s="6" t="inlineStr">
         <is>
           <t>Private Roof Deck</t>
         </is>
       </c>
-      <c r="X21" s="6" t="inlineStr">
+      <c r="X27" s="6" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="Y21" s="9" t="inlineStr">
+      <c r="Y27" s="9" t="inlineStr">
         <is>
           <t>Dishwasher; Private Outdoor Space; View; Washer Dryer</t>
         </is>
       </c>
-      <c r="Z21" s="9" t="inlineStr">
+      <c r="Z27" s="9" t="inlineStr">
         <is>
           <t>Bike Room; Fios Available; Shared Outdoor Space</t>
         </is>
       </c>
-      <c r="AA21" s="6" t="inlineStr"/>
-      <c r="AB21" s="6" t="inlineStr"/>
-      <c r="AC21" s="6" t="inlineStr">
+      <c r="AA27" s="6" t="inlineStr"/>
+      <c r="AB27" s="6" t="inlineStr"/>
+      <c r="AC27" s="6" t="inlineStr">
         <is>
           <t>Roof Deck</t>
         </is>
       </c>
-      <c r="AD21" s="6" t="inlineStr"/>
-      <c r="AE21" s="6" t="inlineStr"/>
-      <c r="AF21" s="6" t="n">
+      <c r="AD27" s="6" t="inlineStr"/>
+      <c r="AE27" s="6" t="inlineStr"/>
+      <c r="AF27" s="6" t="n">
         <v>1920</v>
       </c>
-      <c r="AG21" s="6" t="n">
+      <c r="AG27" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="AH21" s="6" t="n">
+      <c r="AH27" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="AI21" s="6" t="inlineStr">
+      <c r="AI27" s="6" t="inlineStr">
         <is>
           <t>City Wide Apartments</t>
         </is>
       </c>
-      <c r="AJ21" s="6" t="inlineStr">
+      <c r="AJ27" s="6" t="inlineStr">
         <is>
           <t>City Wide Apartments Inc</t>
         </is>
       </c>
-      <c r="AK21" s="6" t="inlineStr">
+      <c r="AK27" s="6" t="inlineStr">
         <is>
           <t>Corporate Broker</t>
         </is>
       </c>
-      <c r="AL21" s="6" t="inlineStr">
+      <c r="AL27" s="6" t="inlineStr">
         <is>
           <t>555 8th Avenue Ste, 2310, New York, NY, 10018</t>
         </is>
       </c>
-      <c r="AM21" s="6" t="inlineStr">
+      <c r="AM27" s="6" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN21" s="8" t="n">
+      <c r="AN27" s="8" t="n">
         <v>16500</v>
       </c>
-      <c r="AO21" s="9" t="inlineStr">
+      <c r="AO27" s="9" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $16,500</t>
         </is>
       </c>
-      <c r="AP21" s="6" t="inlineStr">
+      <c r="AP27" s="6" t="inlineStr">
         <is>
           <t>2026-06-16: $17,500; 2026-07-07: $16,500</t>
         </is>
       </c>
-      <c r="AQ21" s="9" t="inlineStr">
+      <c r="AQ27" s="9" t="inlineStr">
         <is>
           <t>2026-07-07: $16,500 None; 2026-06-16: $17,500 ACTIVE; 2024-08-29: $16,500 RENTED; 2024-08-26: $16,500 ACTIVE</t>
         </is>
       </c>
-      <c r="AR21" s="8" t="n">
+      <c r="AR27" s="8" t="n">
         <v>16000</v>
       </c>
-      <c r="AS21" s="6" t="inlineStr"/>
-      <c r="AT21" s="6" t="n">
+      <c r="AS27" s="6" t="inlineStr"/>
+      <c r="AT27" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="AU21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" s="6" t="inlineStr"/>
-      <c r="AX21" s="6" t="inlineStr"/>
-      <c r="AY21" s="6" t="inlineStr">
+      <c r="AU27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" s="6" t="inlineStr"/>
+      <c r="AX27" s="6" t="inlineStr"/>
+      <c r="AY27" s="6" t="inlineStr">
         <is>
           <t>PARTNER</t>
         </is>
       </c>
-      <c r="AZ21" s="6" t="n">
+      <c r="AZ27" s="6" t="n">
         <v>40.71515</v>
       </c>
-      <c r="BA21" s="6" t="n">
+      <c r="BA27" s="6" t="n">
         <v>-74.010605</v>
       </c>
-      <c r="BB21" s="6" t="inlineStr"/>
-      <c r="BC21" s="9" t="inlineStr">
+      <c r="BB27" s="6" t="inlineStr"/>
+      <c r="BC27" s="9" t="inlineStr">
         <is>
           <t>For Rent: Exquisite Top-Floor Penthouse Loft with Private Roof Deck in Prime Tribeca
 Step into luxury with this stunning top-floor penthouse loft in the heart of Tribeca. Newly renovated and designed with modern elegance, this 3-bedroom gem offers a perfect blend of sophistication and urban convenience. Just moments from the Chambers Street subway stop, you’ll enjoy effortless access to all that New York City has to offer.
@@ -5047,180 +6282,180 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>5072794</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5072794</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>311 11th Avenue #2216</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>#2216</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>West Chelsea</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>10001</t>
         </is>
       </c>
-      <c r="H22" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>9395</v>
       </c>
-      <c r="I22" s="4" t="n"/>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="2" t="n"/>
-      <c r="L22" s="2" t="n">
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M22" s="2" t="n">
+      <c r="M28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="2" t="n">
+      <c r="N28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P22" s="2" t="inlineStr"/>
-      <c r="Q22" s="4" t="inlineStr"/>
-      <c r="R22" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="4" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>Rental unit</t>
         </is>
       </c>
-      <c r="S22" s="2" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T22" s="2" t="inlineStr">
+      <c r="T28" s="2" t="inlineStr">
         <is>
           <t>2026-06-14</t>
         </is>
       </c>
-      <c r="U22" s="2" t="n">
+      <c r="U28" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="W22" s="2" t="inlineStr">
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t>Garden; Terrace</t>
         </is>
       </c>
-      <c r="X22" s="2" t="inlineStr"/>
-      <c r="Y22" s="5" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr"/>
+      <c r="Y28" s="5" t="inlineStr">
         <is>
           <t>Dishwasher; Private Outdoor Space; Washer Dryer</t>
         </is>
       </c>
-      <c r="Z22" s="5" t="inlineStr">
+      <c r="Z28" s="5" t="inlineStr">
         <is>
           <t>Bike Room; Concierge; Doorman; Elevator; Fios Available; Gym; Laundry; Live In Super; Media Room; Package Room; Pool; Shared Outdoor Space; Storage Space</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr"/>
-      <c r="AB22" s="2" t="inlineStr"/>
-      <c r="AC22" s="2" t="inlineStr">
+      <c r="AA28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
         <is>
           <t>Deck; Garden; Patio; Roof Deck</t>
         </is>
       </c>
-      <c r="AD22" s="2" t="inlineStr"/>
-      <c r="AE22" s="2" t="inlineStr">
+      <c r="AD28" s="2" t="inlineStr"/>
+      <c r="AE28" s="2" t="inlineStr">
         <is>
           <t>3 Eleven</t>
         </is>
       </c>
-      <c r="AF22" s="2" t="n">
+      <c r="AF28" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="AG22" s="2" t="n">
+      <c r="AG28" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="AH22" s="2" t="n">
+      <c r="AH28" s="2" t="n">
         <v>938</v>
       </c>
-      <c r="AI22" s="2" t="inlineStr">
+      <c r="AI28" s="2" t="inlineStr">
         <is>
           <t>Clinton Management</t>
         </is>
       </c>
-      <c r="AJ22" s="2" t="inlineStr"/>
-      <c r="AK22" s="2" t="inlineStr"/>
-      <c r="AL22" s="2" t="inlineStr"/>
-      <c r="AM22" s="2" t="inlineStr">
+      <c r="AJ28" s="2" t="inlineStr"/>
+      <c r="AK28" s="2" t="inlineStr"/>
+      <c r="AL28" s="2" t="inlineStr"/>
+      <c r="AM28" s="2" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN22" s="4" t="n"/>
-      <c r="AO22" s="5" t="inlineStr"/>
-      <c r="AP22" s="2" t="inlineStr">
+      <c r="AN28" s="4" t="n"/>
+      <c r="AO28" s="5" t="inlineStr"/>
+      <c r="AP28" s="2" t="inlineStr">
         <is>
           <t>2026-06-14: $9,395</t>
         </is>
       </c>
-      <c r="AQ22" s="5" t="inlineStr">
+      <c r="AQ28" s="5" t="inlineStr">
         <is>
           <t>2026-06-14: $9,395 ACTIVE</t>
         </is>
       </c>
-      <c r="AR22" s="4" t="n">
+      <c r="AR28" s="4" t="n">
         <v>8802</v>
       </c>
-      <c r="AS22" s="2" t="inlineStr">
+      <c r="AS28" s="2" t="inlineStr">
         <is>
           <t>{'id': '20952234', 'startTime': '2026-07-14T11:00:00.000-04:00', 'endTime': '2026-07-14T14:00:00.000-04:00', 'appointmentOnly': True, 'showingNotes': None}; {'id': '20957571', 'startTime': '2026-07-16T11:00:00.000-04:00', 'endTime': '2026-07-16T14:00:00.000-04:00', 'appointmentOnly': True, 'showingNotes': None}; {'id': '20968079', 'startTime': '2026-07-21T11:00:00.000-04:00', 'endTime': '2026-07-21T14:00:00.000-04:00', 'appointmentOnly': True, 'showingNotes': None}; {'id': '20976091', 'startTime': '2026-07-23T11:00:00.000-04:00', 'endTime': '2026-07-23T14:00:00.000-04:00', 'appointmentOnly': True, 'showingNotes': None}</t>
         </is>
       </c>
-      <c r="AT22" s="2" t="n">
+      <c r="AT28" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="AU22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" s="2" t="n">
+      <c r="AU28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AW22" s="2" t="inlineStr"/>
-      <c r="AX22" s="2" t="inlineStr"/>
-      <c r="AY22" s="2" t="inlineStr">
+      <c r="AW28" s="2" t="inlineStr"/>
+      <c r="AX28" s="2" t="inlineStr"/>
+      <c r="AY28" s="2" t="inlineStr">
         <is>
           <t>FEED</t>
         </is>
       </c>
-      <c r="AZ22" s="2" t="n">
+      <c r="AZ28" s="2" t="n">
         <v>40.753277</v>
       </c>
-      <c r="BA22" s="2" t="n">
+      <c r="BA28" s="2" t="n">
         <v>-74.00423000000001</v>
       </c>
-      <c r="BB22" s="2" t="inlineStr"/>
-      <c r="BC22" s="5" t="inlineStr">
+      <c r="BB28" s="2" t="inlineStr"/>
+      <c r="BC28" s="5" t="inlineStr">
         <is>
           <t>3 ELEVEN - CORNER TWO BEDROOM - PERFECT FOR ENTERTAINING!
 Reduced security deposits for highly qualified applicants only.
@@ -5255,550 +6490,550 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>5099749</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5099749</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>535 West 23rd Street #S9C</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>#S9C</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>West Chelsea</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>10011</t>
         </is>
       </c>
-      <c r="H23" s="8" t="n">
+      <c r="H29" s="8" t="n">
         <v>9650</v>
       </c>
-      <c r="I23" s="8" t="n"/>
-      <c r="J23" s="6" t="n"/>
-      <c r="K23" s="6" t="n"/>
-      <c r="L23" s="6" t="n">
+      <c r="I29" s="8" t="n"/>
+      <c r="J29" s="6" t="n"/>
+      <c r="K29" s="6" t="n"/>
+      <c r="L29" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="M23" s="6" t="n">
+      <c r="M29" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="N23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="6" t="n">
+      <c r="N29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="6" t="inlineStr"/>
-      <c r="Q23" s="8" t="inlineStr"/>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="P29" s="6" t="inlineStr"/>
+      <c r="Q29" s="8" t="inlineStr"/>
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>Rental unit</t>
         </is>
       </c>
-      <c r="S23" s="6" t="inlineStr">
+      <c r="S29" s="6" t="inlineStr">
         <is>
           <t>RENTED</t>
         </is>
       </c>
-      <c r="T23" s="6" t="inlineStr">
+      <c r="T29" s="6" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="U23" s="6" t="n">
+      <c r="U29" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="V23" s="6" t="inlineStr">
+      <c r="V29" s="6" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="W23" s="6" t="inlineStr">
+      <c r="W29" s="6" t="inlineStr">
         <is>
           <t>Patio</t>
         </is>
       </c>
-      <c r="X23" s="6" t="inlineStr"/>
-      <c r="Y23" s="9" t="inlineStr">
+      <c r="X29" s="6" t="inlineStr"/>
+      <c r="Y29" s="9" t="inlineStr">
         <is>
           <t>Private Outdoor Space</t>
         </is>
       </c>
-      <c r="Z23" s="9" t="inlineStr">
+      <c r="Z29" s="9" t="inlineStr">
         <is>
           <t>Bike Room; Concierge; Doorman; Elevator; Fios Available; Gym; Laundry; Live In Super; Shared Outdoor Space</t>
         </is>
       </c>
-      <c r="AA23" s="6" t="inlineStr"/>
-      <c r="AB23" s="6" t="inlineStr"/>
-      <c r="AC23" s="6" t="inlineStr">
+      <c r="AA29" s="6" t="inlineStr"/>
+      <c r="AB29" s="6" t="inlineStr"/>
+      <c r="AC29" s="6" t="inlineStr">
         <is>
           <t>Garden; Roof Deck</t>
         </is>
       </c>
-      <c r="AD23" s="6" t="inlineStr"/>
-      <c r="AE23" s="6" t="inlineStr">
+      <c r="AD29" s="6" t="inlineStr"/>
+      <c r="AE29" s="6" t="inlineStr">
         <is>
           <t>The Tate</t>
         </is>
       </c>
-      <c r="AF23" s="6" t="n">
+      <c r="AF29" s="6" t="n">
         <v>2001</v>
       </c>
-      <c r="AG23" s="6" t="n">
+      <c r="AG29" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="AH23" s="6" t="n">
+      <c r="AH29" s="6" t="n">
         <v>313</v>
       </c>
-      <c r="AI23" s="6" t="inlineStr">
+      <c r="AI29" s="6" t="inlineStr">
         <is>
           <t>Related Rentals</t>
         </is>
       </c>
-      <c r="AJ23" s="6" t="inlineStr"/>
-      <c r="AK23" s="6" t="inlineStr"/>
-      <c r="AL23" s="6" t="inlineStr"/>
-      <c r="AM23" s="6" t="inlineStr">
+      <c r="AJ29" s="6" t="inlineStr"/>
+      <c r="AK29" s="6" t="inlineStr"/>
+      <c r="AL29" s="6" t="inlineStr"/>
+      <c r="AM29" s="6" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN23" s="8" t="n"/>
-      <c r="AO23" s="9" t="inlineStr"/>
-      <c r="AP23" s="6" t="inlineStr">
+      <c r="AN29" s="8" t="n"/>
+      <c r="AO29" s="9" t="inlineStr"/>
+      <c r="AP29" s="6" t="inlineStr">
         <is>
           <t>2026-07-11: $9,650</t>
         </is>
       </c>
-      <c r="AQ23" s="9" t="inlineStr">
+      <c r="AQ29" s="9" t="inlineStr">
         <is>
           <t>2026-07-12: $9,650 RENTED; 2026-07-11: $9,650 ACTIVE; 2023-05-20: $8,500 RENTED; 2023-05-20: $8,500 ACTIVE; 2021-06-14: $6,875 RENTED; 2021-06-11: $6,875 ACTIVE; 2021-06-05: $6,875 RENTED; 2021-06-05: $6,875 ACTIVE; 2018-05-30: $6,235 NO_LONGER_AVAILABLE; 2018-04-17: $6,235 ACTIVE; 2013-10-03: $7,000 NO_LONGER_AVAILABLE; 2013-08-28: $7,000 ACTIVE</t>
         </is>
       </c>
-      <c r="AR23" s="8" t="n">
+      <c r="AR29" s="8" t="n">
         <v>8802</v>
       </c>
-      <c r="AS23" s="6" t="inlineStr"/>
-      <c r="AT23" s="6" t="n">
+      <c r="AS29" s="6" t="inlineStr"/>
+      <c r="AT29" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="AU23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV23" s="6" t="n">
+      <c r="AU29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="AW23" s="6" t="inlineStr"/>
-      <c r="AX23" s="6" t="inlineStr"/>
-      <c r="AY23" s="6" t="inlineStr">
+      <c r="AW29" s="6" t="inlineStr"/>
+      <c r="AX29" s="6" t="inlineStr"/>
+      <c r="AY29" s="6" t="inlineStr">
         <is>
           <t>FEED</t>
         </is>
       </c>
-      <c r="AZ23" s="6" t="n">
+      <c r="AZ29" s="6" t="n">
         <v>40.7485</v>
       </c>
-      <c r="BA23" s="6" t="n">
+      <c r="BA29" s="6" t="n">
         <v>-74.00530000000001</v>
       </c>
-      <c r="BB23" s="6" t="inlineStr"/>
-      <c r="BC23" s="9" t="inlineStr">
+      <c r="BB29" s="6" t="inlineStr"/>
+      <c r="BC29" s="9" t="inlineStr">
         <is>
           <t>Beautiful 2 Bedroom, 2 Bath featuring walk-in closets, a pass-through kitchen, an in-home washer/dryer, upgraded strip wood floors, solar shades and northern exposure with courtyard views.
 The Tate welcomes residents home to the ultimate Chelsea apartment building. These luxury NYC rental apartments, designed by Rockwell Group to have a powerful and immediate connection to nature, feature a lobby with sunlit bamboo trees, rich limestone floors, and windowed elevator lobbies overlooking a serene courtyard garden. The Tate offers beautifully proportioned studio, one and two-bedroom apartments featuring gourmet kitchens with granite countertops, stone tile baths, oak parquet floors, large windows, customized closet space and washer/dryer in each home. With its bold take on luxury and attention to detail, The Tate is located in the heart of the gallery district, one of Manhattan's most vibrant and exciting neighborhoods.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>5086520</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5086520</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>450 West 17th Street #542</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>#542</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>West Chelsea</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>10011</t>
         </is>
       </c>
-      <c r="H24" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <v>12595</v>
       </c>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="n"/>
-      <c r="L24" s="2" t="n">
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M24" s="2" t="n">
+      <c r="M30" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="N24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="2" t="n">
+      <c r="N30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P24" s="2" t="inlineStr"/>
-      <c r="Q24" s="4" t="inlineStr"/>
-      <c r="R24" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="4" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="S24" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T24" s="2" t="inlineStr">
+      <c r="T30" s="2" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="U24" s="2" t="n">
+      <c r="U30" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="W24" s="2" t="inlineStr">
+      <c r="W30" s="2" t="inlineStr">
         <is>
           <t>Patio</t>
         </is>
       </c>
-      <c r="X24" s="2" t="inlineStr"/>
-      <c r="Y24" s="5" t="inlineStr">
+      <c r="X30" s="2" t="inlineStr"/>
+      <c r="Y30" s="5" t="inlineStr">
         <is>
           <t>Private Outdoor Space</t>
         </is>
       </c>
-      <c r="Z24" s="5" t="inlineStr">
+      <c r="Z30" s="5" t="inlineStr">
         <is>
           <t>Bike Room; Childrens Playroom; Concierge; Doorman; Elevator; Fios Available; Gym; Laundry; Live In Super; Parking; Shared Outdoor Space; Storage Space</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
+      <c r="AA30" s="2" t="inlineStr">
         <is>
           <t>Full Time</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
+      <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>Garage</t>
         </is>
       </c>
-      <c r="AC24" s="2" t="inlineStr">
+      <c r="AC30" s="2" t="inlineStr">
         <is>
           <t>Garden; Roof Deck</t>
         </is>
       </c>
-      <c r="AD24" s="2" t="inlineStr"/>
-      <c r="AE24" s="2" t="inlineStr">
+      <c r="AD30" s="2" t="inlineStr"/>
+      <c r="AE30" s="2" t="inlineStr">
         <is>
           <t>The Caledonia</t>
         </is>
       </c>
-      <c r="AF24" s="2" t="n">
+      <c r="AF30" s="2" t="n">
         <v>2006</v>
       </c>
-      <c r="AG24" s="2" t="n">
+      <c r="AG30" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="AH24" s="2" t="n">
+      <c r="AH30" s="2" t="n">
         <v>469</v>
       </c>
-      <c r="AI24" s="2" t="inlineStr">
+      <c r="AI30" s="2" t="inlineStr">
         <is>
           <t>Related Rentals</t>
         </is>
       </c>
-      <c r="AJ24" s="2" t="inlineStr"/>
-      <c r="AK24" s="2" t="inlineStr"/>
-      <c r="AL24" s="2" t="inlineStr"/>
-      <c r="AM24" s="2" t="inlineStr">
+      <c r="AJ30" s="2" t="inlineStr"/>
+      <c r="AK30" s="2" t="inlineStr"/>
+      <c r="AL30" s="2" t="inlineStr"/>
+      <c r="AM30" s="2" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN24" s="4" t="n"/>
-      <c r="AO24" s="5" t="inlineStr"/>
-      <c r="AP24" s="2" t="inlineStr">
+      <c r="AN30" s="4" t="n"/>
+      <c r="AO30" s="5" t="inlineStr"/>
+      <c r="AP30" s="2" t="inlineStr">
         <is>
           <t>2026-06-29: $12,595</t>
         </is>
       </c>
-      <c r="AQ24" s="5" t="inlineStr">
+      <c r="AQ30" s="5" t="inlineStr">
         <is>
           <t>2026-07-11: $12,595 ACTIVE; 2026-07-02: $12,595 RENTED; 2026-06-29: $12,595 ACTIVE; 2022-12-16: $9,963 RENTED; 2022-12-15: $9,963 IN_CONTRACT; 2022-11-14: $9,963 ACTIVE; 2021-07-16: $9,895 RENTED; 2021-07-15: $9,895 NO_LONGER_AVAILABLE; 2021-07-01: $9,895 ACTIVE; 2021-06-29: $9,895 RENTED; 2021-06-25: $9,895 None; 2021-06-25: $9,895 ACTIVE; 2021-06-13: $9,815 RENTED; 2021-06-12: $9,815 ACTIVE</t>
         </is>
       </c>
-      <c r="AR24" s="4" t="n">
+      <c r="AR30" s="4" t="n">
         <v>8802</v>
       </c>
-      <c r="AS24" s="2" t="inlineStr"/>
-      <c r="AT24" s="2" t="n">
+      <c r="AS30" s="2" t="inlineStr"/>
+      <c r="AT30" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="AU24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV24" s="2" t="n">
+      <c r="AU30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AW24" s="2" t="inlineStr"/>
-      <c r="AX24" s="2" t="inlineStr"/>
-      <c r="AY24" s="2" t="inlineStr">
+      <c r="AW30" s="2" t="inlineStr"/>
+      <c r="AX30" s="2" t="inlineStr"/>
+      <c r="AY30" s="2" t="inlineStr">
         <is>
           <t>FEED</t>
         </is>
       </c>
-      <c r="AZ24" s="2" t="n">
+      <c r="AZ30" s="2" t="n">
         <v>40.7435</v>
       </c>
-      <c r="BA24" s="2" t="n">
+      <c r="BA30" s="2" t="n">
         <v>-74.0064</v>
       </c>
-      <c r="BB24" s="2" t="inlineStr"/>
-      <c r="BC24" s="5" t="inlineStr">
+      <c r="BB30" s="2" t="inlineStr"/>
+      <c r="BC30" s="5" t="inlineStr">
         <is>
           <t>Beautiful Corner 2 Bedroom, 2 Bath with a gourmet open kitchen, walk-in closet, oversized windows, in-home washer/dryer, upgraded strip wood flooring, oversized private terrace and northern and western exposures with views of the Highline.This apartment is a lease break and is available to new residents only.
 The hottest Chelsea apartment rentals are located adjacent to the High Line, New York's most unique and exciting urban park. This pet-friendly Manhattan apartment building features custom designed studio, one, two and three-bedroom flats. The Caledonia brings the perfect balance of energy and serenity to the middle of the hottest Manhattan neighborhoods: West Chelsea and the Meatpacking District. Situated at the nexus of West Chelsea, Gansevoort Street and the Meatpacking District, this luxurious New York City rental building represents a new and exciting style of living in a historic downtown location. Developed by industry leaders, Related Companies and Taconic Investment Partners, The Caledonia offers exquisite apartments giving renters the unique opportunity to experience unprecedented services and amenities including the first fully integrated Equinox Fitness Club within a residential tower. Chelsea apartments have never been so grand and luxurious as they are at The Caledonia, one of the finest apartment buildings in all of Manhattan.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>5066572</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5066572</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>562 Hudson Street #2</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>West Village</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>10014</t>
         </is>
       </c>
-      <c r="H25" s="8" t="n">
+      <c r="H31" s="8" t="n">
         <v>8995</v>
       </c>
-      <c r="I25" s="8" t="n"/>
-      <c r="J25" s="6" t="n"/>
-      <c r="K25" s="6" t="n"/>
-      <c r="L25" s="6" t="n">
+      <c r="I31" s="8" t="n"/>
+      <c r="J31" s="6" t="n"/>
+      <c r="K31" s="6" t="n"/>
+      <c r="L31" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="M25" s="6" t="n">
+      <c r="M31" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="N25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="6" t="n">
+      <c r="N31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="P25" s="6" t="inlineStr"/>
-      <c r="Q25" s="8" t="inlineStr"/>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="P31" s="6" t="inlineStr"/>
+      <c r="Q31" s="8" t="inlineStr"/>
+      <c r="R31" s="6" t="inlineStr">
         <is>
           <t>Rental unit</t>
         </is>
       </c>
-      <c r="S25" s="6" t="inlineStr">
+      <c r="S31" s="6" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T25" s="6" t="inlineStr">
+      <c r="T31" s="6" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="U25" s="6" t="n">
+      <c r="U31" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="V25" s="6" t="inlineStr">
+      <c r="V31" s="6" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="W25" s="6" t="inlineStr">
+      <c r="W31" s="6" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="X25" s="6" t="inlineStr">
+      <c r="X31" s="6" t="inlineStr">
         <is>
           <t>City; Garden</t>
         </is>
       </c>
-      <c r="Y25" s="9" t="inlineStr">
+      <c r="Y31" s="9" t="inlineStr">
         <is>
           <t>Dishwasher; Fireplace; Hardwood Floors; Private Outdoor Space; View; Washer Dryer</t>
         </is>
       </c>
-      <c r="Z25" s="9" t="inlineStr">
+      <c r="Z31" s="9" t="inlineStr">
         <is>
           <t>Laundry</t>
         </is>
       </c>
-      <c r="AA25" s="6" t="inlineStr"/>
-      <c r="AB25" s="6" t="inlineStr"/>
-      <c r="AC25" s="6" t="inlineStr"/>
-      <c r="AD25" s="6" t="inlineStr"/>
-      <c r="AE25" s="6" t="inlineStr"/>
-      <c r="AF25" s="6" t="n">
+      <c r="AA31" s="6" t="inlineStr"/>
+      <c r="AB31" s="6" t="inlineStr"/>
+      <c r="AC31" s="6" t="inlineStr"/>
+      <c r="AD31" s="6" t="inlineStr"/>
+      <c r="AE31" s="6" t="inlineStr"/>
+      <c r="AF31" s="6" t="n">
         <v>1900</v>
       </c>
-      <c r="AG25" s="6" t="n">
+      <c r="AG31" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="AH25" s="6" t="n">
+      <c r="AH31" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="AI25" s="6" t="inlineStr">
+      <c r="AI31" s="6" t="inlineStr">
         <is>
           <t>DALLAL</t>
         </is>
       </c>
-      <c r="AJ25" s="6" t="inlineStr">
+      <c r="AJ31" s="6" t="inlineStr">
         <is>
           <t>Dallal Group Llc</t>
         </is>
       </c>
-      <c r="AK25" s="6" t="inlineStr">
+      <c r="AK31" s="6" t="inlineStr">
         <is>
           <t>Real Estate Principal Office</t>
         </is>
       </c>
-      <c r="AL25" s="6" t="inlineStr">
+      <c r="AL31" s="6" t="inlineStr">
         <is>
           <t>260 Madison Avenue, 8th Floor, New York, NY, 10016</t>
         </is>
       </c>
-      <c r="AM25" s="6" t="inlineStr">
+      <c r="AM31" s="6" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN25" s="8" t="n">
+      <c r="AN31" s="8" t="n">
         <v>8995</v>
       </c>
-      <c r="AO25" s="9" t="inlineStr">
+      <c r="AO31" s="9" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $8,995</t>
         </is>
       </c>
-      <c r="AP25" s="6" t="inlineStr">
+      <c r="AP31" s="6" t="inlineStr">
         <is>
           <t>2026-06-08: $8,995</t>
         </is>
       </c>
-      <c r="AQ25" s="9" t="inlineStr">
+      <c r="AQ31" s="9" t="inlineStr">
         <is>
           <t>2026-06-08: $8,995 ACTIVE; 2025-07-23: $8,250 DELISTED; 2025-07-09: $8,250 None; 2025-05-18: $8,495 ACTIVE; 2025-04-22: $8,495 RENTED; 2025-03-28: $8,495 ACTIVE; 2025-03-27: $8,495 TEMPORARILY_OFF_MARKET; 2025-03-26: $8,495 ACTIVE; 2024-04-09: $5,995 RENTED; 2024-04-09: $5,995 IN_CONTRACT; 2024-04-01: $5,995 ACTIVE; 2021-04-08: $4,795 RENTED; 2021-04-07: $4,795 ACTIVE; 2020-04-13: $5,095 RENTED; 2020-04-11: $5,095 ACTIVE</t>
         </is>
       </c>
-      <c r="AR25" s="8" t="n">
+      <c r="AR31" s="8" t="n">
         <v>7400</v>
       </c>
-      <c r="AS25" s="6" t="inlineStr"/>
-      <c r="AT25" s="6" t="n">
+      <c r="AS31" s="6" t="inlineStr"/>
+      <c r="AT31" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="AU25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW25" s="6" t="inlineStr"/>
-      <c r="AX25" s="6" t="inlineStr"/>
-      <c r="AY25" s="6" t="inlineStr">
+      <c r="AU31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" s="6" t="inlineStr"/>
+      <c r="AX31" s="6" t="inlineStr"/>
+      <c r="AY31" s="6" t="inlineStr">
         <is>
           <t>PARTNER</t>
         </is>
       </c>
-      <c r="AZ25" s="6" t="n">
+      <c r="AZ31" s="6" t="n">
         <v>40.7355</v>
       </c>
-      <c r="BA25" s="6" t="n">
+      <c r="BA31" s="6" t="n">
         <v>-74.0057</v>
       </c>
-      <c r="BB25" s="6" t="inlineStr"/>
-      <c r="BC25" s="9" t="inlineStr">
+      <c r="BB31" s="6" t="inlineStr"/>
+      <c r="BC31" s="9" t="inlineStr">
         <is>
           <t>Beautifully renovated 2 bedroom duplex in prime west village!
 This stunning home is located in a well-maintained building and offers a thoughtfully updated interior with modern finishes throughout.
@@ -5816,202 +7051,202 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>5092445</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5092445</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>423 West Street #1G</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>#1G</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>West Village</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>10014</t>
         </is>
       </c>
-      <c r="H26" s="4" t="n">
+      <c r="H32" s="4" t="n">
         <v>9495</v>
       </c>
-      <c r="I26" s="4" t="n"/>
-      <c r="J26" s="2" t="n"/>
-      <c r="K26" s="2" t="n"/>
-      <c r="L26" s="2" t="n">
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M26" s="2" t="n">
+      <c r="M32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="2" t="n">
+      <c r="N32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="P26" s="2" t="inlineStr"/>
-      <c r="Q26" s="4" t="inlineStr"/>
-      <c r="R26" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="4" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>Rental unit</t>
         </is>
       </c>
-      <c r="S26" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T26" s="2" t="inlineStr">
+      <c r="T32" s="2" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="U26" s="2" t="n">
+      <c r="U32" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="W26" s="2" t="inlineStr">
+      <c r="W32" s="2" t="inlineStr">
         <is>
           <t>Terrace</t>
         </is>
       </c>
-      <c r="X26" s="2" t="inlineStr">
+      <c r="X32" s="2" t="inlineStr">
         <is>
           <t>City; Garden</t>
         </is>
       </c>
-      <c r="Y26" s="5" t="inlineStr">
+      <c r="Y32" s="5" t="inlineStr">
         <is>
           <t>Central Ac; Dishwasher; Hardwood Floors; Private Outdoor Space; View; Washer Dryer</t>
         </is>
       </c>
-      <c r="Z26" s="5" t="inlineStr">
+      <c r="Z32" s="5" t="inlineStr">
         <is>
           <t>Doorman; Elevator; Laundry; Package Room; Storage Space</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
+      <c r="AA32" s="2" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr"/>
-      <c r="AC26" s="2" t="inlineStr"/>
-      <c r="AD26" s="2" t="inlineStr">
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
         <is>
           <t>Cold Storage</t>
         </is>
       </c>
-      <c r="AE26" s="2" t="inlineStr">
+      <c r="AE32" s="2" t="inlineStr">
         <is>
           <t>FOUR23</t>
         </is>
       </c>
-      <c r="AF26" s="2" t="n">
+      <c r="AF32" s="2" t="n">
         <v>2005</v>
       </c>
-      <c r="AG26" s="2" t="n">
+      <c r="AG32" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="AH26" s="2" t="n">
+      <c r="AH32" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AI26" s="2" t="inlineStr">
+      <c r="AI32" s="2" t="inlineStr">
         <is>
           <t>Next Step Realty New York LLC</t>
         </is>
       </c>
-      <c r="AJ26" s="2" t="inlineStr">
+      <c r="AJ32" s="2" t="inlineStr">
         <is>
           <t>Next Step Realty New York Llc</t>
         </is>
       </c>
-      <c r="AK26" s="2" t="inlineStr">
+      <c r="AK32" s="2" t="inlineStr">
         <is>
           <t>Limited Liability Broker</t>
         </is>
       </c>
-      <c r="AL26" s="2" t="inlineStr">
+      <c r="AL32" s="2" t="inlineStr">
         <is>
           <t>4 East 8th Street, New York, NY, 10003</t>
         </is>
       </c>
-      <c r="AM26" s="2" t="inlineStr">
+      <c r="AM32" s="2" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN26" s="4" t="n">
+      <c r="AN32" s="4" t="n">
         <v>4750</v>
       </c>
-      <c r="AO26" s="5" t="inlineStr">
+      <c r="AO32" s="5" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $4,750</t>
         </is>
       </c>
-      <c r="AP26" s="2" t="inlineStr">
+      <c r="AP32" s="2" t="inlineStr">
         <is>
           <t>2026-07-05: $9,495</t>
         </is>
       </c>
-      <c r="AQ26" s="5" t="inlineStr">
+      <c r="AQ32" s="5" t="inlineStr">
         <is>
           <t>2026-07-06: $9,495 ACTIVE</t>
         </is>
       </c>
-      <c r="AR26" s="4" t="n">
+      <c r="AR32" s="4" t="n">
         <v>11000</v>
       </c>
-      <c r="AS26" s="2" t="inlineStr"/>
-      <c r="AT26" s="2" t="n">
+      <c r="AS32" s="2" t="inlineStr"/>
+      <c r="AT32" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="AU26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" s="2" t="inlineStr"/>
-      <c r="AX26" s="2" t="inlineStr"/>
-      <c r="AY26" s="2" t="inlineStr">
+      <c r="AU32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" s="2" t="inlineStr"/>
+      <c r="AX32" s="2" t="inlineStr"/>
+      <c r="AY32" s="2" t="inlineStr">
         <is>
           <t>PARTNER</t>
         </is>
       </c>
-      <c r="AZ26" s="2" t="n">
+      <c r="AZ32" s="2" t="n">
         <v>40.735077</v>
       </c>
-      <c r="BA26" s="2" t="n">
+      <c r="BA32" s="2" t="n">
         <v>-74.009674</v>
       </c>
-      <c r="BB26" s="2" t="inlineStr"/>
-      <c r="BC26" s="5" t="inlineStr">
+      <c r="BB32" s="2" t="inlineStr"/>
+      <c r="BC32" s="5" t="inlineStr">
         <is>
           <t>MASSIVE TRUE 3 BEDROOM IN ULTRA-PRIME WEST VILLAGE!! *Available August 1*
 IN-UNIT WASHER/DRYER - DISHWASHER - PRIVATE OUTDOOR SPACE - SPACIOUS BEDROOMS &amp; CLOSETS!
@@ -6023,198 +7258,405 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>5101731</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>https://streeteasy.com/rental/5101731</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>423 West Street #1H</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>#1H</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>West Village</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>10014</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>9495</v>
+      </c>
+      <c r="I33" s="8" t="n"/>
+      <c r="J33" s="6" t="n"/>
+      <c r="K33" s="6" t="n"/>
+      <c r="L33" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr"/>
+      <c r="Q33" s="8" t="inlineStr"/>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>Rental unit</t>
+        </is>
+      </c>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="T33" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="W33" s="6" t="inlineStr">
+        <is>
+          <t>Terrace</t>
+        </is>
+      </c>
+      <c r="X33" s="6" t="inlineStr">
+        <is>
+          <t>City; Garden</t>
+        </is>
+      </c>
+      <c r="Y33" s="9" t="inlineStr">
+        <is>
+          <t>Central Ac; Dishwasher; Hardwood Floors; Private Outdoor Space; View; Washer Dryer</t>
+        </is>
+      </c>
+      <c r="Z33" s="9" t="inlineStr">
+        <is>
+          <t>Doorman; Elevator; Laundry; Package Room; Storage Space</t>
+        </is>
+      </c>
+      <c r="AA33" s="6" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="AB33" s="6" t="inlineStr"/>
+      <c r="AC33" s="6" t="inlineStr"/>
+      <c r="AD33" s="6" t="inlineStr">
+        <is>
+          <t>Cold Storage</t>
+        </is>
+      </c>
+      <c r="AE33" s="6" t="inlineStr">
+        <is>
+          <t>FOUR23</t>
+        </is>
+      </c>
+      <c r="AF33" s="6" t="n">
+        <v>2005</v>
+      </c>
+      <c r="AG33" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH33" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI33" s="6" t="inlineStr">
+        <is>
+          <t>Next Step Realty New York LLC</t>
+        </is>
+      </c>
+      <c r="AJ33" s="6" t="inlineStr">
+        <is>
+          <t>Next Step Realty New York Llc</t>
+        </is>
+      </c>
+      <c r="AK33" s="6" t="inlineStr">
+        <is>
+          <t>Limited Liability Broker</t>
+        </is>
+      </c>
+      <c r="AL33" s="6" t="inlineStr">
+        <is>
+          <t>4 East 8th Street, New York, NY, 10003</t>
+        </is>
+      </c>
+      <c r="AM33" s="6" t="inlineStr">
+        <is>
+          <t>None listed</t>
+        </is>
+      </c>
+      <c r="AN33" s="8" t="n">
+        <v>4750</v>
+      </c>
+      <c r="AO33" s="9" t="inlineStr">
+        <is>
+          <t>Application fee: $20; Security deposit: $4,750</t>
+        </is>
+      </c>
+      <c r="AP33" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-14: $9,495</t>
+        </is>
+      </c>
+      <c r="AQ33" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-14: $9,495 ACTIVE</t>
+        </is>
+      </c>
+      <c r="AR33" s="8" t="n">
+        <v>10997</v>
+      </c>
+      <c r="AS33" s="6" t="inlineStr"/>
+      <c r="AT33" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" s="6" t="inlineStr"/>
+      <c r="AX33" s="6" t="inlineStr"/>
+      <c r="AY33" s="6" t="inlineStr">
+        <is>
+          <t>PARTNER</t>
+        </is>
+      </c>
+      <c r="AZ33" s="6" t="n">
+        <v>40.735077</v>
+      </c>
+      <c r="BA33" s="6" t="n">
+        <v>-74.009674</v>
+      </c>
+      <c r="BB33" s="6" t="inlineStr"/>
+      <c r="BC33" s="9" t="inlineStr">
+        <is>
+          <t>MASSIVE TRUE 3 BEDROOM IN ULTRA-PRIME WEST VILLAGE!! *Available August 1*
+IN-UNIT WASHER/DRYER - DISHWASHER - PRIVATE OUTDOOR SPACE - SPACIOUS BEDROOMS &amp; CLOSETS!
+Beautifully renovated 3-bedroom downtown home at 423 West Street, featuring a spacious open-concept layout, chic modern finishes, and stylish loft-inspired interiors throughout. The oversized living and dining area is perfect for entertaining, complemented by a sleek kitchen with stainless steel appliances, abundant cabinetry, and a clean contemporary design.
+All three bedrooms comfortably accommodate queen-size beds and offer excellent closet space, including a large walk-in closet with custom organization. The apartment also features a spa-inspired bathroom, dark hardwood floors, recessed lighting, and an in-unit washer/dryer for ultimate convenience.
+Thoughtfully designed with a bright, airy feel and sophisticated downtown aesthetic, this home blends comfort and functionality in one of Manhattan’s most desirable waterfront locations. Surrounded by trendy restaurants, cafés, nightlife, and nearby transportation, 423 West Street offers the perfect balance of style and convenience!
+Move-In Costs: +1st month's rent, 1/2 month security, $20 application fee, $80 move fee per person &amp; $75 key fee per apartment. No pet fee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>5088552</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5088552</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>72 Carmine Street #2C</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>#2C</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>West Village</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>10014</t>
         </is>
       </c>
-      <c r="H27" s="8" t="n">
+      <c r="H34" s="4" t="n">
         <v>9995</v>
       </c>
-      <c r="I27" s="8" t="n"/>
-      <c r="J27" s="6" t="n"/>
-      <c r="K27" s="6" t="n"/>
-      <c r="L27" s="6" t="n">
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M27" s="6" t="n">
+      <c r="M34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="N27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="6" t="n">
+      <c r="N34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="P27" s="6" t="inlineStr"/>
-      <c r="Q27" s="8" t="inlineStr"/>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="4" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>Rental unit</t>
         </is>
       </c>
-      <c r="S27" s="6" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T27" s="6" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="U27" s="6" t="n">
+      <c r="U34" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="V27" s="6" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="W27" s="6" t="inlineStr">
+      <c r="W34" s="2" t="inlineStr">
         <is>
           <t>Balcony</t>
         </is>
       </c>
-      <c r="X27" s="6" t="inlineStr">
+      <c r="X34" s="2" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="Y27" s="9" t="inlineStr">
+      <c r="Y34" s="5" t="inlineStr">
         <is>
           <t>Central Ac; Dishwasher; Hardwood Floors; Private Outdoor Space; View; Washer Dryer</t>
         </is>
       </c>
-      <c r="Z27" s="9" t="inlineStr">
+      <c r="Z34" s="5" t="inlineStr">
         <is>
           <t>Doorman; Fios Available; Shared Outdoor Space</t>
         </is>
       </c>
-      <c r="AA27" s="6" t="inlineStr">
+      <c r="AA34" s="2" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="AB27" s="6" t="inlineStr"/>
-      <c r="AC27" s="6" t="inlineStr">
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
         <is>
           <t>Courtyard</t>
         </is>
       </c>
-      <c r="AD27" s="6" t="inlineStr"/>
-      <c r="AE27" s="6" t="inlineStr"/>
-      <c r="AF27" s="6" t="n">
+      <c r="AD34" s="2" t="inlineStr"/>
+      <c r="AE34" s="2" t="inlineStr"/>
+      <c r="AF34" s="2" t="n">
         <v>1910</v>
       </c>
-      <c r="AG27" s="6" t="n">
+      <c r="AG34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AH27" s="6" t="n">
+      <c r="AH34" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="AI27" s="6" t="inlineStr">
+      <c r="AI34" s="2" t="inlineStr">
         <is>
           <t>Living New York</t>
         </is>
       </c>
-      <c r="AJ27" s="6" t="inlineStr">
+      <c r="AJ34" s="2" t="inlineStr">
         <is>
           <t>Living New York</t>
         </is>
       </c>
-      <c r="AK27" s="6" t="inlineStr">
+      <c r="AK34" s="2" t="inlineStr">
         <is>
           <t>Limited Liability Broker</t>
         </is>
       </c>
-      <c r="AL27" s="6" t="inlineStr">
+      <c r="AL34" s="2" t="inlineStr">
         <is>
           <t>225 West 35th Street Ste, 1400, New York, NY, 10001</t>
         </is>
       </c>
-      <c r="AM27" s="6" t="inlineStr">
+      <c r="AM34" s="2" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN27" s="8" t="n">
+      <c r="AN34" s="4" t="n">
         <v>4997.5</v>
       </c>
-      <c r="AO27" s="9" t="inlineStr">
+      <c r="AO34" s="5" t="inlineStr">
         <is>
           <t>Move-in fee: $80; Application fee: $20; Key replacement: $75; Security deposit: $4,998</t>
         </is>
       </c>
-      <c r="AP27" s="6" t="inlineStr">
+      <c r="AP34" s="2" t="inlineStr">
         <is>
           <t>2026-06-30: $9,995</t>
         </is>
       </c>
-      <c r="AQ27" s="9" t="inlineStr">
+      <c r="AQ34" s="5" t="inlineStr">
         <is>
           <t>2026-06-30: $9,995 ACTIVE; 2025-07-09: $8,995 RENTED; 2025-06-30: $8,995 ACTIVE; 2021-04-12: $6,995 RENTED; 2021-04-10: $6,995 NO_LONGER_AVAILABLE; 2021-04-10: $6,995 None; 2021-04-09: $6,000 ACTIVE</t>
         </is>
       </c>
-      <c r="AR27" s="8" t="n">
+      <c r="AR34" s="4" t="n">
         <v>11000</v>
       </c>
-      <c r="AS27" s="6" t="inlineStr"/>
-      <c r="AT27" s="6" t="n">
+      <c r="AS34" s="2" t="inlineStr"/>
+      <c r="AT34" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="AU27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" s="6" t="inlineStr"/>
-      <c r="AX27" s="6" t="inlineStr"/>
-      <c r="AY27" s="6" t="inlineStr">
+      <c r="AU34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" s="2" t="inlineStr"/>
+      <c r="AX34" s="2" t="inlineStr"/>
+      <c r="AY34" s="2" t="inlineStr">
         <is>
           <t>PARTNER</t>
         </is>
       </c>
-      <c r="AZ27" s="6" t="n">
+      <c r="AZ34" s="2" t="n">
         <v>40.729496</v>
       </c>
-      <c r="BA27" s="6" t="n">
+      <c r="BA34" s="2" t="n">
         <v>-74.00452</v>
       </c>
-      <c r="BB27" s="6" t="inlineStr"/>
-      <c r="BC27" s="9" t="inlineStr">
+      <c r="BB34" s="2" t="inlineStr"/>
+      <c r="BC34" s="5" t="inlineStr">
         <is>
           <t>72 Carmine Street, Apt 2C – West Village | 3 Bedroom | 2 Bathroom | PRIVATE OUTDOOR SPACE | Available 9/1
 1/2 Month Security Deposit
@@ -6239,194 +7681,390 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>5070997</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>https://streeteasy.com/rental/5070997</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>29 7th Avenue South #2D</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>#2D</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>West Village</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>10014</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>11000</v>
+      </c>
+      <c r="I35" s="8" t="n"/>
+      <c r="J35" s="6" t="n"/>
+      <c r="K35" s="6" t="n"/>
+      <c r="L35" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M35" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr"/>
+      <c r="Q35" s="8" t="inlineStr"/>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>Rental unit</t>
+        </is>
+      </c>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="T35" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="U35" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="V35" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="W35" s="6" t="inlineStr">
+        <is>
+          <t>Terrace</t>
+        </is>
+      </c>
+      <c r="X35" s="6" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="Y35" s="9" t="inlineStr">
+        <is>
+          <t>Central Ac; Dishwasher; Hardwood Floors; Private Outdoor Space; View</t>
+        </is>
+      </c>
+      <c r="Z35" s="9" t="inlineStr">
+        <is>
+          <t>Elevator; Fios Available; Laundry; Live In Super</t>
+        </is>
+      </c>
+      <c r="AA35" s="6" t="inlineStr"/>
+      <c r="AB35" s="6" t="inlineStr"/>
+      <c r="AC35" s="6" t="inlineStr"/>
+      <c r="AD35" s="6" t="inlineStr"/>
+      <c r="AE35" s="6" t="inlineStr"/>
+      <c r="AF35" s="6" t="n">
+        <v>1998</v>
+      </c>
+      <c r="AG35" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH35" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI35" s="6" t="inlineStr">
+        <is>
+          <t>Metropolitan Property Group</t>
+        </is>
+      </c>
+      <c r="AJ35" s="6" t="inlineStr">
+        <is>
+          <t>Metropolitan Property Group Ii Inc</t>
+        </is>
+      </c>
+      <c r="AK35" s="6" t="inlineStr">
+        <is>
+          <t>Corporate Broker</t>
+        </is>
+      </c>
+      <c r="AL35" s="6" t="inlineStr">
+        <is>
+          <t>369 Lexington Avenue Ste, 1202, New York, NY, 10017</t>
+        </is>
+      </c>
+      <c r="AM35" s="6" t="inlineStr">
+        <is>
+          <t>None listed</t>
+        </is>
+      </c>
+      <c r="AN35" s="8" t="n">
+        <v>11000</v>
+      </c>
+      <c r="AO35" s="9" t="inlineStr">
+        <is>
+          <t>Application fee: $20; Security deposit: $11,000</t>
+        </is>
+      </c>
+      <c r="AP35" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-12: $12,000; 2026-07-07: $11,500; 2026-07-08: $11,000</t>
+        </is>
+      </c>
+      <c r="AQ35" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-08: $11,000 None; 2026-07-07: $11,500 None; 2026-06-12: $12,000 ACTIVE; 2025-10-31: $10,000 NO_LONGER_AVAILABLE; 2025-08-01: $10,000 TEMPORARILY_OFF_MARKET; 2025-07-02: $10,000 None; 2025-06-10: $10,800 ACTIVE; 2023-10-04: $9,200 NO_LONGER_AVAILABLE; 2023-07-05: $9,200 TEMPORARILY_OFF_MARKET; 2023-06-25: $9,200 ACTIVE; 2023-06-24: $9,200 IN_CONTRACT; 2023-06-14: $9,200 ACTIVE; 2020-11-05: $6,495 NO_LONGER_AVAILABLE; 2020-08-06: $6,495 TEMPORARILY_OFF_MARKET; 2020-07-28: $6,495 None; 2020-07-20: $6,612 None; 2020-07-01: $6,900 None; 2020-06-22: $7,100 None; 2020-05-17: $7,295 ACTIVE; 2019-06-25: $6,995 NO_LONGER_AVAILABLE; 2019-06-13: $6,995 ACTIVE; 2019-05-08: $7,200 DELISTED; 2019-05-08: $7,200 NO_LONGER_AVAILABLE; 2019-05-08: $7,200 ACTIVE; 2019-05-07: $7,200 ACTIVE; 2019-05-06: $7,200 ACTIVE</t>
+        </is>
+      </c>
+      <c r="AR35" s="8" t="n">
+        <v>10997</v>
+      </c>
+      <c r="AS35" s="6" t="inlineStr">
+        <is>
+          <t>{'id': '20990414', 'startTime': '2026-07-14T11:00:00.000-04:00', 'endTime': '2026-07-14T19:00:00.000-04:00', 'appointmentOnly': True, 'showingNotes': None}</t>
+        </is>
+      </c>
+      <c r="AT35" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" s="6" t="inlineStr"/>
+      <c r="AX35" s="6" t="inlineStr"/>
+      <c r="AY35" s="6" t="inlineStr">
+        <is>
+          <t>PARTNER</t>
+        </is>
+      </c>
+      <c r="AZ35" s="6" t="n">
+        <v>40.730827</v>
+      </c>
+      <c r="BA35" s="6" t="n">
+        <v>-74.00414000000001</v>
+      </c>
+      <c r="BB35" s="6" t="inlineStr"/>
+      <c r="BC35" s="9" t="inlineStr">
+        <is>
+          <t>Rarely available 3-bedroom, 2-bath duplex in an elevator building with laundry in the heart of the West Village.
+This bright and spacious home features an open-concept living/kitchen with beautiful hardwood floors that flows directly onto a massive private terrace — ideal for outdoor dining, relaxing, or entertaining. The primary bedroom includes a wall-mounted TV and great views, while the additional bedrooms offer flexibility (perfect for home office, guests, or family).
+Updated with a dishwasher and modern bathroom. Excellent storage throughout.
+Prime location at 29 Seventh Ave South — steps to shops, restaurants, Hudson River Park, and major subway lines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>5087645</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5087645</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>53 Leroy Street #D</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>#D</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>West Village</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>10014</t>
         </is>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="H36" s="4" t="n">
         <v>11995</v>
       </c>
-      <c r="I28" s="4" t="n"/>
-      <c r="J28" s="2" t="n"/>
-      <c r="K28" s="2" t="n"/>
-      <c r="L28" s="2" t="n">
+      <c r="I36" s="4" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M28" s="2" t="n">
+      <c r="M36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="2" t="n">
+      <c r="N36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="P28" s="2" t="inlineStr"/>
-      <c r="Q28" s="4" t="inlineStr"/>
-      <c r="R28" s="2" t="inlineStr">
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="4" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>Rental unit</t>
         </is>
       </c>
-      <c r="S28" s="2" t="inlineStr">
+      <c r="S36" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T28" s="2" t="inlineStr">
+      <c r="T36" s="2" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="U28" s="2" t="n">
+      <c r="U36" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="W28" s="2" t="inlineStr">
+      <c r="W36" s="2" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="X28" s="2" t="inlineStr">
+      <c r="X36" s="2" t="inlineStr">
         <is>
           <t>City; Garden</t>
         </is>
       </c>
-      <c r="Y28" s="5" t="inlineStr">
+      <c r="Y36" s="5" t="inlineStr">
         <is>
           <t>Dishwasher; Hardwood Floors; Private Outdoor Space; View; Washer Dryer</t>
         </is>
       </c>
-      <c r="Z28" s="5" t="inlineStr">
+      <c r="Z36" s="5" t="inlineStr">
         <is>
           <t>Fios Available; Laundry; Shared Outdoor Space</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr"/>
-      <c r="AB28" s="2" t="inlineStr"/>
-      <c r="AC28" s="2" t="inlineStr">
+      <c r="AA36" s="2" t="inlineStr"/>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
         <is>
           <t>Courtyard</t>
         </is>
       </c>
-      <c r="AD28" s="2" t="inlineStr"/>
-      <c r="AE28" s="2" t="inlineStr"/>
-      <c r="AF28" s="2" t="n">
+      <c r="AD36" s="2" t="inlineStr"/>
+      <c r="AE36" s="2" t="inlineStr"/>
+      <c r="AF36" s="2" t="n">
         <v>1900</v>
       </c>
-      <c r="AG28" s="2" t="n">
+      <c r="AG36" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AH28" s="2" t="n">
+      <c r="AH36" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="AI28" s="2" t="inlineStr">
+      <c r="AI36" s="2" t="inlineStr">
         <is>
           <t>DALLAL</t>
         </is>
       </c>
-      <c r="AJ28" s="2" t="inlineStr">
+      <c r="AJ36" s="2" t="inlineStr">
         <is>
           <t>Dallal Group Llc</t>
         </is>
       </c>
-      <c r="AK28" s="2" t="inlineStr">
+      <c r="AK36" s="2" t="inlineStr">
         <is>
           <t>Real Estate Principal Office</t>
         </is>
       </c>
-      <c r="AL28" s="2" t="inlineStr">
+      <c r="AL36" s="2" t="inlineStr">
         <is>
           <t>260 Madison Avenue, 8th Floor, New York, NY, 10016</t>
         </is>
       </c>
-      <c r="AM28" s="2" t="inlineStr">
+      <c r="AM36" s="2" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN28" s="4" t="n">
+      <c r="AN36" s="4" t="n">
         <v>11995</v>
       </c>
-      <c r="AO28" s="5" t="inlineStr">
+      <c r="AO36" s="5" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $11,995</t>
         </is>
       </c>
-      <c r="AP28" s="2" t="inlineStr">
+      <c r="AP36" s="2" t="inlineStr">
         <is>
           <t>2026-06-30: $11,995</t>
         </is>
       </c>
-      <c r="AQ28" s="5" t="inlineStr">
+      <c r="AQ36" s="5" t="inlineStr">
         <is>
           <t>2026-06-30: $11,995 ACTIVE</t>
         </is>
       </c>
-      <c r="AR28" s="4" t="n">
+      <c r="AR36" s="4" t="n">
         <v>13000</v>
       </c>
-      <c r="AS28" s="2" t="inlineStr"/>
-      <c r="AT28" s="2" t="n">
+      <c r="AS36" s="2" t="inlineStr"/>
+      <c r="AT36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AU28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" s="2" t="inlineStr"/>
-      <c r="AX28" s="2" t="inlineStr"/>
-      <c r="AY28" s="2" t="inlineStr">
+      <c r="AU36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" s="2" t="inlineStr"/>
+      <c r="AX36" s="2" t="inlineStr"/>
+      <c r="AY36" s="2" t="inlineStr">
         <is>
           <t>PARTNER</t>
         </is>
       </c>
-      <c r="AZ28" s="2" t="n">
+      <c r="AZ36" s="2" t="n">
         <v>40.73021</v>
       </c>
-      <c r="BA28" s="2" t="n">
+      <c r="BA36" s="2" t="n">
         <v>-74.00512999999999</v>
       </c>
-      <c r="BB28" s="2" t="inlineStr"/>
-      <c r="BC28" s="5" t="inlineStr">
+      <c r="BB36" s="2" t="inlineStr"/>
+      <c r="BC36" s="5" t="inlineStr">
         <is>
           <t>This stunning 4 bedroom is located in a well-maintained building in prime West Village, and offers a thoughtfully updated interior with modern finishes throughout.
 Apartment Features:
@@ -6442,190 +8080,190 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>5094279</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5094279</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>145 West 10th Street #6</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>#6</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>West Village</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="G37" s="6" t="inlineStr">
         <is>
           <t>10014</t>
         </is>
       </c>
-      <c r="H29" s="8" t="n">
+      <c r="H37" s="8" t="n">
         <v>11995</v>
       </c>
-      <c r="I29" s="8" t="n"/>
-      <c r="J29" s="6" t="n"/>
-      <c r="K29" s="6" t="n"/>
-      <c r="L29" s="6" t="n">
+      <c r="I37" s="8" t="n"/>
+      <c r="J37" s="6" t="n"/>
+      <c r="K37" s="6" t="n"/>
+      <c r="L37" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="M29" s="6" t="n">
+      <c r="M37" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="N29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="6" t="n">
+      <c r="N37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="P29" s="6" t="inlineStr"/>
-      <c r="Q29" s="8" t="inlineStr"/>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="P37" s="6" t="inlineStr"/>
+      <c r="Q37" s="8" t="inlineStr"/>
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>Rental unit</t>
         </is>
       </c>
-      <c r="S29" s="6" t="inlineStr">
+      <c r="S37" s="6" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T29" s="6" t="inlineStr">
+      <c r="T37" s="6" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="U29" s="6" t="n">
+      <c r="U37" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="V29" s="6" t="inlineStr">
+      <c r="V37" s="6" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="W29" s="6" t="inlineStr">
+      <c r="W37" s="6" t="inlineStr">
         <is>
           <t>Roof Rights</t>
         </is>
       </c>
-      <c r="X29" s="6" t="inlineStr"/>
-      <c r="Y29" s="9" t="inlineStr">
+      <c r="X37" s="6" t="inlineStr"/>
+      <c r="Y37" s="9" t="inlineStr">
         <is>
           <t>Central Ac; Dishwasher; Hardwood Floors; Private Outdoor Space; Washer Dryer</t>
         </is>
       </c>
-      <c r="Z29" s="9" t="inlineStr">
+      <c r="Z37" s="9" t="inlineStr">
         <is>
           <t>Doorman; Laundry</t>
         </is>
       </c>
-      <c r="AA29" s="6" t="inlineStr">
+      <c r="AA37" s="6" t="inlineStr">
         <is>
           <t>Virtual</t>
         </is>
       </c>
-      <c r="AB29" s="6" t="inlineStr"/>
-      <c r="AC29" s="6" t="inlineStr"/>
-      <c r="AD29" s="6" t="inlineStr"/>
-      <c r="AE29" s="6" t="inlineStr"/>
-      <c r="AF29" s="6" t="n">
+      <c r="AB37" s="6" t="inlineStr"/>
+      <c r="AC37" s="6" t="inlineStr"/>
+      <c r="AD37" s="6" t="inlineStr"/>
+      <c r="AE37" s="6" t="inlineStr"/>
+      <c r="AF37" s="6" t="n">
         <v>1900</v>
       </c>
-      <c r="AG29" s="6" t="n">
+      <c r="AG37" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="AH29" s="6" t="n">
+      <c r="AH37" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="AI29" s="6" t="inlineStr">
+      <c r="AI37" s="6" t="inlineStr">
         <is>
           <t>Living New York</t>
         </is>
       </c>
-      <c r="AJ29" s="6" t="inlineStr">
+      <c r="AJ37" s="6" t="inlineStr">
         <is>
           <t>Living New York</t>
         </is>
       </c>
-      <c r="AK29" s="6" t="inlineStr">
+      <c r="AK37" s="6" t="inlineStr">
         <is>
           <t>Limited Liability Broker</t>
         </is>
       </c>
-      <c r="AL29" s="6" t="inlineStr">
+      <c r="AL37" s="6" t="inlineStr">
         <is>
           <t>225 West 35th Street Ste, 1400, New York, NY, 10001</t>
         </is>
       </c>
-      <c r="AM29" s="6" t="inlineStr">
+      <c r="AM37" s="6" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN29" s="8" t="n">
+      <c r="AN37" s="8" t="n">
         <v>5997.5</v>
       </c>
-      <c r="AO29" s="9" t="inlineStr">
+      <c r="AO37" s="9" t="inlineStr">
         <is>
           <t>Move-in fee: $80; Application fee: $20; Key replacement: $75; Security deposit: $5,998</t>
         </is>
       </c>
-      <c r="AP29" s="6" t="inlineStr">
+      <c r="AP37" s="6" t="inlineStr">
         <is>
           <t>2026-07-07: $11,995</t>
         </is>
       </c>
-      <c r="AQ29" s="9" t="inlineStr">
+      <c r="AQ37" s="9" t="inlineStr">
         <is>
           <t>2026-07-07: $11,995 ACTIVE</t>
         </is>
       </c>
-      <c r="AR29" s="8" t="n">
+      <c r="AR37" s="8" t="n">
         <v>13000</v>
       </c>
-      <c r="AS29" s="6" t="inlineStr"/>
-      <c r="AT29" s="6" t="n">
+      <c r="AS37" s="6" t="inlineStr"/>
+      <c r="AT37" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="AU29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW29" s="6" t="inlineStr"/>
-      <c r="AX29" s="6" t="inlineStr"/>
-      <c r="AY29" s="6" t="inlineStr">
+      <c r="AU37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" s="6" t="inlineStr"/>
+      <c r="AX37" s="6" t="inlineStr"/>
+      <c r="AY37" s="6" t="inlineStr">
         <is>
           <t>PARTNER</t>
         </is>
       </c>
-      <c r="AZ29" s="6" t="n">
+      <c r="AZ37" s="6" t="n">
         <v>40.734726</v>
       </c>
-      <c r="BA29" s="6" t="n">
+      <c r="BA37" s="6" t="n">
         <v>-74.00106</v>
       </c>
-      <c r="BB29" s="6" t="inlineStr"/>
-      <c r="BC29" s="9" t="inlineStr">
+      <c r="BB37" s="6" t="inlineStr"/>
+      <c r="BC37" s="9" t="inlineStr">
         <is>
           <t>145 West 10th Street – West Village | 4 Bedroom | 2 Bathroom | Available 9/1 |
 1/2 Month Security deposit|
@@ -6652,198 +8290,198 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>5033049</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5033049</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>36 Bedford Street #2</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>West Village</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>10014</t>
         </is>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="H38" s="4" t="n">
         <v>12500</v>
       </c>
-      <c r="I30" s="4" t="n"/>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2" t="n">
+      <c r="I38" s="4" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M30" s="2" t="n">
+      <c r="M38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="2" t="n">
+      <c r="N38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P30" s="2" t="n">
+      <c r="P38" s="2" t="n">
         <v>1200</v>
       </c>
-      <c r="Q30" s="4" t="n">
+      <c r="Q38" s="4" t="n">
         <v>125</v>
       </c>
-      <c r="R30" s="2" t="inlineStr">
+      <c r="R38" s="2" t="inlineStr">
         <is>
           <t>Four-family home</t>
         </is>
       </c>
-      <c r="S30" s="2" t="inlineStr">
+      <c r="S38" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T30" s="2" t="inlineStr">
+      <c r="T38" s="2" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="U30" s="2" t="n">
+      <c r="U38" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="W30" s="2" t="inlineStr">
+      <c r="W38" s="2" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="X30" s="2" t="inlineStr">
+      <c r="X38" s="2" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="Y30" s="5" t="inlineStr">
+      <c r="Y38" s="5" t="inlineStr">
         <is>
           <t>Dishwasher; Hardwood Floors; Private Outdoor Space; View; Washer Dryer</t>
         </is>
       </c>
-      <c r="Z30" s="5" t="inlineStr">
+      <c r="Z38" s="5" t="inlineStr">
         <is>
           <t>Shared Outdoor Space</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr"/>
-      <c r="AB30" s="2" t="inlineStr"/>
-      <c r="AC30" s="2" t="inlineStr">
+      <c r="AA38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
         <is>
           <t>Courtyard</t>
         </is>
       </c>
-      <c r="AD30" s="2" t="inlineStr"/>
-      <c r="AE30" s="2" t="inlineStr"/>
-      <c r="AF30" s="2" t="n">
+      <c r="AD38" s="2" t="inlineStr"/>
+      <c r="AE38" s="2" t="inlineStr"/>
+      <c r="AF38" s="2" t="n">
         <v>1915</v>
       </c>
-      <c r="AG30" s="2" t="n">
+      <c r="AG38" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AH30" s="2" t="n">
+      <c r="AH38" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AI30" s="2" t="inlineStr">
+      <c r="AI38" s="2" t="inlineStr">
         <is>
           <t>Corcoran</t>
         </is>
       </c>
-      <c r="AJ30" s="2" t="inlineStr">
+      <c r="AJ38" s="2" t="inlineStr">
         <is>
           <t>Corcoran Group</t>
         </is>
       </c>
-      <c r="AK30" s="2" t="inlineStr">
+      <c r="AK38" s="2" t="inlineStr">
         <is>
           <t>Limited Liability Broker</t>
         </is>
       </c>
-      <c r="AL30" s="2" t="inlineStr">
+      <c r="AL38" s="2" t="inlineStr">
         <is>
           <t>590 Madison Avenue, New York, NY, 10022</t>
         </is>
       </c>
-      <c r="AM30" s="2" t="inlineStr">
+      <c r="AM38" s="2" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN30" s="4" t="n">
+      <c r="AN38" s="4" t="n">
         <v>12500</v>
       </c>
-      <c r="AO30" s="5" t="inlineStr">
+      <c r="AO38" s="5" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $12,500</t>
         </is>
       </c>
-      <c r="AP30" s="2" t="inlineStr">
+      <c r="AP38" s="2" t="inlineStr">
         <is>
           <t>2026-05-04: $12,500</t>
         </is>
       </c>
-      <c r="AQ30" s="5" t="inlineStr">
+      <c r="AQ38" s="5" t="inlineStr">
         <is>
           <t>2026-07-06: $12,500 ACTIVE; 2026-07-02: $12,500 TEMPORARILY_OFF_MARKET; 2026-06-14: $12,500 ACTIVE; 2026-06-13: $12,500 IN_CONTRACT; 2026-06-10: $12,500 TEMPORARILY_OFF_MARKET; 2026-05-26: $12,500 ACTIVE; 2026-05-20: $12,500 IN_CONTRACT; 2026-05-20: $12,500 TEMPORARILY_OFF_MARKET; 2026-05-14: $12,500 ACTIVE; 2025-06-14: $12,500 RENTED; 2025-06-13: $12,500 NO_LONGER_AVAILABLE; 2025-06-12: $12,500 None; 2025-06-10: $12,000 None; 2025-06-07: $11,000 ACTIVE; 2022-04-28: $9,850 RENTED; 2022-04-25: $9,850 IN_CONTRACT; 2022-04-22: $9,850 ACTIVE; 2019-05-23: $10,000 NO_LONGER_AVAILABLE; 2016-09-01: $9,000 RENTED; 2016-08-24: $9,000 None; 2016-08-13: $9,600 ACTIVE; 2016-08-12: $9,750 NO_LONGER_AVAILABLE; 2016-07-22: $9,750 None; 2016-07-19: $11,500 None; 2016-07-13: $11,800 None; 2016-07-06: $10,000 None; 2016-06-27: $10,750 None; 2016-06-01: $11,000 ACTIVE; 2013-07-22: $10,000 TEMPORARILY_OFF_MARKET; 2013-06-13: $10,000 None; 2013-05-23: $11,000 None; 2013-05-17: $12,500 None; 2013-05-17: $12,000 ACTIVE; 2013-03-16: $12,500 NO_LONGER_AVAILABLE; 2013-02-06: $12,500 ACTIVE; 2009-07-03: $7,500 NO_LONGER_AVAILABLE; 2009-06-30: $7,500 IN_CONTRACT; 2009-06-03: $7,500 ACTIVE; 2009-03-06: $7,999 NO_LONGER_AVAILABLE; 2009-01-28: $7,999 None; 2008-12-21: $8,500 ACTIVE</t>
         </is>
       </c>
-      <c r="AR30" s="4" t="n">
+      <c r="AR38" s="4" t="n">
         <v>7400</v>
       </c>
-      <c r="AS30" s="2" t="inlineStr"/>
-      <c r="AT30" s="2" t="n">
+      <c r="AS38" s="2" t="inlineStr"/>
+      <c r="AT38" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="AU30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW30" s="2" t="inlineStr"/>
-      <c r="AX30" s="2" t="inlineStr"/>
-      <c r="AY30" s="2" t="inlineStr">
+      <c r="AU38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" s="2" t="inlineStr"/>
+      <c r="AX38" s="2" t="inlineStr"/>
+      <c r="AY38" s="2" t="inlineStr">
         <is>
           <t>PARTNER</t>
         </is>
       </c>
-      <c r="AZ30" s="2" t="n">
+      <c r="AZ38" s="2" t="n">
         <v>40.730225</v>
       </c>
-      <c r="BA30" s="2" t="n">
+      <c r="BA38" s="2" t="n">
         <v>-74.00395</v>
       </c>
-      <c r="BB30" s="2" t="inlineStr"/>
-      <c r="BC30" s="5" t="inlineStr">
+      <c r="BB38" s="2" t="inlineStr"/>
+      <c r="BC38" s="5" t="inlineStr">
         <is>
           <t>36 Bedford Street #2 1200sq Plus 1000sq feet Massive Private outdoor space with Washer/Dryer
 INDOOR and OUTDOOR LIVING AT ITS BEST
@@ -6855,202 +8493,202 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>5093236</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5093236</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>1 7th Avenue South #2</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
         <is>
           <t>West Village</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>10014</t>
         </is>
       </c>
-      <c r="H31" s="8" t="n">
+      <c r="H39" s="8" t="n">
         <v>14000</v>
       </c>
-      <c r="I31" s="8" t="n"/>
-      <c r="J31" s="6" t="n"/>
-      <c r="K31" s="6" t="n"/>
-      <c r="L31" s="6" t="n">
+      <c r="I39" s="8" t="n"/>
+      <c r="J39" s="6" t="n"/>
+      <c r="K39" s="6" t="n"/>
+      <c r="L39" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="M31" s="6" t="n">
+      <c r="M39" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="N31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="6" t="n">
+      <c r="N39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="P39" s="6" t="n">
         <v>1558</v>
       </c>
-      <c r="Q31" s="8" t="n">
+      <c r="Q39" s="8" t="n">
         <v>108</v>
       </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>Rental unit</t>
         </is>
       </c>
-      <c r="S31" s="6" t="inlineStr">
+      <c r="S39" s="6" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T31" s="6" t="inlineStr">
+      <c r="T39" s="6" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="U31" s="6" t="n">
+      <c r="U39" s="6" t="n">
         <v>115</v>
       </c>
-      <c r="V31" s="6" t="inlineStr">
+      <c r="V39" s="6" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="W31" s="6" t="inlineStr">
+      <c r="W39" s="6" t="inlineStr">
         <is>
           <t>Balcony</t>
         </is>
       </c>
-      <c r="X31" s="6" t="inlineStr">
+      <c r="X39" s="6" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="Y31" s="9" t="inlineStr">
+      <c r="Y39" s="9" t="inlineStr">
         <is>
           <t>Central Ac; Dishwasher; Hardwood Floors; Private Outdoor Space; View; Washer Dryer</t>
         </is>
       </c>
-      <c r="Z31" s="9" t="inlineStr">
+      <c r="Z39" s="9" t="inlineStr">
         <is>
           <t>Elevator; Fios Available; Storage Space</t>
         </is>
       </c>
-      <c r="AA31" s="6" t="inlineStr"/>
-      <c r="AB31" s="6" t="inlineStr"/>
-      <c r="AC31" s="6" t="inlineStr"/>
-      <c r="AD31" s="6" t="inlineStr">
+      <c r="AA39" s="6" t="inlineStr"/>
+      <c r="AB39" s="6" t="inlineStr"/>
+      <c r="AC39" s="6" t="inlineStr"/>
+      <c r="AD39" s="6" t="inlineStr">
         <is>
           <t>Locker Cage</t>
         </is>
       </c>
-      <c r="AE31" s="6" t="inlineStr">
+      <c r="AE39" s="6" t="inlineStr">
         <is>
           <t>One 7th</t>
         </is>
       </c>
-      <c r="AF31" s="6" t="n">
+      <c r="AF39" s="6" t="n">
         <v>2006</v>
       </c>
-      <c r="AG31" s="6" t="n">
+      <c r="AG39" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="AH31" s="6" t="n">
+      <c r="AH39" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="AI31" s="6" t="inlineStr">
+      <c r="AI39" s="6" t="inlineStr">
         <is>
           <t>Douglas Elliman</t>
         </is>
       </c>
-      <c r="AJ31" s="6" t="inlineStr">
+      <c r="AJ39" s="6" t="inlineStr">
         <is>
           <t>Douglas Elliman Real Estate</t>
         </is>
       </c>
-      <c r="AK31" s="6" t="inlineStr">
+      <c r="AK39" s="6" t="inlineStr">
         <is>
           <t>Limited Liability Broker</t>
         </is>
       </c>
-      <c r="AL31" s="6" t="inlineStr">
+      <c r="AL39" s="6" t="inlineStr">
         <is>
           <t>575 Madison Avenue, 4th Floor, New York, NY, 10022</t>
         </is>
       </c>
-      <c r="AM31" s="6" t="inlineStr">
+      <c r="AM39" s="6" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN31" s="8" t="n">
+      <c r="AN39" s="8" t="n">
         <v>14000</v>
       </c>
-      <c r="AO31" s="9" t="inlineStr">
+      <c r="AO39" s="9" t="inlineStr">
         <is>
           <t>Application fee: $0; Security deposit: $14,000</t>
         </is>
       </c>
-      <c r="AP31" s="6" t="inlineStr">
+      <c r="AP39" s="6" t="inlineStr">
         <is>
           <t>2026-07-06: $14,000</t>
         </is>
       </c>
-      <c r="AQ31" s="9" t="inlineStr">
+      <c r="AQ39" s="9" t="inlineStr">
         <is>
           <t>2026-07-06: $14,000 ACTIVE; 2026-07-04: $14,000 DELISTED; 2026-05-12: $14,000 None; 2026-05-09: $14,700 None; 2026-03-18: $15,000 ACTIVE; 2023-11-13: $10,500 NO_LONGER_AVAILABLE; 2023-08-14: $10,500 TEMPORARILY_OFF_MARKET; 2023-07-28: $10,500 ACTIVE; 2023-07-27: $10,500 TEMPORARILY_OFF_MARKET; 2023-07-26: $10,500 ACTIVE; 2021-08-19: $7,295 RENTED; 2021-08-17: $7,295 ACTIVE; 2021-08-16: $7,295 TEMPORARILY_OFF_MARKET; 2021-08-16: $7,295 ACTIVE; 2019-10-07: $7,950 RENTED; 2019-10-04: $7,950 IN_CONTRACT; 2019-09-24: $7,950 ACTIVE; 2016-03-23: $8,600 RENTED; 2016-03-05: $8,600 NO_LONGER_AVAILABLE; 2016-02-03: $8,600 None; 2016-01-22: $9,500 ACTIVE; 2013-09-08: $7,750 NO_LONGER_AVAILABLE; 2013-09-03: $7,750 None; 2013-08-02: $7,950 None; 2013-07-12: $8,500 ACTIVE; 2013-07-09: $8,500 TEMPORARILY_OFF_MARKET; 2013-07-09: $8,500 ACTIVE; 2011-09-09: $7,500 NO_LONGER_AVAILABLE; 2011-08-09: $7,500 ACTIVE; 2008-12-12: $7,500 NO_LONGER_AVAILABLE; 2008-10-17: $7,500 None; 2008-09-26: $8,000 ACTIVE; 2008-09-09: $8,000 NO_LONGER_AVAILABLE; 2008-09-09: $8,000 NO_LONGER_AVAILABLE; 2008-09-09: $8,000 IN_CONTRACT; 2008-09-04: $8,000 ACTIVE</t>
         </is>
       </c>
-      <c r="AR31" s="8" t="n">
+      <c r="AR39" s="8" t="n">
         <v>7400</v>
       </c>
-      <c r="AS31" s="6" t="inlineStr"/>
-      <c r="AT31" s="6" t="n">
+      <c r="AS39" s="6" t="inlineStr"/>
+      <c r="AT39" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="AU31" s="6" t="n">
+      <c r="AU39" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="AV31" s="6" t="n">
+      <c r="AV39" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="AW31" s="6" t="inlineStr"/>
-      <c r="AX31" s="6" t="inlineStr"/>
-      <c r="AY31" s="6" t="inlineStr">
+      <c r="AW39" s="6" t="inlineStr"/>
+      <c r="AX39" s="6" t="inlineStr"/>
+      <c r="AY39" s="6" t="inlineStr">
         <is>
           <t>PARTNER</t>
         </is>
       </c>
-      <c r="AZ31" s="6" t="n">
+      <c r="AZ39" s="6" t="n">
         <v>40.72976</v>
       </c>
-      <c r="BA31" s="6" t="n">
+      <c r="BA39" s="6" t="n">
         <v>-74.00476999999999</v>
       </c>
-      <c r="BB31" s="6" t="inlineStr"/>
-      <c r="BC31" s="9" t="inlineStr">
+      <c r="BB39" s="6" t="inlineStr"/>
+      <c r="BC39" s="9" t="inlineStr">
         <is>
           <t>Introducing Residence 2 at 1 Seventh Avenue South — a rare full-floor 2-bedroom, 2-bathroom residence spanning approximately 1,558 square feet, with direct keyed elevator entry, 10-foot ceilings, refined modern finishes, and a distinctive architectural presence in the heart of Greenwich Village.
 Perfectly positioned where Greenwich Village, the West Village, SoHo, and Hudson Square meet, this striking home offers a thoughtful blend of privacy, natural light, and downtown sophistication. The building’s unique triangular form allows for oversized floor-to-ceiling windows, open exposures, and a layout that feels both architecturally distinct and highly livable.
@@ -7066,202 +8704,202 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>5045721</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>https://streeteasy.com/rental/5045721</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>369 Bleecker Street #PH</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>#PH</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>West Village</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>10014</t>
         </is>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="H40" s="4" t="n">
         <v>17999</v>
       </c>
-      <c r="I32" s="4" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="n">
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M32" s="2" t="n">
+      <c r="M40" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="N32" s="2" t="n">
+      <c r="N40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O32" s="2" t="n">
+      <c r="O40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="P32" s="2" t="n">
+      <c r="P40" s="2" t="n">
         <v>1600</v>
       </c>
-      <c r="Q32" s="4" t="n">
+      <c r="Q40" s="4" t="n">
         <v>135</v>
       </c>
-      <c r="R32" s="2" t="inlineStr">
+      <c r="R40" s="2" t="inlineStr">
         <is>
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="S32" s="2" t="inlineStr">
+      <c r="S40" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="T32" s="2" t="inlineStr">
+      <c r="T40" s="2" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="U32" s="2" t="n">
+      <c r="U40" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="W32" s="2" t="inlineStr">
+      <c r="W40" s="2" t="inlineStr">
         <is>
           <t>Private Roof Deck</t>
         </is>
       </c>
-      <c r="X32" s="2" t="inlineStr">
+      <c r="X40" s="2" t="inlineStr">
         <is>
           <t>City; Skyline</t>
         </is>
       </c>
-      <c r="Y32" s="5" t="inlineStr">
+      <c r="Y40" s="5" t="inlineStr">
         <is>
           <t>Central Ac; Dishwasher; Fireplace; Furnished; Hardwood Floors; Private Outdoor Space; View; Washer Dryer</t>
         </is>
       </c>
-      <c r="Z32" s="5" t="inlineStr">
+      <c r="Z40" s="5" t="inlineStr">
         <is>
           <t>Fios Available; Laundry; Shared Outdoor Space</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr"/>
-      <c r="AB32" s="2" t="inlineStr"/>
-      <c r="AC32" s="2" t="inlineStr">
+      <c r="AA40" s="2" t="inlineStr"/>
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
         <is>
           <t>Roof Deck</t>
         </is>
       </c>
-      <c r="AD32" s="2" t="inlineStr"/>
-      <c r="AE32" s="2" t="inlineStr">
+      <c r="AD40" s="2" t="inlineStr"/>
+      <c r="AE40" s="2" t="inlineStr">
         <is>
           <t>Maison Pierre</t>
         </is>
       </c>
-      <c r="AF32" s="2" t="n">
+      <c r="AF40" s="2" t="n">
         <v>1905</v>
       </c>
-      <c r="AG32" s="2" t="n">
+      <c r="AG40" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AH32" s="2" t="n">
+      <c r="AH40" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AI32" s="2" t="inlineStr">
+      <c r="AI40" s="2" t="inlineStr">
         <is>
           <t>Lodger Corp</t>
         </is>
       </c>
-      <c r="AJ32" s="2" t="inlineStr">
+      <c r="AJ40" s="2" t="inlineStr">
         <is>
           <t>Lodgers Corp</t>
         </is>
       </c>
-      <c r="AK32" s="2" t="inlineStr">
+      <c r="AK40" s="2" t="inlineStr">
         <is>
           <t>Corporate Broker</t>
         </is>
       </c>
-      <c r="AL32" s="2" t="inlineStr">
+      <c r="AL40" s="2" t="inlineStr">
         <is>
           <t>4102 13th Avenue, #6a, Brooklyn, NY, 11219</t>
         </is>
       </c>
-      <c r="AM32" s="2" t="inlineStr">
+      <c r="AM40" s="2" t="inlineStr">
         <is>
           <t>None listed</t>
         </is>
       </c>
-      <c r="AN32" s="4" t="n">
+      <c r="AN40" s="4" t="n">
         <v>16999</v>
       </c>
-      <c r="AO32" s="5" t="inlineStr">
+      <c r="AO40" s="5" t="inlineStr">
         <is>
           <t>Application fee: $20; Security deposit: $16,999</t>
         </is>
       </c>
-      <c r="AP32" s="2" t="inlineStr">
+      <c r="AP40" s="2" t="inlineStr">
         <is>
           <t>2026-05-17: $21,999; 2026-05-28: $20,999; 2026-06-07: $19,999; 2026-06-22: $18,999; 2026-06-25: $17,999</t>
         </is>
       </c>
-      <c r="AQ32" s="5" t="inlineStr">
+      <c r="AQ40" s="5" t="inlineStr">
         <is>
           <t>2026-06-25: $17,999 None; 2026-06-22: $18,999 None; 2026-06-07: $19,999 None; 2026-05-28: $20,999 None; 2026-05-17: $21,999 ACTIVE; 2021-02-05: $14,000 NO_LONGER_AVAILABLE; 2020-11-06: $14,000 TEMPORARILY_OFF_MARKET; 2020-01-31: $14,000 ACTIVE; 2019-06-04: $18,000 NO_LONGER_AVAILABLE; 2019-04-22: $18,000 None; 2018-12-17: $20,000 ACTIVE</t>
         </is>
       </c>
-      <c r="AR32" s="4" t="n">
+      <c r="AR40" s="4" t="n">
         <v>7400</v>
       </c>
-      <c r="AS32" s="2" t="inlineStr"/>
-      <c r="AT32" s="2" t="n">
+      <c r="AS40" s="2" t="inlineStr"/>
+      <c r="AT40" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="AU32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV32" s="2" t="n">
+      <c r="AU40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AW32" s="2" t="inlineStr"/>
-      <c r="AX32" s="2" t="inlineStr"/>
-      <c r="AY32" s="2" t="inlineStr">
+      <c r="AW40" s="2" t="inlineStr"/>
+      <c r="AX40" s="2" t="inlineStr"/>
+      <c r="AY40" s="2" t="inlineStr">
         <is>
           <t>PARTNER</t>
         </is>
       </c>
-      <c r="AZ32" s="2" t="n">
+      <c r="AZ40" s="2" t="n">
         <v>40.734848</v>
       </c>
-      <c r="BA32" s="2" t="n">
+      <c r="BA40" s="2" t="n">
         <v>-74.00463999999999</v>
       </c>
-      <c r="BB32" s="2" t="inlineStr"/>
-      <c r="BC32" s="5" t="inlineStr">
+      <c r="BB40" s="2" t="inlineStr"/>
+      <c r="BC40" s="5" t="inlineStr">
         <is>
           <t>A rare 2-bedroom 2.5-bath West Village penthouse duplex on iconic Bleecker Street with a private roof deck and sweeping skyline views—an exceptional offering in one of Manhattan’s most coveted neighborhoods.
 The upper level is designed for entertaining, featuring a spacious living room with gas fireplace, wet bar with Sub-Zero wine refrigerator, and a sun-filled west-facing chef’s kitchen with marble countertops and top-tier appliances. A dramatic skylight above the dining area fills the home with natural light throughout the day.
@@ -7272,7 +8910,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BC32"/>
+  <autoFilter ref="A1:BC40"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
@@ -7305,6 +8943,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7316,7 +8962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7326,7 +8972,7 @@
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>StreetEasy Listings — shared 2026-07-12</t>
+          <t>StreetEasy Listings — shared 7/12–7/14/2026 (39 listings)</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr"/>
@@ -7338,7 +8984,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -7348,7 +8994,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>10375</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="5">
@@ -7396,7 +9042,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -7406,23 +9052,23 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Greenwich Village</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>West Chelsea</t>
+          <t>Greenwich Village</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -7432,68 +9078,78 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Noho</t>
+          <t>West Chelsea</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Soho</t>
+          <t>Noho</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>By bedrooms</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr"/>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Soho</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2 BR</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>17</v>
-      </c>
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>By bedrooms</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3 BR</t>
+          <t>2 BR</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4 BR</t>
+          <t>3 BR</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>4 BR</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>5 BR</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" t="n">
         <v>1</v>
       </c>
     </row>
